--- a/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
+++ b/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$L$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$N$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L259"/>
+  <dimension ref="A1:N259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,8 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,6 +507,16 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t># styles rolled up</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Legacy Core Assortment FW27</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Agrees with new FW27-active?</t>
         </is>
       </c>
     </row>
@@ -545,6 +557,12 @@
       <c r="L2" t="n">
         <v>1</v>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -583,6 +601,16 @@
       <c r="L3" t="n">
         <v>1</v>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -625,6 +653,16 @@
       <c r="L4" t="n">
         <v>2</v>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -667,6 +705,12 @@
       <c r="L5" t="n">
         <v>2</v>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -705,6 +749,12 @@
       <c r="L6" t="n">
         <v>1</v>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -743,6 +793,12 @@
       <c r="L7" t="n">
         <v>1</v>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -781,6 +837,12 @@
       <c r="L8" t="n">
         <v>1</v>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -819,6 +881,12 @@
       <c r="L9" t="n">
         <v>1</v>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -861,6 +929,12 @@
       <c r="L10" t="n">
         <v>2</v>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -899,6 +973,12 @@
       <c r="L11" t="n">
         <v>1</v>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -937,6 +1017,12 @@
       <c r="L12" t="n">
         <v>1</v>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -975,6 +1061,12 @@
       <c r="L13" t="n">
         <v>1</v>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1013,6 +1105,12 @@
       <c r="L14" t="n">
         <v>1</v>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1051,6 +1149,12 @@
       <c r="L15" t="n">
         <v>1</v>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1093,6 +1197,12 @@
       <c r="L16" t="n">
         <v>2</v>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1131,6 +1241,12 @@
       <c r="L17" t="n">
         <v>1</v>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1169,6 +1285,12 @@
       <c r="L18" t="n">
         <v>1</v>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1207,6 +1329,12 @@
       <c r="L19" t="n">
         <v>1</v>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1245,6 +1373,12 @@
       <c r="L20" t="n">
         <v>1</v>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1283,6 +1417,12 @@
       <c r="L21" t="n">
         <v>1</v>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1321,6 +1461,12 @@
       <c r="L22" t="n">
         <v>1</v>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1369,6 +1515,12 @@
       <c r="L23" t="n">
         <v>2</v>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1411,6 +1563,12 @@
       <c r="L24" t="n">
         <v>2</v>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1449,6 +1607,12 @@
       <c r="L25" t="n">
         <v>1</v>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1491,6 +1655,12 @@
       <c r="L26" t="n">
         <v>2</v>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1533,6 +1703,12 @@
       <c r="L27" t="n">
         <v>2</v>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1575,6 +1751,12 @@
       <c r="L28" t="n">
         <v>2</v>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1617,6 +1799,12 @@
       <c r="L29" t="n">
         <v>2</v>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1659,6 +1847,12 @@
       <c r="L30" t="n">
         <v>2</v>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1701,6 +1895,12 @@
       <c r="L31" t="n">
         <v>2</v>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1743,6 +1943,12 @@
       <c r="L32" t="n">
         <v>2</v>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1785,6 +1991,12 @@
       <c r="L33" t="n">
         <v>2</v>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1827,6 +2039,12 @@
       <c r="L34" t="n">
         <v>2</v>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1869,6 +2087,12 @@
       <c r="L35" t="n">
         <v>2</v>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1911,6 +2135,12 @@
       <c r="L36" t="n">
         <v>2</v>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1957,6 +2187,12 @@
       <c r="L37" t="n">
         <v>3</v>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1999,6 +2235,16 @@
       <c r="L38" t="n">
         <v>2</v>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2041,6 +2287,16 @@
       <c r="L39" t="n">
         <v>2</v>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2083,6 +2339,12 @@
       <c r="L40" t="n">
         <v>2</v>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2125,6 +2387,12 @@
       <c r="L41" t="n">
         <v>2</v>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2167,6 +2435,12 @@
       <c r="L42" t="n">
         <v>2</v>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2209,6 +2483,12 @@
       <c r="L43" t="n">
         <v>2</v>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2251,6 +2531,12 @@
       <c r="L44" t="n">
         <v>2</v>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2293,6 +2579,12 @@
       <c r="L45" t="n">
         <v>2</v>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2335,6 +2627,16 @@
       <c r="L46" t="n">
         <v>2</v>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2377,6 +2679,12 @@
       <c r="L47" t="n">
         <v>2</v>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2419,6 +2727,12 @@
       <c r="L48" t="n">
         <v>2</v>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2461,6 +2775,12 @@
       <c r="L49" t="n">
         <v>2</v>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2503,6 +2823,12 @@
       <c r="L50" t="n">
         <v>2</v>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2545,6 +2871,12 @@
       <c r="L51" t="n">
         <v>2</v>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2583,6 +2915,12 @@
       <c r="L52" t="n">
         <v>2</v>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2621,6 +2959,12 @@
       <c r="L53" t="n">
         <v>2</v>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2659,6 +3003,12 @@
       <c r="L54" t="n">
         <v>2</v>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2697,6 +3047,12 @@
       <c r="L55" t="n">
         <v>2</v>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2739,6 +3095,12 @@
       <c r="L56" t="n">
         <v>2</v>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2781,6 +3143,16 @@
       <c r="L57" t="n">
         <v>2</v>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2823,6 +3195,16 @@
       <c r="L58" t="n">
         <v>2</v>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2865,6 +3247,12 @@
       <c r="L59" t="n">
         <v>2</v>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2907,6 +3295,12 @@
       <c r="L60" t="n">
         <v>2</v>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2949,6 +3343,12 @@
       <c r="L61" t="n">
         <v>2</v>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2995,6 +3395,12 @@
       <c r="L62" t="n">
         <v>2</v>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3041,6 +3447,12 @@
       <c r="L63" t="n">
         <v>2</v>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3083,6 +3495,16 @@
       <c r="L64" t="n">
         <v>2</v>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3128,6 +3550,16 @@
       </c>
       <c r="L65" t="n">
         <v>3</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -3171,6 +3603,12 @@
       <c r="L66" t="n">
         <v>2</v>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3213,6 +3651,12 @@
       <c r="L67" t="n">
         <v>2</v>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3255,6 +3699,12 @@
       <c r="L68" t="n">
         <v>2</v>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3297,6 +3747,12 @@
       <c r="L69" t="n">
         <v>2</v>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3339,6 +3795,12 @@
       <c r="L70" t="n">
         <v>2</v>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3381,6 +3843,12 @@
       <c r="L71" t="n">
         <v>2</v>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3423,6 +3891,12 @@
       <c r="L72" t="n">
         <v>2</v>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3465,6 +3939,12 @@
       <c r="L73" t="n">
         <v>2</v>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3507,6 +3987,12 @@
       <c r="L74" t="n">
         <v>2</v>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3549,6 +4035,12 @@
       <c r="L75" t="n">
         <v>2</v>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3591,6 +4083,12 @@
       <c r="L76" t="n">
         <v>2</v>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3633,6 +4131,12 @@
       <c r="L77" t="n">
         <v>2</v>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3675,6 +4179,12 @@
       <c r="L78" t="n">
         <v>2</v>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3717,6 +4227,12 @@
       <c r="L79" t="n">
         <v>2</v>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3759,6 +4275,12 @@
       <c r="L80" t="n">
         <v>4</v>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3801,6 +4323,12 @@
       <c r="L81" t="n">
         <v>4</v>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3839,6 +4367,12 @@
       <c r="L82" t="n">
         <v>2</v>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3881,6 +4415,12 @@
       <c r="L83" t="n">
         <v>4</v>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3923,6 +4463,12 @@
       <c r="L84" t="n">
         <v>4</v>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3961,6 +4507,12 @@
       <c r="L85" t="n">
         <v>2</v>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4003,6 +4555,16 @@
       <c r="L86" t="n">
         <v>4</v>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4045,6 +4607,12 @@
       <c r="L87" t="n">
         <v>4</v>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4087,6 +4655,12 @@
       <c r="L88" t="n">
         <v>4</v>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4129,6 +4703,12 @@
       <c r="L89" t="n">
         <v>4</v>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4177,6 +4757,12 @@
       <c r="L90" t="n">
         <v>4</v>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4219,6 +4805,12 @@
       <c r="L91" t="n">
         <v>4</v>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4257,6 +4849,12 @@
       <c r="L92" t="n">
         <v>2</v>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4295,6 +4893,12 @@
       <c r="L93" t="n">
         <v>2</v>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4337,6 +4941,12 @@
       <c r="L94" t="n">
         <v>1</v>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4379,6 +4989,16 @@
       <c r="L95" t="n">
         <v>4</v>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4421,6 +5041,16 @@
       <c r="L96" t="n">
         <v>4</v>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4459,6 +5089,12 @@
       <c r="L97" t="n">
         <v>2</v>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4497,6 +5133,12 @@
       <c r="L98" t="n">
         <v>2</v>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4539,6 +5181,12 @@
       <c r="L99" t="n">
         <v>4</v>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4577,6 +5225,12 @@
       <c r="L100" t="n">
         <v>2</v>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4619,6 +5273,16 @@
       <c r="L101" t="n">
         <v>1</v>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4661,6 +5325,12 @@
       <c r="L102" t="n">
         <v>1</v>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4703,6 +5373,12 @@
       <c r="L103" t="n">
         <v>4</v>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4745,6 +5421,16 @@
       <c r="L104" t="n">
         <v>4</v>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4787,6 +5473,16 @@
       <c r="L105" t="n">
         <v>4</v>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4825,6 +5521,12 @@
       <c r="L106" t="n">
         <v>2</v>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4863,6 +5565,12 @@
       <c r="L107" t="n">
         <v>2</v>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4905,6 +5613,16 @@
       <c r="L108" t="n">
         <v>4</v>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4943,6 +5661,16 @@
       <c r="L109" t="n">
         <v>2</v>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4981,6 +5709,16 @@
       <c r="L110" t="n">
         <v>2</v>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5019,6 +5757,16 @@
       <c r="L111" t="n">
         <v>2</v>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Mixed by gender</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Y (mixed by gender)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5057,6 +5805,12 @@
       <c r="L112" t="n">
         <v>2</v>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5095,6 +5849,12 @@
       <c r="L113" t="n">
         <v>2</v>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5133,6 +5893,12 @@
       <c r="L114" t="n">
         <v>2</v>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5175,6 +5941,16 @@
       <c r="L115" t="n">
         <v>4</v>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5217,6 +5993,16 @@
       <c r="L116" t="n">
         <v>4</v>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5255,6 +6041,12 @@
       <c r="L117" t="n">
         <v>2</v>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5297,6 +6089,12 @@
       <c r="L118" t="n">
         <v>1</v>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5339,6 +6137,12 @@
       <c r="L119" t="n">
         <v>4</v>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5377,6 +6181,12 @@
       <c r="L120" t="n">
         <v>2</v>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5415,6 +6225,12 @@
       <c r="L121" t="n">
         <v>2</v>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5457,6 +6273,12 @@
       <c r="L122" t="n">
         <v>4</v>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5495,6 +6317,12 @@
       <c r="L123" t="n">
         <v>2</v>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5537,6 +6365,12 @@
       <c r="L124" t="n">
         <v>1</v>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5575,6 +6409,12 @@
       <c r="L125" t="n">
         <v>2</v>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5613,6 +6453,12 @@
       <c r="L126" t="n">
         <v>2</v>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5651,6 +6497,12 @@
       <c r="L127" t="n">
         <v>2</v>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5689,6 +6541,12 @@
       <c r="L128" t="n">
         <v>2</v>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5731,6 +6589,12 @@
       <c r="L129" t="n">
         <v>4</v>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5769,6 +6633,12 @@
       <c r="L130" t="n">
         <v>2</v>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5807,6 +6677,12 @@
       <c r="L131" t="n">
         <v>2</v>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5845,6 +6721,12 @@
       <c r="L132" t="n">
         <v>2</v>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5887,6 +6769,16 @@
       <c r="L133" t="n">
         <v>4</v>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5925,6 +6817,12 @@
       <c r="L134" t="n">
         <v>2</v>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5963,6 +6861,12 @@
       <c r="L135" t="n">
         <v>2</v>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6001,6 +6905,12 @@
       <c r="L136" t="n">
         <v>2</v>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6039,6 +6949,12 @@
       <c r="L137" t="n">
         <v>2</v>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6077,6 +6993,12 @@
       <c r="L138" t="n">
         <v>2</v>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6119,6 +7041,12 @@
       <c r="L139" t="n">
         <v>4</v>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6157,6 +7085,12 @@
       <c r="L140" t="n">
         <v>2</v>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6195,6 +7129,12 @@
       <c r="L141" t="n">
         <v>1</v>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6237,6 +7177,12 @@
       <c r="L142" t="n">
         <v>4</v>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6279,6 +7225,16 @@
       <c r="L143" t="n">
         <v>4</v>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Mixed by gender</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Y (mixed by gender)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6317,6 +7273,12 @@
       <c r="L144" t="n">
         <v>2</v>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6359,6 +7321,12 @@
       <c r="L145" t="n">
         <v>4</v>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6401,6 +7369,12 @@
       <c r="L146" t="n">
         <v>4</v>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6443,6 +7417,12 @@
       <c r="L147" t="n">
         <v>4</v>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6485,6 +7465,12 @@
       <c r="L148" t="n">
         <v>4</v>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6523,6 +7509,12 @@
       <c r="L149" t="n">
         <v>2</v>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6565,6 +7557,12 @@
       <c r="L150" t="n">
         <v>4</v>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6603,6 +7601,12 @@
       <c r="L151" t="n">
         <v>2</v>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6641,6 +7645,12 @@
       <c r="L152" t="n">
         <v>2</v>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6683,6 +7693,12 @@
       <c r="L153" t="n">
         <v>4</v>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6721,6 +7737,12 @@
       <c r="L154" t="n">
         <v>2</v>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6763,6 +7785,16 @@
       <c r="L155" t="n">
         <v>4</v>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6805,6 +7837,16 @@
       <c r="L156" t="n">
         <v>4</v>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6847,6 +7889,12 @@
       <c r="L157" t="n">
         <v>4</v>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6889,6 +7937,12 @@
       <c r="L158" t="n">
         <v>4</v>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6935,6 +7989,12 @@
       <c r="L159" t="n">
         <v>2</v>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6981,6 +8041,12 @@
       <c r="L160" t="n">
         <v>2</v>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7023,6 +8089,12 @@
       <c r="L161" t="n">
         <v>4</v>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7061,6 +8133,12 @@
       <c r="L162" t="n">
         <v>2</v>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7099,6 +8177,12 @@
       <c r="L163" t="n">
         <v>1</v>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7137,6 +8221,12 @@
       <c r="L164" t="n">
         <v>1</v>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7175,6 +8265,12 @@
       <c r="L165" t="n">
         <v>1</v>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7217,6 +8313,12 @@
       <c r="L166" t="n">
         <v>4</v>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7255,6 +8357,16 @@
       <c r="L167" t="n">
         <v>2</v>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7292,6 +8404,16 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="n">
         <v>2</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -7335,6 +8457,16 @@
       <c r="L169" t="n">
         <v>4</v>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7377,6 +8509,12 @@
       <c r="L170" t="n">
         <v>4</v>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7419,6 +8557,16 @@
       <c r="L171" t="n">
         <v>4</v>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7461,6 +8609,12 @@
       <c r="L172" t="n">
         <v>6</v>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7503,6 +8657,12 @@
       <c r="L173" t="n">
         <v>6</v>
       </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7545,6 +8705,12 @@
       <c r="L174" t="n">
         <v>4</v>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7587,6 +8753,12 @@
       <c r="L175" t="n">
         <v>4</v>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7625,6 +8797,12 @@
       <c r="L176" t="n">
         <v>2</v>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7663,6 +8841,12 @@
       <c r="L177" t="n">
         <v>2</v>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7701,6 +8885,12 @@
       <c r="L178" t="n">
         <v>2</v>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7739,6 +8929,12 @@
       <c r="L179" t="n">
         <v>2</v>
       </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7777,6 +8973,12 @@
       <c r="L180" t="n">
         <v>2</v>
       </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7819,6 +9021,12 @@
       <c r="L181" t="n">
         <v>4</v>
       </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7857,6 +9065,12 @@
       <c r="L182" t="n">
         <v>2</v>
       </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7895,6 +9109,12 @@
       <c r="L183" t="n">
         <v>2</v>
       </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7933,6 +9153,12 @@
       <c r="L184" t="n">
         <v>2</v>
       </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7971,6 +9197,16 @@
       <c r="L185" t="n">
         <v>2</v>
       </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8008,6 +9244,16 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="n">
         <v>2</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -8051,6 +9297,12 @@
       <c r="L187" t="n">
         <v>4</v>
       </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8089,6 +9341,12 @@
       <c r="L188" t="n">
         <v>2</v>
       </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8127,6 +9385,12 @@
       <c r="L189" t="n">
         <v>2</v>
       </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8169,6 +9433,12 @@
       <c r="L190" t="n">
         <v>4</v>
       </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8211,6 +9481,12 @@
       <c r="L191" t="n">
         <v>4</v>
       </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8253,6 +9529,12 @@
       <c r="L192" t="n">
         <v>4</v>
       </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8295,6 +9577,12 @@
       <c r="L193" t="n">
         <v>4</v>
       </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8333,6 +9621,12 @@
       <c r="L194" t="n">
         <v>2</v>
       </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8371,6 +9665,12 @@
       <c r="L195" t="n">
         <v>2</v>
       </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8413,6 +9713,12 @@
       <c r="L196" t="n">
         <v>4</v>
       </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8455,6 +9761,12 @@
       <c r="L197" t="n">
         <v>4</v>
       </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8493,6 +9805,12 @@
       <c r="L198" t="n">
         <v>2</v>
       </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8531,6 +9849,12 @@
       <c r="L199" t="n">
         <v>2</v>
       </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8569,6 +9893,12 @@
       <c r="L200" t="n">
         <v>2</v>
       </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8607,6 +9937,12 @@
       <c r="L201" t="n">
         <v>2</v>
       </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8645,6 +9981,12 @@
       <c r="L202" t="n">
         <v>2</v>
       </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8683,6 +10025,12 @@
       <c r="L203" t="n">
         <v>2</v>
       </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8721,6 +10069,12 @@
       <c r="L204" t="n">
         <v>2</v>
       </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8759,6 +10113,12 @@
       <c r="L205" t="n">
         <v>2</v>
       </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8805,6 +10165,12 @@
       <c r="L206" t="n">
         <v>2</v>
       </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8847,6 +10213,12 @@
       <c r="L207" t="n">
         <v>2</v>
       </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8889,6 +10261,12 @@
       <c r="L208" t="n">
         <v>2</v>
       </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8931,6 +10309,12 @@
       <c r="L209" t="n">
         <v>2</v>
       </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8973,6 +10357,12 @@
       <c r="L210" t="n">
         <v>2</v>
       </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9015,6 +10405,12 @@
       <c r="L211" t="n">
         <v>2</v>
       </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9057,6 +10453,12 @@
       <c r="L212" t="n">
         <v>2</v>
       </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9099,6 +10501,12 @@
       <c r="L213" t="n">
         <v>2</v>
       </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9137,6 +10545,12 @@
       <c r="L214" t="n">
         <v>1</v>
       </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9179,6 +10593,12 @@
       <c r="L215" t="n">
         <v>2</v>
       </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9221,6 +10641,12 @@
       <c r="L216" t="n">
         <v>2</v>
       </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9263,6 +10689,12 @@
       <c r="L217" t="n">
         <v>2</v>
       </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9305,6 +10737,12 @@
       <c r="L218" t="n">
         <v>4</v>
       </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9347,6 +10785,12 @@
       <c r="L219" t="n">
         <v>4</v>
       </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9389,6 +10833,12 @@
       <c r="L220" t="n">
         <v>4</v>
       </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9431,6 +10881,12 @@
       <c r="L221" t="n">
         <v>4</v>
       </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9468,6 +10924,16 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="n">
         <v>2</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -9511,6 +10977,12 @@
       <c r="L223" t="n">
         <v>4</v>
       </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9553,6 +11025,12 @@
       <c r="L224" t="n">
         <v>4</v>
       </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9591,6 +11069,12 @@
       <c r="L225" t="n">
         <v>2</v>
       </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9629,6 +11113,12 @@
       <c r="L226" t="n">
         <v>2</v>
       </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9671,6 +11161,12 @@
       <c r="L227" t="n">
         <v>1</v>
       </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9713,6 +11209,12 @@
       <c r="L228" t="n">
         <v>1</v>
       </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9755,6 +11257,12 @@
       <c r="L229" t="n">
         <v>1</v>
       </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9793,6 +11301,12 @@
       <c r="L230" t="n">
         <v>2</v>
       </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9839,6 +11353,12 @@
       <c r="L231" t="n">
         <v>2</v>
       </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9881,6 +11401,12 @@
       <c r="L232" t="n">
         <v>3</v>
       </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9919,6 +11445,12 @@
       <c r="L233" t="n">
         <v>2</v>
       </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9961,6 +11493,12 @@
       <c r="L234" t="n">
         <v>4</v>
       </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10003,6 +11541,16 @@
       <c r="L235" t="n">
         <v>4</v>
       </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10045,6 +11593,12 @@
       <c r="L236" t="n">
         <v>1</v>
       </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10083,6 +11637,12 @@
       <c r="L237" t="n">
         <v>2</v>
       </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10121,6 +11681,12 @@
       <c r="L238" t="n">
         <v>2</v>
       </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10163,6 +11729,12 @@
       <c r="L239" t="n">
         <v>1</v>
       </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10201,6 +11773,12 @@
       <c r="L240" t="n">
         <v>2</v>
       </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10243,6 +11821,12 @@
       <c r="L241" t="n">
         <v>1</v>
       </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10285,6 +11869,12 @@
       <c r="L242" t="n">
         <v>4</v>
       </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10323,6 +11913,12 @@
       <c r="L243" t="n">
         <v>2</v>
       </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10361,6 +11957,12 @@
       <c r="L244" t="n">
         <v>1</v>
       </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10399,6 +12001,12 @@
       <c r="L245" t="n">
         <v>2</v>
       </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10437,6 +12045,12 @@
       <c r="L246" t="n">
         <v>2</v>
       </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10479,6 +12093,16 @@
       <c r="L247" t="n">
         <v>4</v>
       </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10521,6 +12145,12 @@
       <c r="L248" t="n">
         <v>4</v>
       </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10563,6 +12193,12 @@
       <c r="L249" t="n">
         <v>4</v>
       </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10601,6 +12237,12 @@
       <c r="L250" t="n">
         <v>2</v>
       </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10639,6 +12281,12 @@
       <c r="L251" t="n">
         <v>2</v>
       </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10677,6 +12325,12 @@
       <c r="L252" t="n">
         <v>2</v>
       </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -10719,6 +12373,12 @@
       <c r="L253" t="n">
         <v>2</v>
       </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -10761,6 +12421,12 @@
       <c r="L254" t="n">
         <v>2</v>
       </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10803,6 +12469,12 @@
       <c r="L255" t="n">
         <v>2</v>
       </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -10845,6 +12517,12 @@
       <c r="L256" t="n">
         <v>2</v>
       </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10883,6 +12561,12 @@
       <c r="L257" t="n">
         <v>1</v>
       </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -10925,6 +12609,12 @@
       <c r="L258" t="n">
         <v>2</v>
       </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -10963,9 +12653,15 @@
       <c r="L259" t="n">
         <v>1</v>
       </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Not in legacy portfolio</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L259"/>
+  <autoFilter ref="A1:N259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10976,7 +12672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11043,6 +12739,30 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Legacy Core Assortment FW27</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>A pre-Tobias-data flag already in the SS26 tiering workbook (57/1,860 Base+Gender rows = 'Yes') -- sparse and partial, not a full FW27 range list. Rolled up to Base grain here (Yes if either gender was Yes); 2 bases are genuinely 'Mixed by gender'. 'Not in legacy portfolio' means this franchise's base name has no match in the 1,860-row tiering sheet (new, renamed, or a naming mismatch).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Agrees with new FW27-active?</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>'Core Assortment FW27' is a narrow strategic-item flag (57/1,860 bases), not a full range flag -- most franchises are legitimately 'No' and still Active in FW27, so that's NOT a disagreement and this column is left blank for 'No'/'Not in legacy portfolio' rows. Only computed where the legacy flag said Yes/Mixed: 'N' rows are the ones worth a second look -- a franchise previously flagged core for FW27 that no longer shows Active there in the new data.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
+++ b/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
@@ -444,8 +444,8 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,12 +511,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Legacy Core Assortment FW27</t>
+          <t>Core Assortment FW27</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Agrees with new FW27-active?</t>
+          <t>Core Assortment SS28</t>
         </is>
       </c>
     </row>
@@ -559,10 +559,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -608,7 +612,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -660,7 +664,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -710,7 +714,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -754,7 +762,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -798,7 +810,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -839,10 +855,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -886,7 +906,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -934,7 +958,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -978,7 +1006,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1022,7 +1054,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1063,10 +1099,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1110,7 +1150,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1154,7 +1198,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1202,7 +1250,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1243,10 +1295,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1290,7 +1346,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1331,10 +1391,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1378,7 +1442,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1422,7 +1490,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1466,7 +1538,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1520,7 +1596,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1568,7 +1648,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1609,10 +1693,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1660,7 +1748,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1705,10 +1797,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1756,7 +1852,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1804,7 +1904,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1852,7 +1956,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1900,7 +2008,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1948,7 +2060,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1996,7 +2112,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2044,7 +2164,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2092,7 +2216,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2137,10 +2265,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2192,7 +2324,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2242,7 +2378,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2430,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2480,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2389,10 +2529,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2440,7 +2584,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2488,7 +2636,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2536,7 +2688,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2584,7 +2740,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2634,7 +2794,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2844,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2732,7 +2896,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2780,7 +2948,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2828,7 +3000,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2873,10 +3049,14 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2920,7 +3100,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2964,7 +3148,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3008,7 +3196,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3049,10 +3241,14 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3100,7 +3296,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3150,7 +3350,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3402,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3452,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3300,7 +3504,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3348,7 +3556,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3400,7 +3612,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3452,7 +3668,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3502,7 +3722,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3778,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3828,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3656,7 +3880,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3704,7 +3932,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3752,7 +3984,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3800,7 +4036,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3848,7 +4088,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3896,7 +4140,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3944,7 +4192,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3989,10 +4241,14 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4040,7 +4296,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4088,7 +4348,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4136,7 +4400,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4184,7 +4452,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4229,10 +4501,14 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4277,10 +4553,14 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4325,10 +4605,14 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4372,7 +4656,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4417,10 +4705,14 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4465,10 +4757,14 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4512,7 +4808,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4562,7 +4862,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4912,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4660,7 +4964,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4708,7 +5016,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4759,10 +5071,14 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4807,10 +5123,14 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4854,7 +5174,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4898,7 +5222,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4946,7 +5274,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4996,7 +5328,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5380,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -5091,10 +5423,14 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5138,7 +5474,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5183,10 +5523,14 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5227,10 +5571,14 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5280,7 +5628,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5678,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5375,10 +5727,14 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5428,7 +5784,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5836,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5882,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5570,7 +5930,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5620,7 +5984,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -5668,7 +6032,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -5716,7 +6080,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -5759,12 +6123,12 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Mixed by gender</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Y (mixed by gender)</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -5810,7 +6174,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5854,7 +6222,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5898,7 +6270,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5948,7 +6324,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6376,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6422,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6091,10 +6471,14 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6142,7 +6526,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6183,10 +6571,14 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6227,10 +6619,14 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6278,7 +6674,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6322,7 +6722,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6367,10 +6771,14 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6414,7 +6822,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6458,7 +6870,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6502,7 +6918,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6543,10 +6963,14 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6594,7 +7018,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6638,7 +7066,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6682,7 +7114,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6726,7 +7162,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6776,7 +7216,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -6819,10 +7259,14 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6866,7 +7310,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6910,7 +7358,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6954,7 +7406,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6998,7 +7454,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7046,7 +7506,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7087,10 +7551,14 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7131,10 +7599,14 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7179,10 +7651,14 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7227,12 +7703,12 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Mixed by gender</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Y (mixed by gender)</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7754,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7326,7 +7806,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7374,7 +7858,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7422,7 +7910,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7470,7 +7962,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7511,10 +8007,14 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7562,7 +8062,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7606,7 +8110,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7647,10 +8155,14 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7698,7 +8210,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7742,7 +8258,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7792,7 +8312,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -7844,7 +8364,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -7894,7 +8414,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7942,7 +8466,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7991,10 +8519,14 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8043,10 +8575,14 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8094,7 +8630,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8138,7 +8678,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8179,10 +8723,14 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8223,10 +8771,14 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8267,10 +8819,14 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8318,7 +8874,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8364,7 +8924,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8972,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -8464,7 +9024,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -8514,7 +9074,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8564,7 +9128,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -8611,10 +9175,14 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8659,10 +9227,14 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8710,7 +9282,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8758,7 +9334,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8802,7 +9382,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8846,7 +9430,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8887,10 +9475,14 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8931,10 +9523,14 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8978,7 +9574,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9026,7 +9626,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9070,7 +9674,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9111,10 +9719,14 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9155,10 +9767,14 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9204,7 +9820,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9868,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -9299,10 +9915,14 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9346,7 +9966,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9390,7 +10014,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9435,10 +10063,14 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9486,7 +10118,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9534,7 +10170,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9582,7 +10222,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9623,10 +10267,14 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9667,10 +10315,14 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9715,10 +10367,14 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9766,7 +10422,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9807,10 +10467,14 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9851,10 +10515,14 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9898,7 +10566,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9942,7 +10614,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9986,7 +10662,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10030,7 +10710,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10074,7 +10758,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10118,7 +10806,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10170,7 +10862,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10218,7 +10914,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10266,7 +10966,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10314,7 +11018,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10362,7 +11070,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10410,7 +11122,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10458,7 +11174,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10506,7 +11226,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10550,7 +11274,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10598,7 +11326,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10646,7 +11378,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10694,7 +11430,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10739,10 +11479,14 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10787,10 +11531,14 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10838,7 +11586,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10886,7 +11638,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10932,7 +11688,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -10982,7 +11738,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11030,7 +11790,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11074,7 +11838,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11118,7 +11886,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11163,10 +11935,14 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11214,7 +11990,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11262,7 +12042,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11303,10 +12087,14 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11358,7 +12146,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11406,7 +12198,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11450,7 +12246,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11498,7 +12298,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11548,7 +12352,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -11598,7 +12402,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11642,7 +12450,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11686,7 +12498,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11734,7 +12550,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11778,7 +12598,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11826,7 +12650,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11871,10 +12699,14 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11915,10 +12747,14 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11959,10 +12795,14 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12006,7 +12846,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12050,7 +12894,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12100,7 +12948,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>To confirm</t>
         </is>
       </c>
     </row>
@@ -12147,10 +12995,14 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N248" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12198,7 +13050,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -12239,10 +13095,14 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12283,10 +13143,14 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12327,10 +13191,14 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N252" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12378,7 +13246,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N253" t="inlineStr"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12426,7 +13298,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N254" t="inlineStr"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12471,10 +13347,14 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N255" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12519,10 +13399,14 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N256" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12566,7 +13450,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N257" t="inlineStr"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12611,10 +13499,14 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N258" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12655,10 +13547,14 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Not in legacy portfolio</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N259"/>
@@ -12742,24 +13638,24 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Legacy Core Assortment FW27</t>
+          <t>Core Assortment FW27</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A pre-Tobias-data flag already in the SS26 tiering workbook (57/1,860 Base+Gender rows = 'Yes') -- sparse and partial, not a full FW27 range list. Rolled up to Base grain here (Yes if either gender was Yes); 2 bases are genuinely 'Mixed by gender'. 'Not in legacy portfolio' means this franchise's base name has no match in the 1,860-row tiering sheet (new, renamed, or a naming mismatch).</t>
+          <t>Yes/No, from the flag already in the SS26 tiering workbook (57/1,860 Base+Gender rows = 'Yes'), rolled up to Base grain (Yes if either gender was Yes).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Agrees with new FW27-active?</t>
+          <t>Core Assortment SS28</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>'Core Assortment FW27' is a narrow strategic-item flag (57/1,860 bases), not a full range flag -- most franchises are legitimately 'No' and still Active in FW27, so that's NOT a disagreement and this column is left blank for 'No'/'Not in legacy portfolio' rows. Only computed where the legacy flag said Yes/Mixed: 'N' rows are the ones worth a second look -- a franchise previously flagged core for FW27 that no longer shows Active there in the new data.</t>
+          <t>No source yet -- the flag was only ever defined for FW27. Left as 'To confirm' for every row until Tobias/Isabelle define it for SS28.</t>
         </is>
       </c>
     </row>

--- a/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
+++ b/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$N$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$Q$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N259"/>
+  <dimension ref="A1:Q259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -444,8 +444,11 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,12 +514,27 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t># active colors</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Core Assortment FW27</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Core Assortment SS28</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Asia Fit</t>
         </is>
       </c>
     </row>
@@ -557,14 +575,27 @@
       <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M2" t="n">
+        <v>5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -605,14 +636,27 @@
       <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -657,14 +701,27 @@
       <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -709,14 +766,27 @@
       <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M5" t="n">
+        <v>6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -757,14 +827,27 @@
       <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M6" t="n">
+        <v>4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -805,14 +888,27 @@
       <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M7" t="n">
+        <v>3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -853,14 +949,27 @@
       <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M8" t="n">
+        <v>3</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -901,14 +1010,27 @@
       <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M9" t="n">
+        <v>2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -953,14 +1075,27 @@
       <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M10" t="n">
+        <v>8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1001,14 +1136,27 @@
       <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M11" t="n">
+        <v>5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1049,14 +1197,27 @@
       <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M12" t="n">
+        <v>5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1097,14 +1258,27 @@
       <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M13" t="n">
+        <v>5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1145,14 +1319,27 @@
       <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M14" t="n">
+        <v>1</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1193,14 +1380,27 @@
       <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M15" t="n">
+        <v>2</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,14 +1445,27 @@
       <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M16" t="n">
+        <v>2</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1293,14 +1506,27 @@
       <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1341,14 +1567,27 @@
       <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M18" t="n">
+        <v>3</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1389,14 +1628,27 @@
       <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M19" t="n">
+        <v>3</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1437,14 +1689,27 @@
       <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M20" t="n">
+        <v>2</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1485,14 +1750,27 @@
       <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M21" t="n">
+        <v>5</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1533,14 +1811,27 @@
       <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M22" t="n">
+        <v>4</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1591,14 +1882,27 @@
       <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M23" t="n">
+        <v>4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1643,14 +1947,27 @@
       <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M24" t="n">
+        <v>2</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1691,14 +2008,27 @@
       <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M25" t="n">
+        <v>1</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1743,14 +2073,27 @@
       <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M26" t="n">
+        <v>4</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1795,14 +2138,27 @@
       <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M27" t="n">
+        <v>6</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1847,14 +2203,27 @@
       <c r="L28" t="n">
         <v>2</v>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M28" t="n">
+        <v>0</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1899,14 +2268,27 @@
       <c r="L29" t="n">
         <v>2</v>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M29" t="n">
+        <v>0</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1951,14 +2333,27 @@
       <c r="L30" t="n">
         <v>2</v>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M30" t="n">
+        <v>0</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2003,14 +2398,27 @@
       <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M31" t="n">
+        <v>0</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2055,14 +2463,27 @@
       <c r="L32" t="n">
         <v>2</v>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M32" t="n">
+        <v>0</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2107,14 +2528,27 @@
       <c r="L33" t="n">
         <v>2</v>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M33" t="n">
+        <v>0</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2159,14 +2593,27 @@
       <c r="L34" t="n">
         <v>2</v>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M34" t="n">
+        <v>0</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2211,14 +2658,27 @@
       <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M35" t="n">
+        <v>0</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2263,14 +2723,27 @@
       <c r="L36" t="n">
         <v>2</v>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M36" t="n">
+        <v>3</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2319,14 +2792,27 @@
       <c r="L37" t="n">
         <v>3</v>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M37" t="n">
+        <v>6</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2371,14 +2857,27 @@
       <c r="L38" t="n">
         <v>2</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" t="n">
+        <v>8</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,14 +2922,27 @@
       <c r="L39" t="n">
         <v>2</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" t="n">
+        <v>8</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2475,14 +2987,27 @@
       <c r="L40" t="n">
         <v>2</v>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M40" t="n">
+        <v>2</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2527,14 +3052,27 @@
       <c r="L41" t="n">
         <v>2</v>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M41" t="n">
+        <v>2</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2579,14 +3117,27 @@
       <c r="L42" t="n">
         <v>2</v>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M42" t="n">
+        <v>4</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2631,14 +3182,27 @@
       <c r="L43" t="n">
         <v>2</v>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M43" t="n">
+        <v>4</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2683,14 +3247,27 @@
       <c r="L44" t="n">
         <v>2</v>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M44" t="n">
+        <v>0</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2735,14 +3312,27 @@
       <c r="L45" t="n">
         <v>2</v>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M45" t="n">
+        <v>2</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2787,14 +3377,27 @@
       <c r="L46" t="n">
         <v>2</v>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" t="n">
+        <v>6</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2839,14 +3442,27 @@
       <c r="L47" t="n">
         <v>2</v>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M47" t="n">
+        <v>4</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2891,14 +3507,27 @@
       <c r="L48" t="n">
         <v>2</v>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M48" t="n">
+        <v>4</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2943,14 +3572,27 @@
       <c r="L49" t="n">
         <v>2</v>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M49" t="n">
+        <v>2</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2995,14 +3637,27 @@
       <c r="L50" t="n">
         <v>2</v>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M50" t="n">
+        <v>2</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3047,14 +3702,27 @@
       <c r="L51" t="n">
         <v>2</v>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M51" t="n">
+        <v>2</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3095,14 +3763,27 @@
       <c r="L52" t="n">
         <v>2</v>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M52" t="n">
+        <v>0</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3143,14 +3824,27 @@
       <c r="L53" t="n">
         <v>2</v>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M53" t="n">
+        <v>0</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3191,14 +3885,27 @@
       <c r="L54" t="n">
         <v>2</v>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M54" t="n">
+        <v>0</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3239,14 +3946,27 @@
       <c r="L55" t="n">
         <v>2</v>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M55" t="n">
+        <v>4</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,14 +4011,27 @@
       <c r="L56" t="n">
         <v>2</v>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M56" t="n">
+        <v>2</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3343,14 +4076,27 @@
       <c r="L57" t="n">
         <v>2</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M57" t="n">
+        <v>4</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3395,14 +4141,27 @@
       <c r="L58" t="n">
         <v>2</v>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M58" t="n">
+        <v>4</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3447,14 +4206,27 @@
       <c r="L59" t="n">
         <v>2</v>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M59" t="n">
+        <v>4</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3499,14 +4271,27 @@
       <c r="L60" t="n">
         <v>2</v>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M60" t="n">
+        <v>4</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3551,14 +4336,27 @@
       <c r="L61" t="n">
         <v>2</v>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M61" t="n">
+        <v>6</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3607,14 +4405,27 @@
       <c r="L62" t="n">
         <v>2</v>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M62" t="n">
+        <v>4</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,14 +4474,27 @@
       <c r="L63" t="n">
         <v>2</v>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M63" t="n">
+        <v>4</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3715,14 +4539,27 @@
       <c r="L64" t="n">
         <v>2</v>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M64" t="n">
+        <v>7</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3771,14 +4608,27 @@
       <c r="L65" t="n">
         <v>3</v>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M65" t="n">
+        <v>17</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3823,14 +4673,27 @@
       <c r="L66" t="n">
         <v>2</v>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M66" t="n">
+        <v>0</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3875,14 +4738,27 @@
       <c r="L67" t="n">
         <v>2</v>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M67" t="n">
+        <v>0</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3927,14 +4803,27 @@
       <c r="L68" t="n">
         <v>2</v>
       </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M68" t="n">
+        <v>7</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3979,14 +4868,27 @@
       <c r="L69" t="n">
         <v>2</v>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M69" t="n">
+        <v>4</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4031,14 +4933,27 @@
       <c r="L70" t="n">
         <v>2</v>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M70" t="n">
+        <v>6</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4083,14 +4998,27 @@
       <c r="L71" t="n">
         <v>2</v>
       </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M71" t="n">
+        <v>2</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4135,14 +5063,27 @@
       <c r="L72" t="n">
         <v>2</v>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M72" t="n">
+        <v>3</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4187,14 +5128,27 @@
       <c r="L73" t="n">
         <v>2</v>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M73" t="n">
+        <v>3</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4239,14 +5193,27 @@
       <c r="L74" t="n">
         <v>2</v>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M74" t="n">
+        <v>4</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4291,14 +5258,27 @@
       <c r="L75" t="n">
         <v>2</v>
       </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M75" t="n">
+        <v>2</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4343,14 +5323,27 @@
       <c r="L76" t="n">
         <v>2</v>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M76" t="n">
+        <v>2</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4395,14 +5388,27 @@
       <c r="L77" t="n">
         <v>2</v>
       </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M77" t="n">
+        <v>2</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4447,14 +5453,27 @@
       <c r="L78" t="n">
         <v>2</v>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M78" t="n">
+        <v>4</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4499,14 +5518,27 @@
       <c r="L79" t="n">
         <v>2</v>
       </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M79" t="n">
+        <v>4</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4551,14 +5583,27 @@
       <c r="L80" t="n">
         <v>4</v>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M80" t="n">
+        <v>4</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4603,14 +5648,27 @@
       <c r="L81" t="n">
         <v>4</v>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M81" t="n">
+        <v>4</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4651,14 +5709,27 @@
       <c r="L82" t="n">
         <v>2</v>
       </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M82" t="n">
+        <v>2</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4703,14 +5774,27 @@
       <c r="L83" t="n">
         <v>4</v>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M83" t="n">
+        <v>7</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4755,14 +5839,27 @@
       <c r="L84" t="n">
         <v>4</v>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M84" t="n">
+        <v>7</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4803,14 +5900,27 @@
       <c r="L85" t="n">
         <v>2</v>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M85" t="n">
+        <v>2</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4855,14 +5965,27 @@
       <c r="L86" t="n">
         <v>4</v>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="M86" t="n">
+        <v>4</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4907,14 +6030,27 @@
       <c r="L87" t="n">
         <v>4</v>
       </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M87" t="n">
+        <v>8</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4959,14 +6095,27 @@
       <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M88" t="n">
+        <v>4</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5011,14 +6160,27 @@
       <c r="L89" t="n">
         <v>4</v>
       </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M89" t="n">
+        <v>8</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5069,14 +6231,27 @@
       <c r="L90" t="n">
         <v>4</v>
       </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M90" t="n">
+        <v>8</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5121,14 +6296,27 @@
       <c r="L91" t="n">
         <v>4</v>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M91" t="n">
+        <v>6</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5169,14 +6357,27 @@
       <c r="L92" t="n">
         <v>2</v>
       </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M92" t="n">
+        <v>6</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5217,14 +6418,27 @@
       <c r="L93" t="n">
         <v>2</v>
       </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M93" t="n">
+        <v>3</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5269,14 +6483,27 @@
       <c r="L94" t="n">
         <v>1</v>
       </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M94" t="n">
+        <v>2</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5321,14 +6548,27 @@
       <c r="L95" t="n">
         <v>4</v>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="M95" t="n">
+        <v>14</v>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5373,14 +6613,27 @@
       <c r="L96" t="n">
         <v>4</v>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="M96" t="n">
+        <v>8</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5421,14 +6674,27 @@
       <c r="L97" t="n">
         <v>2</v>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M97" t="n">
+        <v>4</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5469,14 +6735,27 @@
       <c r="L98" t="n">
         <v>2</v>
       </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M98" t="n">
+        <v>6</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5521,14 +6800,27 @@
       <c r="L99" t="n">
         <v>4</v>
       </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M99" t="n">
+        <v>14</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5569,14 +6861,27 @@
       <c r="L100" t="n">
         <v>2</v>
       </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M100" t="n">
+        <v>6</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5621,14 +6926,27 @@
       <c r="L101" t="n">
         <v>1</v>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M101" t="n">
+        <v>3</v>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5673,14 +6991,27 @@
       <c r="L102" t="n">
         <v>1</v>
       </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M102" t="n">
+        <v>3</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5725,14 +7056,27 @@
       <c r="L103" t="n">
         <v>4</v>
       </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M103" t="n">
+        <v>4</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5777,14 +7121,27 @@
       <c r="L104" t="n">
         <v>4</v>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="M104" t="n">
+        <v>13</v>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5829,14 +7186,27 @@
       <c r="L105" t="n">
         <v>4</v>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="M105" t="n">
+        <v>11</v>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5877,14 +7247,27 @@
       <c r="L106" t="n">
         <v>2</v>
       </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M106" t="n">
+        <v>8</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5925,14 +7308,27 @@
       <c r="L107" t="n">
         <v>2</v>
       </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M107" t="n">
+        <v>3</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5977,14 +7373,27 @@
       <c r="L108" t="n">
         <v>4</v>
       </c>
-      <c r="M108" t="inlineStr">
+      <c r="M108" t="n">
+        <v>16</v>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6025,14 +7434,27 @@
       <c r="L109" t="n">
         <v>2</v>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="M109" t="n">
+        <v>7</v>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6073,14 +7495,27 @@
       <c r="L110" t="n">
         <v>2</v>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="M110" t="n">
+        <v>4</v>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6121,14 +7556,27 @@
       <c r="L111" t="n">
         <v>2</v>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="M111" t="n">
+        <v>8</v>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6169,14 +7617,27 @@
       <c r="L112" t="n">
         <v>2</v>
       </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M112" t="n">
+        <v>4</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6217,14 +7678,27 @@
       <c r="L113" t="n">
         <v>2</v>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M113" t="n">
+        <v>6</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6265,14 +7739,27 @@
       <c r="L114" t="n">
         <v>2</v>
       </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M114" t="n">
+        <v>8</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6317,14 +7804,27 @@
       <c r="L115" t="n">
         <v>4</v>
       </c>
-      <c r="M115" t="inlineStr">
+      <c r="M115" t="n">
+        <v>16</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6369,14 +7869,27 @@
       <c r="L116" t="n">
         <v>4</v>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="M116" t="n">
+        <v>10</v>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6417,14 +7930,27 @@
       <c r="L117" t="n">
         <v>2</v>
       </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M117" t="n">
+        <v>7</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6469,14 +7995,27 @@
       <c r="L118" t="n">
         <v>1</v>
       </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M118" t="n">
+        <v>2</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6521,14 +8060,27 @@
       <c r="L119" t="n">
         <v>4</v>
       </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M119" t="n">
+        <v>4</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6569,14 +8121,27 @@
       <c r="L120" t="n">
         <v>2</v>
       </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M120" t="n">
+        <v>4</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6617,14 +8182,27 @@
       <c r="L121" t="n">
         <v>2</v>
       </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M121" t="n">
+        <v>4</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6669,14 +8247,27 @@
       <c r="L122" t="n">
         <v>4</v>
       </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M122" t="n">
+        <v>6</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6717,14 +8308,27 @@
       <c r="L123" t="n">
         <v>2</v>
       </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M123" t="n">
+        <v>2</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6769,14 +8373,27 @@
       <c r="L124" t="n">
         <v>1</v>
       </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M124" t="n">
+        <v>1</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6817,14 +8434,27 @@
       <c r="L125" t="n">
         <v>2</v>
       </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M125" t="n">
+        <v>7</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6865,14 +8495,27 @@
       <c r="L126" t="n">
         <v>2</v>
       </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M126" t="n">
+        <v>8</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6913,14 +8556,27 @@
       <c r="L127" t="n">
         <v>2</v>
       </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M127" t="n">
+        <v>6</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6961,14 +8617,27 @@
       <c r="L128" t="n">
         <v>2</v>
       </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M128" t="n">
+        <v>4</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7013,14 +8682,27 @@
       <c r="L129" t="n">
         <v>4</v>
       </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M129" t="n">
+        <v>6</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7061,14 +8743,27 @@
       <c r="L130" t="n">
         <v>2</v>
       </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M130" t="n">
+        <v>6</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7109,14 +8804,27 @@
       <c r="L131" t="n">
         <v>2</v>
       </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M131" t="n">
+        <v>4</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7157,14 +8865,27 @@
       <c r="L132" t="n">
         <v>2</v>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M132" t="n">
+        <v>4</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7209,14 +8930,27 @@
       <c r="L133" t="n">
         <v>4</v>
       </c>
-      <c r="M133" t="inlineStr">
+      <c r="M133" t="n">
+        <v>7</v>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7257,14 +8991,27 @@
       <c r="L134" t="n">
         <v>2</v>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M134" t="n">
+        <v>3</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7305,14 +9052,27 @@
       <c r="L135" t="n">
         <v>2</v>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M135" t="n">
+        <v>4</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7353,14 +9113,27 @@
       <c r="L136" t="n">
         <v>2</v>
       </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M136" t="n">
+        <v>4</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7401,14 +9174,27 @@
       <c r="L137" t="n">
         <v>2</v>
       </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M137" t="n">
+        <v>0</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7449,14 +9235,27 @@
       <c r="L138" t="n">
         <v>2</v>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M138" t="n">
+        <v>4</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7501,14 +9300,27 @@
       <c r="L139" t="n">
         <v>4</v>
       </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M139" t="n">
+        <v>8</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7549,14 +9361,27 @@
       <c r="L140" t="n">
         <v>2</v>
       </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M140" t="n">
+        <v>2</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7597,14 +9422,27 @@
       <c r="L141" t="n">
         <v>1</v>
       </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M141" t="n">
+        <v>0</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7649,14 +9487,27 @@
       <c r="L142" t="n">
         <v>4</v>
       </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M142" t="n">
+        <v>13</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7701,14 +9552,27 @@
       <c r="L143" t="n">
         <v>4</v>
       </c>
-      <c r="M143" t="inlineStr">
+      <c r="M143" t="n">
+        <v>26</v>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7749,14 +9613,27 @@
       <c r="L144" t="n">
         <v>2</v>
       </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M144" t="n">
+        <v>6</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7801,14 +9678,27 @@
       <c r="L145" t="n">
         <v>4</v>
       </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M145" t="n">
+        <v>11</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7853,14 +9743,27 @@
       <c r="L146" t="n">
         <v>4</v>
       </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M146" t="n">
+        <v>13</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7905,14 +9808,27 @@
       <c r="L147" t="n">
         <v>4</v>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M147" t="n">
+        <v>21</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7957,14 +9873,27 @@
       <c r="L148" t="n">
         <v>4</v>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M148" t="n">
+        <v>15</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8005,14 +9934,27 @@
       <c r="L149" t="n">
         <v>2</v>
       </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M149" t="n">
+        <v>0</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8057,14 +9999,27 @@
       <c r="L150" t="n">
         <v>4</v>
       </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M150" t="n">
+        <v>12</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8105,14 +10060,27 @@
       <c r="L151" t="n">
         <v>2</v>
       </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M151" t="n">
+        <v>6</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8153,14 +10121,27 @@
       <c r="L152" t="n">
         <v>2</v>
       </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M152" t="n">
+        <v>4</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8205,14 +10186,27 @@
       <c r="L153" t="n">
         <v>4</v>
       </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M153" t="n">
+        <v>9</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8253,14 +10247,27 @@
       <c r="L154" t="n">
         <v>2</v>
       </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M154" t="n">
+        <v>0</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8305,14 +10312,27 @@
       <c r="L155" t="n">
         <v>4</v>
       </c>
-      <c r="M155" t="inlineStr">
+      <c r="M155" t="n">
+        <v>22</v>
+      </c>
+      <c r="N155" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8357,14 +10377,27 @@
       <c r="L156" t="n">
         <v>4</v>
       </c>
-      <c r="M156" t="inlineStr">
+      <c r="M156" t="n">
+        <v>18</v>
+      </c>
+      <c r="N156" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8409,14 +10442,27 @@
       <c r="L157" t="n">
         <v>4</v>
       </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M157" t="n">
+        <v>12</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8461,14 +10507,27 @@
       <c r="L158" t="n">
         <v>4</v>
       </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M158" t="n">
+        <v>12</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8517,14 +10576,27 @@
       <c r="L159" t="n">
         <v>2</v>
       </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M159" t="n">
+        <v>4</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8573,14 +10645,27 @@
       <c r="L160" t="n">
         <v>2</v>
       </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M160" t="n">
+        <v>4</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8625,14 +10710,27 @@
       <c r="L161" t="n">
         <v>4</v>
       </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M161" t="n">
+        <v>4</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8673,14 +10771,27 @@
       <c r="L162" t="n">
         <v>2</v>
       </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M162" t="n">
+        <v>4</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8721,14 +10832,27 @@
       <c r="L163" t="n">
         <v>1</v>
       </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M163" t="n">
+        <v>2</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8769,14 +10893,27 @@
       <c r="L164" t="n">
         <v>1</v>
       </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M164" t="n">
+        <v>2</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8817,14 +10954,27 @@
       <c r="L165" t="n">
         <v>1</v>
       </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M165" t="n">
+        <v>2</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8869,14 +11019,27 @@
       <c r="L166" t="n">
         <v>4</v>
       </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M166" t="n">
+        <v>16</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8917,14 +11080,27 @@
       <c r="L167" t="n">
         <v>2</v>
       </c>
-      <c r="M167" t="inlineStr">
+      <c r="M167" t="n">
+        <v>7</v>
+      </c>
+      <c r="N167" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8965,14 +11141,27 @@
       <c r="L168" t="n">
         <v>2</v>
       </c>
-      <c r="M168" t="inlineStr">
+      <c r="M168" t="n">
+        <v>6</v>
+      </c>
+      <c r="N168" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9017,14 +11206,27 @@
       <c r="L169" t="n">
         <v>4</v>
       </c>
-      <c r="M169" t="inlineStr">
+      <c r="M169" t="n">
+        <v>20</v>
+      </c>
+      <c r="N169" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9069,14 +11271,27 @@
       <c r="L170" t="n">
         <v>4</v>
       </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M170" t="n">
+        <v>20</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9121,14 +11336,27 @@
       <c r="L171" t="n">
         <v>4</v>
       </c>
-      <c r="M171" t="inlineStr">
+      <c r="M171" t="n">
+        <v>20</v>
+      </c>
+      <c r="N171" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9173,14 +11401,27 @@
       <c r="L172" t="n">
         <v>6</v>
       </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M172" t="n">
+        <v>0</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9225,14 +11466,27 @@
       <c r="L173" t="n">
         <v>6</v>
       </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M173" t="n">
+        <v>15</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9277,14 +11531,27 @@
       <c r="L174" t="n">
         <v>4</v>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M174" t="n">
+        <v>0</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9329,14 +11596,27 @@
       <c r="L175" t="n">
         <v>4</v>
       </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M175" t="n">
+        <v>10</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9377,14 +11657,27 @@
       <c r="L176" t="n">
         <v>2</v>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M176" t="n">
+        <v>7</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9425,14 +11718,27 @@
       <c r="L177" t="n">
         <v>2</v>
       </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M177" t="n">
+        <v>0</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9473,14 +11779,27 @@
       <c r="L178" t="n">
         <v>2</v>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M178" t="n">
+        <v>8</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9521,14 +11840,27 @@
       <c r="L179" t="n">
         <v>2</v>
       </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M179" t="n">
+        <v>2</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9569,14 +11901,27 @@
       <c r="L180" t="n">
         <v>2</v>
       </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M180" t="n">
+        <v>8</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9621,14 +11966,27 @@
       <c r="L181" t="n">
         <v>4</v>
       </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M181" t="n">
+        <v>16</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9669,14 +12027,27 @@
       <c r="L182" t="n">
         <v>2</v>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M182" t="n">
+        <v>0</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9717,14 +12088,27 @@
       <c r="L183" t="n">
         <v>2</v>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M183" t="n">
+        <v>4</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9765,14 +12149,27 @@
       <c r="L184" t="n">
         <v>2</v>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M184" t="n">
+        <v>6</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9813,14 +12210,27 @@
       <c r="L185" t="n">
         <v>2</v>
       </c>
-      <c r="M185" t="inlineStr">
+      <c r="M185" t="n">
+        <v>6</v>
+      </c>
+      <c r="N185" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9861,14 +12271,27 @@
       <c r="L186" t="n">
         <v>2</v>
       </c>
-      <c r="M186" t="inlineStr">
+      <c r="M186" t="n">
+        <v>6</v>
+      </c>
+      <c r="N186" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9913,14 +12336,27 @@
       <c r="L187" t="n">
         <v>4</v>
       </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M187" t="n">
+        <v>4</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9961,14 +12397,27 @@
       <c r="L188" t="n">
         <v>2</v>
       </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M188" t="n">
+        <v>2</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10009,14 +12458,27 @@
       <c r="L189" t="n">
         <v>2</v>
       </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M189" t="n">
+        <v>4</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10061,14 +12523,27 @@
       <c r="L190" t="n">
         <v>4</v>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M190" t="n">
+        <v>15</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -10113,14 +12588,27 @@
       <c r="L191" t="n">
         <v>4</v>
       </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M191" t="n">
+        <v>16</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -10165,14 +12653,27 @@
       <c r="L192" t="n">
         <v>4</v>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M192" t="n">
+        <v>0</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10217,14 +12718,27 @@
       <c r="L193" t="n">
         <v>4</v>
       </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M193" t="n">
+        <v>11</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10265,14 +12779,27 @@
       <c r="L194" t="n">
         <v>2</v>
       </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M194" t="n">
+        <v>4</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10313,14 +12840,27 @@
       <c r="L195" t="n">
         <v>2</v>
       </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M195" t="n">
+        <v>4</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10365,14 +12905,27 @@
       <c r="L196" t="n">
         <v>4</v>
       </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M196" t="n">
+        <v>6</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10417,14 +12970,27 @@
       <c r="L197" t="n">
         <v>4</v>
       </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M197" t="n">
+        <v>8</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10465,14 +13031,27 @@
       <c r="L198" t="n">
         <v>2</v>
       </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M198" t="n">
+        <v>6</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -10513,14 +13092,27 @@
       <c r="L199" t="n">
         <v>2</v>
       </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M199" t="n">
+        <v>6</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10561,14 +13153,27 @@
       <c r="L200" t="n">
         <v>2</v>
       </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M200" t="n">
+        <v>4</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10609,14 +13214,27 @@
       <c r="L201" t="n">
         <v>2</v>
       </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M201" t="n">
+        <v>7</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10657,14 +13275,27 @@
       <c r="L202" t="n">
         <v>2</v>
       </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M202" t="n">
+        <v>6</v>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10705,14 +13336,27 @@
       <c r="L203" t="n">
         <v>2</v>
       </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M203" t="n">
+        <v>6</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10753,14 +13397,27 @@
       <c r="L204" t="n">
         <v>2</v>
       </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M204" t="n">
+        <v>4</v>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10801,14 +13458,27 @@
       <c r="L205" t="n">
         <v>2</v>
       </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M205" t="n">
+        <v>4</v>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10857,14 +13527,27 @@
       <c r="L206" t="n">
         <v>2</v>
       </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M206" t="n">
+        <v>0</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10909,14 +13592,27 @@
       <c r="L207" t="n">
         <v>2</v>
       </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M207" t="n">
+        <v>0</v>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10961,14 +13657,27 @@
       <c r="L208" t="n">
         <v>2</v>
       </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M208" t="n">
+        <v>0</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11013,14 +13722,27 @@
       <c r="L209" t="n">
         <v>2</v>
       </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M209" t="n">
+        <v>0</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11065,14 +13787,27 @@
       <c r="L210" t="n">
         <v>2</v>
       </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M210" t="n">
+        <v>0</v>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11117,14 +13852,27 @@
       <c r="L211" t="n">
         <v>2</v>
       </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M211" t="n">
+        <v>0</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11169,14 +13917,27 @@
       <c r="L212" t="n">
         <v>2</v>
       </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M212" t="n">
+        <v>0</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11221,14 +13982,27 @@
       <c r="L213" t="n">
         <v>2</v>
       </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M213" t="n">
+        <v>0</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11269,14 +14043,27 @@
       <c r="L214" t="n">
         <v>1</v>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M214" t="n">
+        <v>0</v>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11321,14 +14108,27 @@
       <c r="L215" t="n">
         <v>2</v>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M215" t="n">
+        <v>0</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11373,14 +14173,27 @@
       <c r="L216" t="n">
         <v>2</v>
       </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M216" t="n">
+        <v>0</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11425,14 +14238,27 @@
       <c r="L217" t="n">
         <v>2</v>
       </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M217" t="n">
+        <v>0</v>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11477,14 +14303,27 @@
       <c r="L218" t="n">
         <v>4</v>
       </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M218" t="n">
+        <v>13</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -11529,14 +14368,27 @@
       <c r="L219" t="n">
         <v>4</v>
       </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M219" t="n">
+        <v>4</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11581,14 +14433,27 @@
       <c r="L220" t="n">
         <v>4</v>
       </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M220" t="n">
+        <v>8</v>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -11633,14 +14498,27 @@
       <c r="L221" t="n">
         <v>4</v>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M221" t="n">
+        <v>4</v>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11681,14 +14559,27 @@
       <c r="L222" t="n">
         <v>2</v>
       </c>
-      <c r="M222" t="inlineStr">
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11733,14 +14624,27 @@
       <c r="L223" t="n">
         <v>4</v>
       </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M223" t="n">
+        <v>16</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11785,14 +14689,27 @@
       <c r="L224" t="n">
         <v>4</v>
       </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M224" t="n">
+        <v>16</v>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11833,14 +14750,27 @@
       <c r="L225" t="n">
         <v>2</v>
       </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M225" t="n">
+        <v>5</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11881,14 +14811,27 @@
       <c r="L226" t="n">
         <v>2</v>
       </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M226" t="n">
+        <v>5</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11933,14 +14876,27 @@
       <c r="L227" t="n">
         <v>1</v>
       </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M227" t="n">
+        <v>2</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11985,14 +14941,27 @@
       <c r="L228" t="n">
         <v>1</v>
       </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M228" t="n">
+        <v>4</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12037,14 +15006,27 @@
       <c r="L229" t="n">
         <v>1</v>
       </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M229" t="n">
+        <v>4</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12085,14 +15067,27 @@
       <c r="L230" t="n">
         <v>2</v>
       </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M230" t="n">
+        <v>4</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12141,14 +15136,27 @@
       <c r="L231" t="n">
         <v>2</v>
       </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M231" t="n">
+        <v>8</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12193,14 +15201,27 @@
       <c r="L232" t="n">
         <v>3</v>
       </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M232" t="n">
+        <v>12</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12241,14 +15262,27 @@
       <c r="L233" t="n">
         <v>2</v>
       </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M233" t="n">
+        <v>6</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12293,14 +15327,27 @@
       <c r="L234" t="n">
         <v>4</v>
       </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M234" t="n">
+        <v>13</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12345,14 +15392,27 @@
       <c r="L235" t="n">
         <v>4</v>
       </c>
-      <c r="M235" t="inlineStr">
+      <c r="M235" t="n">
+        <v>18</v>
+      </c>
+      <c r="N235" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12397,14 +15457,27 @@
       <c r="L236" t="n">
         <v>1</v>
       </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M236" t="n">
+        <v>3</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12445,14 +15518,27 @@
       <c r="L237" t="n">
         <v>2</v>
       </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M237" t="n">
+        <v>6</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12493,14 +15579,27 @@
       <c r="L238" t="n">
         <v>2</v>
       </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M238" t="n">
+        <v>8</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12545,14 +15644,27 @@
       <c r="L239" t="n">
         <v>1</v>
       </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M239" t="n">
+        <v>2</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12593,14 +15705,27 @@
       <c r="L240" t="n">
         <v>2</v>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M240" t="n">
+        <v>5</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12645,14 +15770,27 @@
       <c r="L241" t="n">
         <v>1</v>
       </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M241" t="n">
+        <v>3</v>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12697,14 +15835,27 @@
       <c r="L242" t="n">
         <v>4</v>
       </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M242" t="n">
+        <v>12</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -12745,14 +15896,27 @@
       <c r="L243" t="n">
         <v>2</v>
       </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M243" t="n">
+        <v>2</v>
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12793,14 +15957,27 @@
       <c r="L244" t="n">
         <v>1</v>
       </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M244" t="n">
+        <v>0</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12841,14 +16018,27 @@
       <c r="L245" t="n">
         <v>2</v>
       </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M245" t="n">
+        <v>6</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12889,14 +16079,27 @@
       <c r="L246" t="n">
         <v>2</v>
       </c>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M246" t="n">
+        <v>8</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12941,14 +16144,27 @@
       <c r="L247" t="n">
         <v>4</v>
       </c>
-      <c r="M247" t="inlineStr">
+      <c r="M247" t="n">
+        <v>10</v>
+      </c>
+      <c r="N247" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12993,14 +16209,27 @@
       <c r="L248" t="n">
         <v>4</v>
       </c>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M248" t="n">
+        <v>8</v>
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13045,14 +16274,27 @@
       <c r="L249" t="n">
         <v>4</v>
       </c>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M249" t="n">
+        <v>10</v>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13093,14 +16335,27 @@
       <c r="L250" t="n">
         <v>2</v>
       </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M250" t="n">
+        <v>6</v>
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13141,14 +16396,27 @@
       <c r="L251" t="n">
         <v>2</v>
       </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M251" t="n">
+        <v>2</v>
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13189,14 +16457,27 @@
       <c r="L252" t="n">
         <v>2</v>
       </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M252" t="n">
+        <v>2</v>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13241,14 +16522,27 @@
       <c r="L253" t="n">
         <v>2</v>
       </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M253" t="n">
+        <v>0</v>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13293,14 +16587,27 @@
       <c r="L254" t="n">
         <v>2</v>
       </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M254" t="n">
+        <v>0</v>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13345,14 +16652,27 @@
       <c r="L255" t="n">
         <v>2</v>
       </c>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M255" t="n">
+        <v>0</v>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13397,14 +16717,27 @@
       <c r="L256" t="n">
         <v>2</v>
       </c>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M256" t="n">
+        <v>0</v>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13445,14 +16778,27 @@
       <c r="L257" t="n">
         <v>1</v>
       </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M257" t="n">
+        <v>1</v>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13497,14 +16843,27 @@
       <c r="L258" t="n">
         <v>2</v>
       </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M258" t="n">
+        <v>2</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13545,19 +16904,32 @@
       <c r="L259" t="n">
         <v>1</v>
       </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="M259" t="n">
+        <v>1</v>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N259"/>
+  <autoFilter ref="A1:Q259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13568,7 +16940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13659,6 +17031,42 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t># active colors</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Sum of active colorways (the colorway-level Active flag, not just a row listed in the sheet) across every style rolled into this franchise -- both genders, both seasons. A colorway still in the file but not Active this season (e.g. a discontinued or carried-forward-for-reference color) is not counted. CAVEAT: 88/616 main-range style rows (incl. 18 Shell styles) have NO colorway sub-rows at all in this export -- showing 0 here, which may be a real single-color item or a data gap in the export. Worth confirming with Tobias before treating 0 as fact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Yes if an ABS or ABS Exclusive variant of this franchise exists anywhere in FW27/SS28 (even though RR-006 keeps those styles out of the main range count above) -- so a reviewer knows one exists before deciding the franchise's main-range fate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Asia Fit</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Yes if an 'AF'-suffixed (Asian Fit) variant of this franchise exists anywhere in FW27/SS28 (RR-007) -- always also ABS=Yes, since every AF style is tagged ABS Exclusive in the source data.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
+++ b/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$Q$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$Y$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q259"/>
+  <dimension ref="A1:Y259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,14 @@
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,6 +543,46 @@
       <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Asia Fit</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Status FW27</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Status SS28</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast Qty (total)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast GP% (blended)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast Qty (DTC)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast GP% (DTC)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast Qty (Wholesale)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast GP% (Wholesale)</t>
         </is>
       </c>
     </row>
@@ -598,6 +646,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>5788</v>
+      </c>
+      <c r="U2" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1130</v>
+      </c>
+      <c r="W2" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4658</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>53.4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -659,6 +731,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>5200</v>
+      </c>
+      <c r="U3" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="W3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4180</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -724,6 +820,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>4067</v>
+      </c>
+      <c r="U4" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>69</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3067</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>59.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -788,6 +912,30 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>639</v>
+      </c>
+      <c r="U5" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>450</v>
+      </c>
+      <c r="W5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="X5" t="n">
+        <v>189</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>50.1</v>
       </c>
     </row>
     <row r="6">
@@ -850,6 +998,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>1008</v>
+      </c>
+      <c r="U6" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>400</v>
+      </c>
+      <c r="W6" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>608</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>55.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -911,6 +1083,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>3491</v>
+      </c>
+      <c r="U7" t="n">
+        <v>58</v>
+      </c>
+      <c r="V7" t="n">
+        <v>510</v>
+      </c>
+      <c r="W7" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2981</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>55.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -972,6 +1168,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>2575</v>
+      </c>
+      <c r="U8" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="W8" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1075</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1033,6 +1253,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>480</v>
+      </c>
+      <c r="U9" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>110</v>
+      </c>
+      <c r="W9" t="n">
+        <v>65</v>
+      </c>
+      <c r="X9" t="n">
+        <v>370</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>56.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1097,6 +1341,30 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>1845</v>
+      </c>
+      <c r="U10" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>490</v>
+      </c>
+      <c r="W10" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1355</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>58.3</v>
       </c>
     </row>
     <row r="11">
@@ -1159,6 +1427,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>4210</v>
+      </c>
+      <c r="U11" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1095</v>
+      </c>
+      <c r="W11" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3115</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>48.3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1220,6 +1512,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>5407</v>
+      </c>
+      <c r="U12" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1460</v>
+      </c>
+      <c r="W12" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3947</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>55.6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1281,6 +1597,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>2970</v>
+      </c>
+      <c r="U13" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1030</v>
+      </c>
+      <c r="W13" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1940</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>65.3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1342,6 +1682,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>2010</v>
+      </c>
+      <c r="U14" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>800</v>
+      </c>
+      <c r="W14" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1210</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>51.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1403,6 +1767,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>1414</v>
+      </c>
+      <c r="U15" t="n">
+        <v>52</v>
+      </c>
+      <c r="V15" t="n">
+        <v>400</v>
+      </c>
+      <c r="W15" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1014</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>48.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1468,6 +1856,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>2420</v>
+      </c>
+      <c r="U16" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>590</v>
+      </c>
+      <c r="W16" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1830</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>45.6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1529,6 +1945,14 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1590,6 +2014,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="U18" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>600</v>
+      </c>
+      <c r="W18" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1340</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>51.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1651,6 +2099,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>4531</v>
+      </c>
+      <c r="U19" t="n">
+        <v>46</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1110</v>
+      </c>
+      <c r="W19" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3421</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1712,6 +2184,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>665</v>
+      </c>
+      <c r="U20" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>400</v>
+      </c>
+      <c r="W20" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>265</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1773,6 +2269,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>4043</v>
+      </c>
+      <c r="U21" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>950</v>
+      </c>
+      <c r="W21" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3093</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>51.9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1834,6 +2354,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>1497</v>
+      </c>
+      <c r="U22" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>465</v>
+      </c>
+      <c r="W22" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1032</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>53.9</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1904,6 +2448,34 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>2801</v>
+      </c>
+      <c r="U23" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>730</v>
+      </c>
+      <c r="W23" t="n">
+        <v>63</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2071</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>31.1</v>
       </c>
     </row>
     <row r="24">
@@ -1970,6 +2542,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>1135</v>
+      </c>
+      <c r="U24" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>230</v>
+      </c>
+      <c r="W24" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>905</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>49.4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2031,6 +2631,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>2038</v>
+      </c>
+      <c r="U25" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>550</v>
+      </c>
+      <c r="W25" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1488</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.9</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2096,6 +2720,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>1545</v>
+      </c>
+      <c r="U26" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V26" t="n">
+        <v>330</v>
+      </c>
+      <c r="W26" t="n">
+        <v>63</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1215</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>54.7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2161,6 +2813,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>2622</v>
+      </c>
+      <c r="U27" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>770</v>
+      </c>
+      <c r="W27" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1852</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>43.1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2226,6 +2906,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>398</v>
+      </c>
+      <c r="U28" t="n">
+        <v>39</v>
+      </c>
+      <c r="V28" t="n">
+        <v>225</v>
+      </c>
+      <c r="W28" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="X28" t="n">
+        <v>173</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>28.3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2291,6 +2999,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>385</v>
+      </c>
+      <c r="U29" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="V29" t="n">
+        <v>215</v>
+      </c>
+      <c r="W29" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>170</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>26.7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2356,6 +3092,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>154</v>
+      </c>
+      <c r="U30" t="n">
+        <v>54</v>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="n">
+        <v>154</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2421,6 +3181,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>134</v>
+      </c>
+      <c r="U31" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="n">
+        <v>134</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>50.4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2486,6 +3270,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>229</v>
+      </c>
+      <c r="U32" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="n">
+        <v>229</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>46.3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2551,6 +3359,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>224</v>
+      </c>
+      <c r="U33" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="n">
+        <v>224</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>52.9</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2616,6 +3448,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>356</v>
+      </c>
+      <c r="U34" t="n">
+        <v>57</v>
+      </c>
+      <c r="V34" t="n">
+        <v>270</v>
+      </c>
+      <c r="W34" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>48.9</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2681,6 +3541,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>329</v>
+      </c>
+      <c r="U35" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="V35" t="n">
+        <v>230</v>
+      </c>
+      <c r="W35" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="X35" t="n">
+        <v>99</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>55.5</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2746,6 +3634,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>2103</v>
+      </c>
+      <c r="U36" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="V36" t="n">
+        <v>770</v>
+      </c>
+      <c r="W36" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1333</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>50.1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2814,6 +3730,34 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>5140</v>
+      </c>
+      <c r="U37" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="V37" t="n">
+        <v>890</v>
+      </c>
+      <c r="W37" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4250</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>47.2</v>
       </c>
     </row>
     <row r="38">
@@ -2880,6 +3824,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>7736</v>
+      </c>
+      <c r="U38" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1220</v>
+      </c>
+      <c r="W38" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>6516</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>43.1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2945,6 +3917,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>5349</v>
+      </c>
+      <c r="U39" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1280</v>
+      </c>
+      <c r="W39" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4069</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>39.5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3010,6 +4010,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>879</v>
+      </c>
+      <c r="U40" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>490</v>
+      </c>
+      <c r="W40" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>389</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>43.7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3075,6 +4103,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>1602</v>
+      </c>
+      <c r="U41" t="n">
+        <v>51</v>
+      </c>
+      <c r="V41" t="n">
+        <v>380</v>
+      </c>
+      <c r="W41" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1222</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>45.2</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3140,6 +4196,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>2325</v>
+      </c>
+      <c r="U42" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V42" t="n">
+        <v>155</v>
+      </c>
+      <c r="W42" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2170</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>53.6</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3205,6 +4289,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>2075</v>
+      </c>
+      <c r="U43" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>165</v>
+      </c>
+      <c r="W43" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1910</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>57.7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3270,6 +4382,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>489</v>
+      </c>
+      <c r="U44" t="n">
+        <v>47</v>
+      </c>
+      <c r="V44" t="n">
+        <v>45</v>
+      </c>
+      <c r="W44" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="X44" t="n">
+        <v>444</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>45.8</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3335,6 +4475,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>1708</v>
+      </c>
+      <c r="U45" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="V45" t="n">
+        <v>170</v>
+      </c>
+      <c r="W45" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1538</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>49.2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3400,6 +4568,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>4383</v>
+      </c>
+      <c r="U46" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="V46" t="n">
+        <v>230</v>
+      </c>
+      <c r="W46" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="X46" t="n">
+        <v>4153</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3465,6 +4661,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>1488</v>
+      </c>
+      <c r="U47" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="V47" t="n">
+        <v>195</v>
+      </c>
+      <c r="W47" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1293</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>46.5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3530,6 +4754,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>1816</v>
+      </c>
+      <c r="U48" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>160</v>
+      </c>
+      <c r="W48" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1656</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>46.9</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3595,6 +4847,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>658</v>
+      </c>
+      <c r="U49" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="V49" t="n">
+        <v>255</v>
+      </c>
+      <c r="W49" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="X49" t="n">
+        <v>403</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3660,6 +4940,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>549</v>
+      </c>
+      <c r="U50" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="V50" t="n">
+        <v>220</v>
+      </c>
+      <c r="W50" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="X50" t="n">
+        <v>329</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>46.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3725,6 +5033,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
+        <v>226</v>
+      </c>
+      <c r="U51" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="V51" t="n">
+        <v>30</v>
+      </c>
+      <c r="W51" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="X51" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>50.9</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3786,6 +5122,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="n">
+        <v>561</v>
+      </c>
+      <c r="U52" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V52" t="n">
+        <v>440</v>
+      </c>
+      <c r="W52" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X52" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3847,6 +5207,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="n">
+        <v>1011</v>
+      </c>
+      <c r="U53" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="V53" t="n">
+        <v>590</v>
+      </c>
+      <c r="W53" t="n">
+        <v>54</v>
+      </c>
+      <c r="X53" t="n">
+        <v>421</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>16.1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3908,6 +5292,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="n">
+        <v>831</v>
+      </c>
+      <c r="U54" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>560</v>
+      </c>
+      <c r="W54" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="X54" t="n">
+        <v>271</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3969,6 +5377,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U55" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="V55" t="n">
+        <v>490</v>
+      </c>
+      <c r="W55" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1010</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4034,6 +5466,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>1504</v>
+      </c>
+      <c r="U56" t="n">
+        <v>56</v>
+      </c>
+      <c r="V56" t="n">
+        <v>115</v>
+      </c>
+      <c r="W56" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1389</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>55.2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4099,6 +5559,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>5261</v>
+      </c>
+      <c r="U57" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="V57" t="n">
+        <v>315</v>
+      </c>
+      <c r="W57" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="X57" t="n">
+        <v>4946</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>40.3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4164,6 +5652,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>4495</v>
+      </c>
+      <c r="U58" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="V58" t="n">
+        <v>265</v>
+      </c>
+      <c r="W58" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="X58" t="n">
+        <v>4230</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>46.8</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4229,6 +5745,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
+        <v>3136</v>
+      </c>
+      <c r="U59" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="V59" t="n">
+        <v>550</v>
+      </c>
+      <c r="W59" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2586</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>48.6</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4294,6 +5838,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
+        <v>4843</v>
+      </c>
+      <c r="U60" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="V60" t="n">
+        <v>620</v>
+      </c>
+      <c r="W60" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="X60" t="n">
+        <v>4223</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>45.4</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4359,6 +5931,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
+        <v>1136</v>
+      </c>
+      <c r="U61" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="V61" t="n">
+        <v>360</v>
+      </c>
+      <c r="W61" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="X61" t="n">
+        <v>776</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>44.9</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4428,6 +6028,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T62" t="n">
+        <v>1629</v>
+      </c>
+      <c r="U62" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="V62" t="n">
+        <v>90</v>
+      </c>
+      <c r="W62" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1539</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4497,6 +6125,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T63" t="n">
+        <v>909</v>
+      </c>
+      <c r="U63" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="V63" t="n">
+        <v>90</v>
+      </c>
+      <c r="W63" t="n">
+        <v>63</v>
+      </c>
+      <c r="X63" t="n">
+        <v>819</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>44.7</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4562,6 +6218,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
+        <v>8957</v>
+      </c>
+      <c r="U64" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="V64" t="n">
+        <v>605</v>
+      </c>
+      <c r="W64" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="X64" t="n">
+        <v>8352</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4630,6 +6314,34 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T65" t="n">
+        <v>9873</v>
+      </c>
+      <c r="U65" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="V65" t="n">
+        <v>580</v>
+      </c>
+      <c r="W65" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="X65" t="n">
+        <v>9293</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="66">
@@ -4696,6 +6408,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T66" t="n">
+        <v>2459</v>
+      </c>
+      <c r="U66" t="n">
+        <v>49</v>
+      </c>
+      <c r="V66" t="n">
+        <v>50</v>
+      </c>
+      <c r="W66" t="n">
+        <v>59</v>
+      </c>
+      <c r="X66" t="n">
+        <v>2409</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>48.7</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4761,6 +6501,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T67" t="n">
+        <v>2444</v>
+      </c>
+      <c r="U67" t="n">
+        <v>49</v>
+      </c>
+      <c r="V67" t="n">
+        <v>20</v>
+      </c>
+      <c r="W67" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="X67" t="n">
+        <v>2424</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>48.9</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4826,6 +6594,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T68" t="n">
+        <v>5143</v>
+      </c>
+      <c r="U68" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="V68" t="n">
+        <v>585</v>
+      </c>
+      <c r="W68" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="X68" t="n">
+        <v>4558</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>44.4</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4891,6 +6687,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
+        <v>1332</v>
+      </c>
+      <c r="U69" t="n">
+        <v>51</v>
+      </c>
+      <c r="V69" t="n">
+        <v>255</v>
+      </c>
+      <c r="W69" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1077</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>48.1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4956,6 +6780,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T70" t="n">
+        <v>2762</v>
+      </c>
+      <c r="U70" t="n">
+        <v>47</v>
+      </c>
+      <c r="V70" t="n">
+        <v>385</v>
+      </c>
+      <c r="W70" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="X70" t="n">
+        <v>2377</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>45.1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5021,6 +6873,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T71" t="n">
+        <v>526</v>
+      </c>
+      <c r="U71" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="V71" t="n">
+        <v>330</v>
+      </c>
+      <c r="W71" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="X71" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>48.3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5086,6 +6966,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T72" t="n">
+        <v>503</v>
+      </c>
+      <c r="U72" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="V72" t="n">
+        <v>205</v>
+      </c>
+      <c r="W72" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="X72" t="n">
+        <v>298</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>38.9</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5151,6 +7059,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T73" t="n">
+        <v>415</v>
+      </c>
+      <c r="U73" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V73" t="n">
+        <v>195</v>
+      </c>
+      <c r="W73" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="X73" t="n">
+        <v>220</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5216,6 +7152,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T74" t="n">
+        <v>1227</v>
+      </c>
+      <c r="U74" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="V74" t="n">
+        <v>360</v>
+      </c>
+      <c r="W74" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="X74" t="n">
+        <v>867</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>51.7</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5281,6 +7245,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T75" t="n">
+        <v>499</v>
+      </c>
+      <c r="U75" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="V75" t="n">
+        <v>295</v>
+      </c>
+      <c r="W75" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>204</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>43.4</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5346,6 +7338,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T76" t="n">
+        <v>560</v>
+      </c>
+      <c r="U76" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="V76" t="n">
+        <v>345</v>
+      </c>
+      <c r="W76" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="X76" t="n">
+        <v>215</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>45.6</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5411,6 +7431,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T77" t="n">
+        <v>767</v>
+      </c>
+      <c r="U77" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="V77" t="n">
+        <v>220</v>
+      </c>
+      <c r="W77" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="X77" t="n">
+        <v>547</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>44.4</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5476,6 +7524,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T78" t="n">
+        <v>4205</v>
+      </c>
+      <c r="U78" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="V78" t="n">
+        <v>480</v>
+      </c>
+      <c r="W78" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="X78" t="n">
+        <v>3725</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5541,6 +7617,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T79" t="n">
+        <v>5275</v>
+      </c>
+      <c r="U79" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="V79" t="n">
+        <v>515</v>
+      </c>
+      <c r="W79" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="X79" t="n">
+        <v>4760</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>52.9</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5606,6 +7710,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T80" t="n">
+        <v>2912</v>
+      </c>
+      <c r="U80" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="V80" t="n">
+        <v>750</v>
+      </c>
+      <c r="W80" t="n">
+        <v>58</v>
+      </c>
+      <c r="X80" t="n">
+        <v>2162</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>30.2</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5671,6 +7803,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T81" t="n">
+        <v>2333</v>
+      </c>
+      <c r="U81" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1100</v>
+      </c>
+      <c r="W81" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1233</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>49.7</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5732,6 +7892,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="n">
+        <v>1933</v>
+      </c>
+      <c r="U82" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="V82" t="n">
+        <v>590</v>
+      </c>
+      <c r="W82" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="X82" t="n">
+        <v>1343</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>52.8</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5797,6 +7981,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T83" t="n">
+        <v>12383</v>
+      </c>
+      <c r="U83" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="V83" t="n">
+        <v>870</v>
+      </c>
+      <c r="W83" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="X83" t="n">
+        <v>11513</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>42.6</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5862,6 +8074,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T84" t="n">
+        <v>6217</v>
+      </c>
+      <c r="U84" t="n">
+        <v>50</v>
+      </c>
+      <c r="V84" t="n">
+        <v>590</v>
+      </c>
+      <c r="W84" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="X84" t="n">
+        <v>5627</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>48.8</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5923,6 +8163,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="n">
+        <v>300</v>
+      </c>
+      <c r="U85" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="V85" t="n">
+        <v>240</v>
+      </c>
+      <c r="W85" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="X85" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>35.3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5988,6 +8252,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T86" t="n">
+        <v>9877</v>
+      </c>
+      <c r="U86" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="V86" t="n">
+        <v>910</v>
+      </c>
+      <c r="W86" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="X86" t="n">
+        <v>8967</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>50.1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6053,6 +8345,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T87" t="n">
+        <v>3757</v>
+      </c>
+      <c r="U87" t="n">
+        <v>52</v>
+      </c>
+      <c r="V87" t="n">
+        <v>700</v>
+      </c>
+      <c r="W87" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="X87" t="n">
+        <v>3057</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>49.8</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6118,6 +8438,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T88" t="n">
+        <v>1396</v>
+      </c>
+      <c r="U88" t="n">
+        <v>51</v>
+      </c>
+      <c r="V88" t="n">
+        <v>160</v>
+      </c>
+      <c r="W88" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="X88" t="n">
+        <v>1236</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>49.4</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6183,6 +8531,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T89" t="n">
+        <v>1730</v>
+      </c>
+      <c r="U89" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="V89" t="n">
+        <v>230</v>
+      </c>
+      <c r="W89" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>45.3</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6253,6 +8629,34 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T90" t="n">
+        <v>3644</v>
+      </c>
+      <c r="U90" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1070</v>
+      </c>
+      <c r="W90" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="X90" t="n">
+        <v>2574</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>49.8</v>
       </c>
     </row>
     <row r="91">
@@ -6319,6 +8723,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T91" t="n">
+        <v>5286</v>
+      </c>
+      <c r="U91" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="V91" t="n">
+        <v>930</v>
+      </c>
+      <c r="W91" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="X91" t="n">
+        <v>4356</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>52.2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6380,6 +8812,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="n">
+        <v>2416</v>
+      </c>
+      <c r="U92" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="V92" t="n">
+        <v>640</v>
+      </c>
+      <c r="W92" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="X92" t="n">
+        <v>1776</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>63.2</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6441,6 +8897,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="n">
+        <v>1075</v>
+      </c>
+      <c r="U93" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>280</v>
+      </c>
+      <c r="W93" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="X93" t="n">
+        <v>795</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>48.3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6506,6 +8986,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="n">
+        <v>472</v>
+      </c>
+      <c r="U94" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="V94" t="n">
+        <v>250</v>
+      </c>
+      <c r="W94" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="X94" t="n">
+        <v>222</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>58.8</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6571,6 +9075,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T95" t="n">
+        <v>4904</v>
+      </c>
+      <c r="U95" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V95" t="n">
+        <v>1765</v>
+      </c>
+      <c r="W95" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="X95" t="n">
+        <v>3139</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>51.7</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6636,6 +9168,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T96" t="n">
+        <v>2505</v>
+      </c>
+      <c r="U96" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="V96" t="n">
+        <v>1690</v>
+      </c>
+      <c r="W96" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="X96" t="n">
+        <v>815</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>58.2</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6697,6 +9257,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T97" t="n">
+        <v>1851</v>
+      </c>
+      <c r="U97" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="V97" t="n">
+        <v>660</v>
+      </c>
+      <c r="W97" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="X97" t="n">
+        <v>1191</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>29.1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6758,6 +9342,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="n">
+        <v>2772</v>
+      </c>
+      <c r="U98" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="V98" t="n">
+        <v>655</v>
+      </c>
+      <c r="W98" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="X98" t="n">
+        <v>2117</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6822,6 +9430,30 @@
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T99" t="n">
+        <v>4425</v>
+      </c>
+      <c r="U99" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="V99" t="n">
+        <v>1350</v>
+      </c>
+      <c r="W99" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="X99" t="n">
+        <v>3075</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>44.9</v>
       </c>
     </row>
     <row r="100">
@@ -6884,6 +9516,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T100" t="n">
+        <v>2215</v>
+      </c>
+      <c r="U100" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="V100" t="n">
+        <v>950</v>
+      </c>
+      <c r="W100" t="n">
+        <v>63</v>
+      </c>
+      <c r="X100" t="n">
+        <v>1265</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>51.4</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6949,6 +9605,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="n">
+        <v>4246</v>
+      </c>
+      <c r="U101" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="V101" t="n">
+        <v>730</v>
+      </c>
+      <c r="W101" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="X101" t="n">
+        <v>3516</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>53.8</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7014,6 +9694,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="n">
+        <v>3607</v>
+      </c>
+      <c r="U102" t="n">
+        <v>60</v>
+      </c>
+      <c r="V102" t="n">
+        <v>230</v>
+      </c>
+      <c r="W102" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="X102" t="n">
+        <v>3377</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>59.3</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7079,6 +9783,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T103" t="n">
+        <v>2281</v>
+      </c>
+      <c r="U103" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="V103" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W103" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="X103" t="n">
+        <v>1006</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>60.7</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7144,6 +9876,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T104" t="n">
+        <v>8176</v>
+      </c>
+      <c r="U104" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="V104" t="n">
+        <v>1865</v>
+      </c>
+      <c r="W104" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="X104" t="n">
+        <v>6311</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>40.1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7209,6 +9969,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T105" t="n">
+        <v>4500</v>
+      </c>
+      <c r="U105" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="V105" t="n">
+        <v>1680</v>
+      </c>
+      <c r="W105" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="X105" t="n">
+        <v>2820</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>34.2</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7270,6 +10058,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="n">
+        <v>2865</v>
+      </c>
+      <c r="U106" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="V106" t="n">
+        <v>1580</v>
+      </c>
+      <c r="W106" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="X106" t="n">
+        <v>1285</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7331,6 +10143,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="n">
+        <v>1027</v>
+      </c>
+      <c r="U107" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="V107" t="n">
+        <v>695</v>
+      </c>
+      <c r="W107" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="X107" t="n">
+        <v>332</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>36.8</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7396,6 +10232,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T108" t="n">
+        <v>9218</v>
+      </c>
+      <c r="U108" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="V108" t="n">
+        <v>1680</v>
+      </c>
+      <c r="W108" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="X108" t="n">
+        <v>7538</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>49.8</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7457,6 +10321,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="n">
+        <v>3378</v>
+      </c>
+      <c r="U109" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="V109" t="n">
+        <v>855</v>
+      </c>
+      <c r="W109" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="X109" t="n">
+        <v>2523</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>47.7</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7518,6 +10406,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="n">
+        <v>2766</v>
+      </c>
+      <c r="U110" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="V110" t="n">
+        <v>625</v>
+      </c>
+      <c r="W110" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="X110" t="n">
+        <v>2141</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>50.1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7579,6 +10491,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="n">
+        <v>4988</v>
+      </c>
+      <c r="U111" t="n">
+        <v>50</v>
+      </c>
+      <c r="V111" t="n">
+        <v>610</v>
+      </c>
+      <c r="W111" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="X111" t="n">
+        <v>4378</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>48.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7640,6 +10576,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="n">
+        <v>1365</v>
+      </c>
+      <c r="U112" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="V112" t="n">
+        <v>230</v>
+      </c>
+      <c r="W112" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1135</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>50.6</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7701,6 +10661,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="n">
+        <v>3469</v>
+      </c>
+      <c r="U113" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="V113" t="n">
+        <v>550</v>
+      </c>
+      <c r="W113" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="X113" t="n">
+        <v>2919</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>58.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7762,6 +10746,30 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="n">
+        <v>4721</v>
+      </c>
+      <c r="U114" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="V114" t="n">
+        <v>735</v>
+      </c>
+      <c r="W114" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="X114" t="n">
+        <v>3986</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>35.7</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7827,6 +10835,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T115" t="n">
+        <v>24293</v>
+      </c>
+      <c r="U115" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="V115" t="n">
+        <v>1620</v>
+      </c>
+      <c r="W115" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="X115" t="n">
+        <v>22673</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>66.59999999999999</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7892,6 +10928,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T116" t="n">
+        <v>17996</v>
+      </c>
+      <c r="U116" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="V116" t="n">
+        <v>1585</v>
+      </c>
+      <c r="W116" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="X116" t="n">
+        <v>16411</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>53.1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7953,6 +11017,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T117" t="n">
+        <v>3476</v>
+      </c>
+      <c r="U117" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="V117" t="n">
+        <v>430</v>
+      </c>
+      <c r="W117" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="X117" t="n">
+        <v>3046</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>54.4</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8018,6 +11106,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T118" t="n">
+        <v>996</v>
+      </c>
+      <c r="U118" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="V118" t="n">
+        <v>670</v>
+      </c>
+      <c r="W118" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="X118" t="n">
+        <v>326</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>49.5</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8083,6 +11195,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T119" t="n">
+        <v>3502</v>
+      </c>
+      <c r="U119" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="V119" t="n">
+        <v>590</v>
+      </c>
+      <c r="W119" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="X119" t="n">
+        <v>2912</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>52.7</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8144,6 +11284,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T120" t="n">
+        <v>7600</v>
+      </c>
+      <c r="U120" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="V120" t="n">
+        <v>1190</v>
+      </c>
+      <c r="W120" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="X120" t="n">
+        <v>6410</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>50.9</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8205,6 +11369,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T121" t="n">
+        <v>8550</v>
+      </c>
+      <c r="U121" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="V121" t="n">
+        <v>1360</v>
+      </c>
+      <c r="W121" t="n">
+        <v>63</v>
+      </c>
+      <c r="X121" t="n">
+        <v>7190</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8270,6 +11458,26 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="T122" t="n">
+        <v>1309</v>
+      </c>
+      <c r="U122" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="n">
+        <v>1309</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>52.3</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8331,6 +11539,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="T123" t="n">
+        <v>2451</v>
+      </c>
+      <c r="U123" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="V123" t="n">
+        <v>1290</v>
+      </c>
+      <c r="W123" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="X123" t="n">
+        <v>1161</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>55.6</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8396,6 +11628,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T124" t="n">
+        <v>1124</v>
+      </c>
+      <c r="U124" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="V124" t="n">
+        <v>580</v>
+      </c>
+      <c r="W124" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="X124" t="n">
+        <v>544</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>54.1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8457,6 +11713,30 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T125" t="n">
+        <v>3652</v>
+      </c>
+      <c r="U125" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="V125" t="n">
+        <v>460</v>
+      </c>
+      <c r="W125" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="X125" t="n">
+        <v>3192</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>58.7</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8518,6 +11798,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T126" t="n">
+        <v>4165</v>
+      </c>
+      <c r="U126" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="V126" t="n">
+        <v>590</v>
+      </c>
+      <c r="W126" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="X126" t="n">
+        <v>3575</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>56.2</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8579,6 +11883,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T127" t="n">
+        <v>4095</v>
+      </c>
+      <c r="U127" t="n">
+        <v>45</v>
+      </c>
+      <c r="V127" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W127" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="X127" t="n">
+        <v>3095</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>28.1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8640,6 +11968,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T128" t="n">
+        <v>3351</v>
+      </c>
+      <c r="U128" t="n">
+        <v>47</v>
+      </c>
+      <c r="V128" t="n">
+        <v>1100</v>
+      </c>
+      <c r="W128" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="X128" t="n">
+        <v>2251</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>33.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8705,6 +12057,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T129" t="n">
+        <v>7278</v>
+      </c>
+      <c r="U129" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="V129" t="n">
+        <v>1280</v>
+      </c>
+      <c r="W129" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="X129" t="n">
+        <v>5998</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>24.7</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8766,6 +12146,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T130" t="n">
+        <v>3870</v>
+      </c>
+      <c r="U130" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="V130" t="n">
+        <v>1170</v>
+      </c>
+      <c r="W130" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="X130" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8827,6 +12231,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T131" t="n">
+        <v>6119</v>
+      </c>
+      <c r="U131" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="V131" t="n">
+        <v>580</v>
+      </c>
+      <c r="W131" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="X131" t="n">
+        <v>5539</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>58.6</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8888,6 +12316,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T132" t="n">
+        <v>3070</v>
+      </c>
+      <c r="U132" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="V132" t="n">
+        <v>1180</v>
+      </c>
+      <c r="W132" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="X132" t="n">
+        <v>1890</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>67.09999999999999</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8953,6 +12405,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T133" t="n">
+        <v>5201</v>
+      </c>
+      <c r="U133" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="V133" t="n">
+        <v>1190</v>
+      </c>
+      <c r="W133" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="X133" t="n">
+        <v>4011</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>48.8</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9014,6 +12494,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T134" t="n">
+        <v>4630</v>
+      </c>
+      <c r="U134" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="V134" t="n">
+        <v>1060</v>
+      </c>
+      <c r="W134" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="X134" t="n">
+        <v>3570</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9075,6 +12579,14 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9136,6 +12648,14 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9197,6 +12717,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="n">
+        <v>2750</v>
+      </c>
+      <c r="U137" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="V137" t="n">
+        <v>330</v>
+      </c>
+      <c r="W137" t="n">
+        <v>65</v>
+      </c>
+      <c r="X137" t="n">
+        <v>2420</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>56.1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9258,6 +12802,26 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T138" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U138" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="V138" t="inlineStr"/>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-11.3</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9323,6 +12887,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T139" t="n">
+        <v>2093</v>
+      </c>
+      <c r="U139" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="V139" t="n">
+        <v>1510</v>
+      </c>
+      <c r="W139" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="X139" t="n">
+        <v>583</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>46.4</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9384,6 +12976,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T140" t="n">
+        <v>1723</v>
+      </c>
+      <c r="U140" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="V140" t="n">
+        <v>780</v>
+      </c>
+      <c r="W140" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="X140" t="n">
+        <v>943</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9445,6 +13061,14 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9510,6 +13134,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T142" t="n">
+        <v>7534</v>
+      </c>
+      <c r="U142" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="V142" t="n">
+        <v>2090</v>
+      </c>
+      <c r="W142" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="X142" t="n">
+        <v>5444</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9575,6 +13227,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T143" t="n">
+        <v>48395</v>
+      </c>
+      <c r="U143" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="V143" t="n">
+        <v>5210</v>
+      </c>
+      <c r="W143" t="n">
+        <v>66</v>
+      </c>
+      <c r="X143" t="n">
+        <v>43185</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>56.4</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9636,6 +13316,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="n">
+        <v>4567</v>
+      </c>
+      <c r="U144" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V144" t="n">
+        <v>1130</v>
+      </c>
+      <c r="W144" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="X144" t="n">
+        <v>3437</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>52.5</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9701,6 +13405,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T145" t="n">
+        <v>3118</v>
+      </c>
+      <c r="U145" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="V145" t="n">
+        <v>1590</v>
+      </c>
+      <c r="W145" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="X145" t="n">
+        <v>1528</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>43.2</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9766,6 +13498,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T146" t="n">
+        <v>3052</v>
+      </c>
+      <c r="U146" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="V146" t="n">
+        <v>505</v>
+      </c>
+      <c r="W146" t="n">
+        <v>65</v>
+      </c>
+      <c r="X146" t="n">
+        <v>2547</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>51.9</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9831,6 +13591,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T147" t="n">
+        <v>7605</v>
+      </c>
+      <c r="U147" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="V147" t="n">
+        <v>810</v>
+      </c>
+      <c r="W147" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="X147" t="n">
+        <v>6795</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9896,6 +13684,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T148" t="n">
+        <v>7619</v>
+      </c>
+      <c r="U148" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="V148" t="n">
+        <v>600</v>
+      </c>
+      <c r="W148" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="X148" t="n">
+        <v>7019</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>54.9</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9957,6 +13773,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T149" t="n">
+        <v>2692</v>
+      </c>
+      <c r="U149" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="V149" t="n">
+        <v>540</v>
+      </c>
+      <c r="W149" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="X149" t="n">
+        <v>2152</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>39.9</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10022,6 +13862,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T150" t="n">
+        <v>3848</v>
+      </c>
+      <c r="U150" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="V150" t="n">
+        <v>1020</v>
+      </c>
+      <c r="W150" t="n">
+        <v>57</v>
+      </c>
+      <c r="X150" t="n">
+        <v>2828</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10083,6 +13951,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T151" t="n">
+        <v>1840</v>
+      </c>
+      <c r="U151" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="V151" t="n">
+        <v>720</v>
+      </c>
+      <c r="W151" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="X151" t="n">
+        <v>1120</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10144,6 +14036,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T152" t="n">
+        <v>3322</v>
+      </c>
+      <c r="U152" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="V152" t="n">
+        <v>870</v>
+      </c>
+      <c r="W152" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="X152" t="n">
+        <v>2452</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>61.8</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10209,6 +14125,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T153" t="n">
+        <v>4597</v>
+      </c>
+      <c r="U153" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="V153" t="n">
+        <v>1550</v>
+      </c>
+      <c r="W153" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X153" t="n">
+        <v>3047</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>37.3</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10270,6 +14214,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="n">
+        <v>1712</v>
+      </c>
+      <c r="U154" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="V154" t="n">
+        <v>490</v>
+      </c>
+      <c r="W154" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="X154" t="n">
+        <v>1222</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>56.6</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10335,6 +14303,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T155" t="n">
+        <v>10590</v>
+      </c>
+      <c r="U155" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="V155" t="n">
+        <v>2695</v>
+      </c>
+      <c r="W155" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="X155" t="n">
+        <v>7895</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>54.7</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10400,6 +14396,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T156" t="n">
+        <v>11020</v>
+      </c>
+      <c r="U156" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2530</v>
+      </c>
+      <c r="W156" t="n">
+        <v>61</v>
+      </c>
+      <c r="X156" t="n">
+        <v>8490</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>48.6</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10465,6 +14489,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T157" t="n">
+        <v>2990</v>
+      </c>
+      <c r="U157" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="V157" t="n">
+        <v>505</v>
+      </c>
+      <c r="W157" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="X157" t="n">
+        <v>2485</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>55.3</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10530,6 +14582,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T158" t="n">
+        <v>3712</v>
+      </c>
+      <c r="U158" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="V158" t="n">
+        <v>495</v>
+      </c>
+      <c r="W158" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="X158" t="n">
+        <v>3217</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>53.7</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10599,6 +14679,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T159" t="n">
+        <v>2481</v>
+      </c>
+      <c r="U159" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="V159" t="n">
+        <v>580</v>
+      </c>
+      <c r="W159" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X159" t="n">
+        <v>1901</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>36.8</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10668,6 +14776,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T160" t="n">
+        <v>1707</v>
+      </c>
+      <c r="U160" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="V160" t="n">
+        <v>610</v>
+      </c>
+      <c r="W160" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="X160" t="n">
+        <v>1097</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>40.4</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10733,6 +14869,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T161" t="n">
+        <v>4836</v>
+      </c>
+      <c r="U161" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="V161" t="n">
+        <v>1840</v>
+      </c>
+      <c r="W161" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="X161" t="n">
+        <v>2996</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>43.4</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10794,6 +14958,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="n">
+        <v>2548</v>
+      </c>
+      <c r="U162" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="V162" t="n">
+        <v>750</v>
+      </c>
+      <c r="W162" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="X162" t="n">
+        <v>1798</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>23.7</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10855,6 +15043,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="n">
+        <v>831</v>
+      </c>
+      <c r="U163" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="V163" t="n">
+        <v>240</v>
+      </c>
+      <c r="W163" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="X163" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>56.7</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10916,6 +15128,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="n">
+        <v>1013</v>
+      </c>
+      <c r="U164" t="n">
+        <v>46</v>
+      </c>
+      <c r="V164" t="n">
+        <v>210</v>
+      </c>
+      <c r="W164" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="X164" t="n">
+        <v>803</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>40.6</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10977,6 +15213,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="n">
+        <v>1249</v>
+      </c>
+      <c r="U165" t="n">
+        <v>48</v>
+      </c>
+      <c r="V165" t="n">
+        <v>205</v>
+      </c>
+      <c r="W165" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="X165" t="n">
+        <v>1044</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>43.2</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11042,6 +15302,30 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="n">
+        <v>2604</v>
+      </c>
+      <c r="U166" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="V166" t="n">
+        <v>385</v>
+      </c>
+      <c r="W166" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="X166" t="n">
+        <v>2219</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>49.6</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11103,6 +15387,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="n">
+        <v>5307</v>
+      </c>
+      <c r="U167" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="V167" t="n">
+        <v>1370</v>
+      </c>
+      <c r="W167" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="X167" t="n">
+        <v>3937</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>43.6</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11164,6 +15472,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="n">
+        <v>4117</v>
+      </c>
+      <c r="U168" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="V168" t="n">
+        <v>1145</v>
+      </c>
+      <c r="W168" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="X168" t="n">
+        <v>2972</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>44.6</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11229,6 +15561,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T169" t="n">
+        <v>14077</v>
+      </c>
+      <c r="U169" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="V169" t="n">
+        <v>1640</v>
+      </c>
+      <c r="W169" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="X169" t="n">
+        <v>12437</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>41.8</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11294,6 +15654,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T170" t="n">
+        <v>13899</v>
+      </c>
+      <c r="U170" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="V170" t="n">
+        <v>1135</v>
+      </c>
+      <c r="W170" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="X170" t="n">
+        <v>12764</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>52.5</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11359,6 +15747,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T171" t="n">
+        <v>13735</v>
+      </c>
+      <c r="U171" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="V171" t="n">
+        <v>2450</v>
+      </c>
+      <c r="W171" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="X171" t="n">
+        <v>11285</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11424,6 +15840,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T172" t="n">
+        <v>10135</v>
+      </c>
+      <c r="U172" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="V172" t="n">
+        <v>1060</v>
+      </c>
+      <c r="W172" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="X172" t="n">
+        <v>9075</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>47.6</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11489,6 +15933,30 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T173" t="n">
+        <v>3385</v>
+      </c>
+      <c r="U173" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="V173" t="inlineStr"/>
+      <c r="W173" t="inlineStr"/>
+      <c r="X173" t="n">
+        <v>3385</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>51.1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11554,6 +16022,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T174" t="n">
+        <v>6622</v>
+      </c>
+      <c r="U174" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="V174" t="n">
+        <v>240</v>
+      </c>
+      <c r="W174" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="X174" t="n">
+        <v>6382</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>57.9</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11619,6 +16115,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T175" t="n">
+        <v>16885</v>
+      </c>
+      <c r="U175" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="V175" t="n">
+        <v>575</v>
+      </c>
+      <c r="W175" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="X175" t="n">
+        <v>16310</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>56.7</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11680,6 +16204,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="n">
+        <v>1026</v>
+      </c>
+      <c r="U176" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="V176" t="n">
+        <v>375</v>
+      </c>
+      <c r="W176" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X176" t="n">
+        <v>651</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>37.4</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11741,6 +16289,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="n">
+        <v>1286</v>
+      </c>
+      <c r="U177" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="V177" t="n">
+        <v>80</v>
+      </c>
+      <c r="W177" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="X177" t="n">
+        <v>1206</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11802,6 +16374,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T178" t="n">
+        <v>14692</v>
+      </c>
+      <c r="U178" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="V178" t="n">
+        <v>1820</v>
+      </c>
+      <c r="W178" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="X178" t="n">
+        <v>12872</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>41.2</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11863,6 +16459,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T179" t="n">
+        <v>6736</v>
+      </c>
+      <c r="U179" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="V179" t="n">
+        <v>1460</v>
+      </c>
+      <c r="W179" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="X179" t="n">
+        <v>5276</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>44.7</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11924,6 +16544,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="n">
+        <v>1551</v>
+      </c>
+      <c r="U180" t="n">
+        <v>38</v>
+      </c>
+      <c r="V180" t="n">
+        <v>460</v>
+      </c>
+      <c r="W180" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="X180" t="n">
+        <v>1091</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>31.3</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11989,6 +16633,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T181" t="n">
+        <v>18741</v>
+      </c>
+      <c r="U181" t="n">
+        <v>40</v>
+      </c>
+      <c r="V181" t="n">
+        <v>3495</v>
+      </c>
+      <c r="W181" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="X181" t="n">
+        <v>15246</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>35.9</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12050,6 +16722,14 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="inlineStr"/>
+      <c r="Y182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12111,6 +16791,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T183" t="n">
+        <v>3122</v>
+      </c>
+      <c r="U183" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="V183" t="n">
+        <v>1190</v>
+      </c>
+      <c r="W183" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="X183" t="n">
+        <v>1932</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>40.4</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12172,6 +16876,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T184" t="n">
+        <v>6010</v>
+      </c>
+      <c r="U184" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="V184" t="n">
+        <v>1210</v>
+      </c>
+      <c r="W184" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="X184" t="n">
+        <v>4800</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12233,6 +16961,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="n">
+        <v>6322</v>
+      </c>
+      <c r="U185" t="n">
+        <v>42</v>
+      </c>
+      <c r="V185" t="n">
+        <v>1770</v>
+      </c>
+      <c r="W185" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="X185" t="n">
+        <v>4552</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>36.4</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12294,6 +17046,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="n">
+        <v>4487</v>
+      </c>
+      <c r="U186" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="V186" t="n">
+        <v>1515</v>
+      </c>
+      <c r="W186" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X186" t="n">
+        <v>2972</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>49.9</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12359,6 +17135,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T187" t="n">
+        <v>1855</v>
+      </c>
+      <c r="U187" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="V187" t="n">
+        <v>985</v>
+      </c>
+      <c r="W187" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="X187" t="n">
+        <v>870</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>45.9</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12420,6 +17224,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U188" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="V188" t="n">
+        <v>945</v>
+      </c>
+      <c r="W188" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="X188" t="n">
+        <v>1055</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>36.1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12481,6 +17309,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="n">
+        <v>2070</v>
+      </c>
+      <c r="U189" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="V189" t="n">
+        <v>1150</v>
+      </c>
+      <c r="W189" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="X189" t="n">
+        <v>920</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>37.2</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12546,6 +17398,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T190" t="n">
+        <v>12178</v>
+      </c>
+      <c r="U190" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="V190" t="n">
+        <v>1700</v>
+      </c>
+      <c r="W190" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="X190" t="n">
+        <v>10478</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12611,6 +17491,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T191" t="n">
+        <v>4328</v>
+      </c>
+      <c r="U191" t="n">
+        <v>58</v>
+      </c>
+      <c r="V191" t="n">
+        <v>910</v>
+      </c>
+      <c r="W191" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="X191" t="n">
+        <v>3418</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>55.7</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12676,6 +17584,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T192" t="n">
+        <v>1157</v>
+      </c>
+      <c r="U192" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="V192" t="n">
+        <v>490</v>
+      </c>
+      <c r="W192" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="X192" t="n">
+        <v>667</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>54.2</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12741,6 +17677,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T193" t="n">
+        <v>3901</v>
+      </c>
+      <c r="U193" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="V193" t="n">
+        <v>950</v>
+      </c>
+      <c r="W193" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="X193" t="n">
+        <v>2951</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>26.1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12802,6 +17766,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="n">
+        <v>5126</v>
+      </c>
+      <c r="U194" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="V194" t="n">
+        <v>1610</v>
+      </c>
+      <c r="W194" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="X194" t="n">
+        <v>3516</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>53.5</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12863,6 +17851,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="n">
+        <v>4541</v>
+      </c>
+      <c r="U195" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="V195" t="n">
+        <v>1630</v>
+      </c>
+      <c r="W195" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="X195" t="n">
+        <v>2911</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>60.4</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12928,6 +17940,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T196" t="n">
+        <v>1890</v>
+      </c>
+      <c r="U196" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="V196" t="n">
+        <v>1500</v>
+      </c>
+      <c r="W196" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="X196" t="n">
+        <v>390</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>43.6</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12993,6 +18033,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T197" t="n">
+        <v>2106</v>
+      </c>
+      <c r="U197" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="V197" t="n">
+        <v>695</v>
+      </c>
+      <c r="W197" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="X197" t="n">
+        <v>1411</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>29.2</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13054,6 +18122,30 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="n">
+        <v>10452</v>
+      </c>
+      <c r="U198" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="V198" t="n">
+        <v>1930</v>
+      </c>
+      <c r="W198" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="X198" t="n">
+        <v>8522</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>51.7</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13115,6 +18207,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="n">
+        <v>9390</v>
+      </c>
+      <c r="U199" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="V199" t="n">
+        <v>1630</v>
+      </c>
+      <c r="W199" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="X199" t="n">
+        <v>7760</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13176,6 +18292,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="n">
+        <v>1499</v>
+      </c>
+      <c r="U200" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="V200" t="n">
+        <v>715</v>
+      </c>
+      <c r="W200" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="X200" t="n">
+        <v>784</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13237,6 +18377,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="n">
+        <v>2986</v>
+      </c>
+      <c r="U201" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="V201" t="n">
+        <v>1205</v>
+      </c>
+      <c r="W201" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="X201" t="n">
+        <v>1781</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>31.9</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13298,6 +18462,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="n">
+        <v>2599</v>
+      </c>
+      <c r="U202" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="V202" t="n">
+        <v>1195</v>
+      </c>
+      <c r="W202" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="X202" t="n">
+        <v>1404</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>41.2</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13359,6 +18547,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U203" t="n">
+        <v>43</v>
+      </c>
+      <c r="V203" t="n">
+        <v>1405</v>
+      </c>
+      <c r="W203" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="X203" t="n">
+        <v>1523</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>34.1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13420,6 +18632,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="n">
+        <v>2608</v>
+      </c>
+      <c r="U204" t="n">
+        <v>40</v>
+      </c>
+      <c r="V204" t="n">
+        <v>910</v>
+      </c>
+      <c r="W204" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="X204" t="n">
+        <v>1698</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13481,6 +18717,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="n">
+        <v>2557</v>
+      </c>
+      <c r="U205" t="n">
+        <v>57</v>
+      </c>
+      <c r="V205" t="n">
+        <v>790</v>
+      </c>
+      <c r="W205" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="X205" t="n">
+        <v>1767</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>53.7</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13550,6 +18810,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T206" t="n">
+        <v>132</v>
+      </c>
+      <c r="U206" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="V206" t="n">
+        <v>10</v>
+      </c>
+      <c r="W206" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="X206" t="n">
+        <v>122</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>34.3</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13615,6 +18903,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T207" t="n">
+        <v>850</v>
+      </c>
+      <c r="U207" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="V207" t="n">
+        <v>20</v>
+      </c>
+      <c r="W207" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="X207" t="n">
+        <v>830</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>51.6</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13680,6 +18996,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T208" t="n">
+        <v>667</v>
+      </c>
+      <c r="U208" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="V208" t="n">
+        <v>20</v>
+      </c>
+      <c r="W208" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="X208" t="n">
+        <v>647</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13745,6 +19089,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T209" t="n">
+        <v>815</v>
+      </c>
+      <c r="U209" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V209" t="n">
+        <v>20</v>
+      </c>
+      <c r="W209" t="n">
+        <v>62</v>
+      </c>
+      <c r="X209" t="n">
+        <v>795</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13810,6 +19182,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T210" t="n">
+        <v>1089</v>
+      </c>
+      <c r="U210" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="V210" t="n">
+        <v>30</v>
+      </c>
+      <c r="W210" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="X210" t="n">
+        <v>1059</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>52.4</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13875,6 +19275,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T211" t="n">
+        <v>1144</v>
+      </c>
+      <c r="U211" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="V211" t="n">
+        <v>30</v>
+      </c>
+      <c r="W211" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="X211" t="n">
+        <v>1114</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>52.9</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13940,6 +19368,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T212" t="n">
+        <v>1557</v>
+      </c>
+      <c r="U212" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="V212" t="n">
+        <v>60</v>
+      </c>
+      <c r="W212" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="X212" t="n">
+        <v>1497</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>54.2</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14005,6 +19461,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T213" t="n">
+        <v>694</v>
+      </c>
+      <c r="U213" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="V213" t="n">
+        <v>20</v>
+      </c>
+      <c r="W213" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="X213" t="n">
+        <v>674</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>51.6</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14066,6 +19550,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="n">
+        <v>245</v>
+      </c>
+      <c r="U214" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="V214" t="n">
+        <v>10</v>
+      </c>
+      <c r="W214" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="X214" t="n">
+        <v>235</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -14131,6 +19639,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T215" t="n">
+        <v>1920</v>
+      </c>
+      <c r="U215" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="V215" t="n">
+        <v>35</v>
+      </c>
+      <c r="W215" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X215" t="n">
+        <v>1885</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>51.2</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -14196,6 +19732,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T216" t="n">
+        <v>3245</v>
+      </c>
+      <c r="U216" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V216" t="n">
+        <v>35</v>
+      </c>
+      <c r="W216" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="X216" t="n">
+        <v>3210</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>54.1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -14261,6 +19825,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T217" t="n">
+        <v>829</v>
+      </c>
+      <c r="U217" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="V217" t="n">
+        <v>35</v>
+      </c>
+      <c r="W217" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="X217" t="n">
+        <v>794</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>53.4</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14326,6 +19918,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T218" t="n">
+        <v>8999</v>
+      </c>
+      <c r="U218" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="V218" t="n">
+        <v>2235</v>
+      </c>
+      <c r="W218" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="X218" t="n">
+        <v>6764</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>64.5</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -14391,6 +20011,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T219" t="n">
+        <v>7820</v>
+      </c>
+      <c r="U219" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="V219" t="n">
+        <v>1460</v>
+      </c>
+      <c r="W219" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="X219" t="n">
+        <v>6360</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>47.9</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14456,6 +20104,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T220" t="n">
+        <v>2275</v>
+      </c>
+      <c r="U220" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="V220" t="n">
+        <v>1045</v>
+      </c>
+      <c r="W220" t="n">
+        <v>67</v>
+      </c>
+      <c r="X220" t="n">
+        <v>1230</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>42.4</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -14521,6 +20197,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T221" t="n">
+        <v>2880</v>
+      </c>
+      <c r="U221" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="V221" t="n">
+        <v>585</v>
+      </c>
+      <c r="W221" t="n">
+        <v>61</v>
+      </c>
+      <c r="X221" t="n">
+        <v>2295</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>24.1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14582,6 +20286,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="n">
+        <v>7290</v>
+      </c>
+      <c r="U222" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="V222" t="n">
+        <v>420</v>
+      </c>
+      <c r="W222" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="X222" t="n">
+        <v>6870</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>45.3</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14647,6 +20375,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T223" t="n">
+        <v>5974</v>
+      </c>
+      <c r="U223" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="V223" t="n">
+        <v>2645</v>
+      </c>
+      <c r="W223" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="X223" t="n">
+        <v>3329</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>50.5</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14712,6 +20468,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T224" t="n">
+        <v>5916</v>
+      </c>
+      <c r="U224" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="V224" t="n">
+        <v>1710</v>
+      </c>
+      <c r="W224" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="X224" t="n">
+        <v>4206</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>50.4</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14773,6 +20557,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T225" t="n">
+        <v>2559</v>
+      </c>
+      <c r="U225" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="V225" t="n">
+        <v>1020</v>
+      </c>
+      <c r="W225" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="X225" t="n">
+        <v>1539</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>46.6</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14834,6 +20642,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T226" t="n">
+        <v>2601</v>
+      </c>
+      <c r="U226" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="V226" t="n">
+        <v>1030</v>
+      </c>
+      <c r="W226" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="X226" t="n">
+        <v>1571</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>49.5</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -14899,6 +20731,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T227" t="n">
+        <v>585</v>
+      </c>
+      <c r="U227" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="V227" t="n">
+        <v>340</v>
+      </c>
+      <c r="W227" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="X227" t="n">
+        <v>245</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>52.5</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14964,6 +20820,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T228" t="n">
+        <v>1372</v>
+      </c>
+      <c r="U228" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="V228" t="n">
+        <v>480</v>
+      </c>
+      <c r="W228" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="X228" t="n">
+        <v>892</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>54.3</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -15029,6 +20909,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T229" t="n">
+        <v>1880</v>
+      </c>
+      <c r="U229" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="V229" t="n">
+        <v>590</v>
+      </c>
+      <c r="W229" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="X229" t="n">
+        <v>1290</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>46.2</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -15090,6 +20994,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T230" t="n">
+        <v>9506</v>
+      </c>
+      <c r="U230" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="V230" t="n">
+        <v>890</v>
+      </c>
+      <c r="W230" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="X230" t="n">
+        <v>8616</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>24.3</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -15159,6 +21087,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T231" t="n">
+        <v>1675</v>
+      </c>
+      <c r="U231" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="V231" t="n">
+        <v>520</v>
+      </c>
+      <c r="W231" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="X231" t="n">
+        <v>1155</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>29.3</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15223,6 +21175,30 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T232" t="n">
+        <v>9765</v>
+      </c>
+      <c r="U232" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V232" t="n">
+        <v>1190</v>
+      </c>
+      <c r="W232" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="X232" t="n">
+        <v>8575</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>26.7</v>
       </c>
     </row>
     <row r="233">
@@ -15285,6 +21261,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T233" t="n">
+        <v>2415</v>
+      </c>
+      <c r="U233" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="V233" t="n">
+        <v>880</v>
+      </c>
+      <c r="W233" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="X233" t="n">
+        <v>1535</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -15350,6 +21350,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T234" t="n">
+        <v>17844</v>
+      </c>
+      <c r="U234" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="V234" t="n">
+        <v>2010</v>
+      </c>
+      <c r="W234" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="X234" t="n">
+        <v>15834</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>24.1</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -15415,6 +21443,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T235" t="n">
+        <v>15132</v>
+      </c>
+      <c r="U235" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="V235" t="n">
+        <v>1920</v>
+      </c>
+      <c r="W235" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="X235" t="n">
+        <v>13212</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>32.3</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -15480,6 +21536,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R236" t="inlineStr"/>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T236" t="n">
+        <v>866</v>
+      </c>
+      <c r="U236" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="V236" t="n">
+        <v>120</v>
+      </c>
+      <c r="W236" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="X236" t="n">
+        <v>746</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15541,6 +21621,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T237" t="n">
+        <v>7705</v>
+      </c>
+      <c r="U237" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="V237" t="n">
+        <v>1310</v>
+      </c>
+      <c r="W237" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="X237" t="n">
+        <v>6395</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>27.4</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -15602,6 +21706,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R238" t="inlineStr"/>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T238" t="n">
+        <v>14658</v>
+      </c>
+      <c r="U238" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="V238" t="n">
+        <v>1600</v>
+      </c>
+      <c r="W238" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="X238" t="n">
+        <v>13058</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>23.2</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -15667,6 +21795,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T239" t="n">
+        <v>2090</v>
+      </c>
+      <c r="U239" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="V239" t="n">
+        <v>460</v>
+      </c>
+      <c r="W239" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="X239" t="n">
+        <v>1630</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15728,6 +21880,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R240" t="inlineStr"/>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T240" t="n">
+        <v>2490</v>
+      </c>
+      <c r="U240" t="n">
+        <v>55</v>
+      </c>
+      <c r="V240" t="n">
+        <v>620</v>
+      </c>
+      <c r="W240" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="X240" t="n">
+        <v>1870</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>50.8</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15793,6 +21969,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R241" t="inlineStr"/>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T241" t="n">
+        <v>1185</v>
+      </c>
+      <c r="U241" t="n">
+        <v>54</v>
+      </c>
+      <c r="V241" t="n">
+        <v>220</v>
+      </c>
+      <c r="W241" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="X241" t="n">
+        <v>965</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>51.2</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -15858,6 +22058,34 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T242" t="n">
+        <v>3723</v>
+      </c>
+      <c r="U242" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="V242" t="n">
+        <v>2090</v>
+      </c>
+      <c r="W242" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="X242" t="n">
+        <v>1633</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>55.4</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -15919,6 +22147,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R243" t="inlineStr"/>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T243" t="n">
+        <v>1552</v>
+      </c>
+      <c r="U243" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="V243" t="n">
+        <v>620</v>
+      </c>
+      <c r="W243" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="X243" t="n">
+        <v>932</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -15980,6 +22232,14 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R244" t="inlineStr"/>
+      <c r="S244" t="inlineStr"/>
+      <c r="T244" t="inlineStr"/>
+      <c r="U244" t="inlineStr"/>
+      <c r="V244" t="inlineStr"/>
+      <c r="W244" t="inlineStr"/>
+      <c r="X244" t="inlineStr"/>
+      <c r="Y244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16041,6 +22301,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T245" t="n">
+        <v>3195</v>
+      </c>
+      <c r="U245" t="n">
+        <v>62</v>
+      </c>
+      <c r="V245" t="n">
+        <v>450</v>
+      </c>
+      <c r="W245" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="X245" t="n">
+        <v>2745</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>60.8</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -16102,6 +22386,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T246" t="n">
+        <v>5990</v>
+      </c>
+      <c r="U246" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="V246" t="n">
+        <v>700</v>
+      </c>
+      <c r="W246" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="X246" t="n">
+        <v>5290</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>49.4</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -16167,6 +22475,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T247" t="n">
+        <v>4437</v>
+      </c>
+      <c r="U247" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="V247" t="n">
+        <v>1040</v>
+      </c>
+      <c r="W247" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="X247" t="n">
+        <v>3397</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>37.6</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -16232,6 +22568,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T248" t="n">
+        <v>3660</v>
+      </c>
+      <c r="U248" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="V248" t="n">
+        <v>915</v>
+      </c>
+      <c r="W248" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="X248" t="n">
+        <v>2745</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>34.4</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -16297,6 +22661,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T249" t="n">
+        <v>4952</v>
+      </c>
+      <c r="U249" t="n">
+        <v>26</v>
+      </c>
+      <c r="V249" t="n">
+        <v>885</v>
+      </c>
+      <c r="W249" t="n">
+        <v>57</v>
+      </c>
+      <c r="X249" t="n">
+        <v>4067</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>12.2</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -16358,6 +22750,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R250" t="inlineStr"/>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T250" t="n">
+        <v>4370</v>
+      </c>
+      <c r="U250" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="V250" t="n">
+        <v>510</v>
+      </c>
+      <c r="W250" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="X250" t="n">
+        <v>3860</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>18.3</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -16419,6 +22835,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R251" t="inlineStr"/>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T251" t="n">
+        <v>4015</v>
+      </c>
+      <c r="U251" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="V251" t="n">
+        <v>405</v>
+      </c>
+      <c r="W251" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="X251" t="n">
+        <v>3610</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -16480,6 +22920,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R252" t="inlineStr"/>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T252" t="n">
+        <v>4450</v>
+      </c>
+      <c r="U252" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="V252" t="n">
+        <v>460</v>
+      </c>
+      <c r="W252" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="X252" t="n">
+        <v>3990</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>13.5</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -16545,6 +23009,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T253" t="n">
+        <v>90</v>
+      </c>
+      <c r="U253" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="V253" t="n">
+        <v>50</v>
+      </c>
+      <c r="W253" t="n">
+        <v>55</v>
+      </c>
+      <c r="X253" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>48.7</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -16610,6 +23102,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T254" t="n">
+        <v>100</v>
+      </c>
+      <c r="U254" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="V254" t="n">
+        <v>50</v>
+      </c>
+      <c r="W254" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="X254" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -16675,6 +23195,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T255" t="n">
+        <v>115</v>
+      </c>
+      <c r="U255" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="V255" t="n">
+        <v>30</v>
+      </c>
+      <c r="W255" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="X255" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>51.9</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -16740,6 +23288,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T256" t="n">
+        <v>132</v>
+      </c>
+      <c r="U256" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="V256" t="n">
+        <v>100</v>
+      </c>
+      <c r="W256" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="X256" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>53.3</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -16801,6 +23377,26 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr"/>
+      <c r="T257" t="n">
+        <v>50</v>
+      </c>
+      <c r="U257" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="V257" t="inlineStr"/>
+      <c r="W257" t="inlineStr"/>
+      <c r="X257" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>51.6</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -16866,6 +23462,30 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="T258" t="n">
+        <v>36</v>
+      </c>
+      <c r="U258" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="V258" t="inlineStr"/>
+      <c r="W258" t="inlineStr"/>
+      <c r="X258" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>57.2</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -16927,9 +23547,33 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>Carry Over</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr"/>
+      <c r="T259" t="n">
+        <v>146</v>
+      </c>
+      <c r="U259" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="V259" t="n">
+        <v>60</v>
+      </c>
+      <c r="W259" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="X259" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q259"/>
+  <autoFilter ref="A1:Y259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16940,7 +23584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17067,6 +23711,30 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Status FW27 / Status SS28</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Carry Over / New / Update, from the forecast files' Status field -- shown per season since a franchise can differ between them (e.g. New in FW27, Carry Over in SS28). Blank if no forecast row matched that season (see RR-014).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Forecast Qty / GP% (total, DTC, Wholesale)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Summed across every style and season rolled into the franchise, from the two forecast files (RR-011/RR-012). Blank (not 0) when none of the franchise's styles have a forecast match -- 25/616 main-range style rows don't (RR-014). GP% blended vs. DTC/Wholesale split -- blended hides a real spread, so both are shown.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
+++ b/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$Y$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$Z$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,6 +138,4911 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>74</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>79</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>82</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>89</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>90</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>96</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>116</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>117</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>118</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>119</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>120</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>121</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>122</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>123</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>124</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>125</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>126</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>127</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>129</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>131</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>132</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>133</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId101"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>134</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>135</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>137</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>138</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId105"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>139</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId106"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>140</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId107"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>141</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>142</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>144</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="110" name="Image 110" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId110"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="111" name="Image 111" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId111"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>146</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="112" name="Image 112" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId112"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>147</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId113"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>148</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId114"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>149</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="115" name="Image 115" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId115"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>150</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="116" name="Image 116" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId116"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>151</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="117" name="Image 117" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId117"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>152</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="118" name="Image 118" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId118"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>154</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="119" name="Image 119" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId119"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>155</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="120" name="Image 120" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId120"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>156</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="121" name="Image 121" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId121"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>157</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="122" name="Image 122" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId122"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>158</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="123" name="Image 123" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId123"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>159</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="124" name="Image 124" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId124"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="125" name="Image 125" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId125"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>165</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="126" name="Image 126" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId126"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>168</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="127" name="Image 127" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId127"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>169</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="128" name="Image 128" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId128"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>170</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="129" name="Image 129" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId129"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>171</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="130" name="Image 130" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId130"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>172</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="131" name="Image 131" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId131"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>173</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="132" name="Image 132" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId132"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>174</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="133" name="Image 133" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId133"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>177</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="134" name="Image 134" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId134"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>178</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="135" name="Image 135" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId135"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>180</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="136" name="Image 136" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId136"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>181</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="137" name="Image 137" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId137"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>182</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="138" name="Image 138" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId138"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>183</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="139" name="Image 139" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId139"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>186</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="140" name="Image 140" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId140"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>189</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="141" name="Image 141" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId141"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>190</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="142" name="Image 142" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId142"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>191</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="143" name="Image 143" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId143"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>192</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="144" name="Image 144" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId144"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>195</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="145" name="Image 145" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId145"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>196</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="146" name="Image 146" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId146"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>205</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="147" name="Image 147" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId147"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>206</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="148" name="Image 148" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId148"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>207</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="149" name="Image 149" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId149"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>208</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="150" name="Image 150" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId150"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>209</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="151" name="Image 151" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId151"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>210</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="152" name="Image 152" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId152"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>211</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="153" name="Image 153" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId153"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>212</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="154" name="Image 154" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId154"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="155" name="Image 155" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId155"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>215</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="156" name="Image 156" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId156"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>216</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="157" name="Image 157" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId157"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>217</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="158" name="Image 158" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId158"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>218</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="159" name="Image 159" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId159"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>219</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="160" name="Image 160" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId160"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>220</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="161" name="Image 161" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId161"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>222</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="162" name="Image 162" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId162"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>223</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="163" name="Image 163" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId163"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>224</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="164" name="Image 164" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId164"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>225</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="165" name="Image 165" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId165"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>226</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="166" name="Image 166" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId166"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>227</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="167" name="Image 167" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId167"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>228</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="168" name="Image 168" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId168"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>229</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="169" name="Image 169" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId169"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>230</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="170" name="Image 170" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId170"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>231</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="171" name="Image 171" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId171"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>232</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="172" name="Image 172" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId172"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>233</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="173" name="Image 173" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId173"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>234</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="174" name="Image 174" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId174"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>235</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="175" name="Image 175" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId175"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>236</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="176" name="Image 176" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId176"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>237</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="177" name="Image 177" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId177"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>238</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="178" name="Image 178" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId178"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>239</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="179" name="Image 179" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId179"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>240</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="180" name="Image 180" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId180"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>241</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="181" name="Image 181" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId181"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>242</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="182" name="Image 182" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId182"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>243</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="183" name="Image 183" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId183"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>244</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="184" name="Image 184" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId184"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>245</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="185" name="Image 185" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId185"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>246</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="186" name="Image 186" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId186"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>247</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="187" name="Image 187" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId187"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>248</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="188" name="Image 188" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId188"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>249</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="189" name="Image 189" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId189"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>250</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="190" name="Image 190" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId190"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>251</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="191" name="Image 191" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId191"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>252</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="192" name="Image 192" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId192"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>253</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="193" name="Image 193" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId193"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>254</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="194" name="Image 194" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId194"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>255</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="195" name="Image 195" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId195"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>257</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="196" name="Image 196" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId196"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,7 +5334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y259"/>
+  <dimension ref="A1:Z259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -457,6 +5362,7 @@
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="26" customWidth="1" min="24" max="24"/>
     <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="8.571428571428571" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,8 +5491,13 @@
           <t>Forecast GP% (Wholesale)</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Product Image</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>Aresk Beanie</t>
@@ -671,7 +5582,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>Aze II Beanie</t>
@@ -756,7 +5667,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>Brand Five Panel Cap</t>
@@ -792,7 +5703,9 @@
         <v>450</v>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>61.3</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>2</v>
@@ -849,7 +5762,7 @@
         <v>59.4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>Haglöfs Bandana</t>
@@ -881,7 +5794,9 @@
         <v>400</v>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>60</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Special edition: Blueberry</t>
@@ -938,7 +5853,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>Haglöfs Cap</t>
@@ -970,7 +5885,9 @@
         <v>400</v>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>61.3</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>1</v>
@@ -1023,7 +5940,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>Haglöfs LX Hat</t>
@@ -1055,7 +5972,9 @@
         <v>500</v>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>52.4</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>1</v>
@@ -1108,7 +6027,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>Haglöfs Neck Tube</t>
@@ -1140,7 +6059,9 @@
         <v>300</v>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>1</v>
@@ -1193,7 +6114,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>Haglöfs Trucker Cap</t>
@@ -1225,7 +6146,9 @@
         <v>400</v>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>61</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>1</v>
@@ -1278,7 +6201,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>L.I.M Pace Cap</t>
@@ -1310,7 +6233,9 @@
         <v>500</v>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Special edition: Blueberry</t>
@@ -1367,7 +6292,7 @@
         <v>58.3</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>Mountain II Cap</t>
@@ -1452,7 +6377,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>Outsiders Beanie</t>
@@ -1537,7 +6462,7 @@
         <v>55.6</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>Rosson Beanie</t>
@@ -1622,7 +6547,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>Rosson II Balaclava</t>
@@ -1707,7 +6632,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>Solis Hat</t>
@@ -1739,7 +6664,9 @@
         <v>600</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>60</v>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>1</v>
@@ -1792,7 +6719,7 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>Stretch Webbing Belt</t>
@@ -1828,7 +6755,9 @@
         <v>400</v>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>62</v>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>2</v>
@@ -1885,7 +6814,7 @@
         <v>45.6</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>Sun Capsule Multi Cover</t>
@@ -1917,7 +6846,9 @@
         <v>1800</v>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>61.3</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>1</v>
@@ -1954,7 +6885,7 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>Thermal Beanie</t>
@@ -2039,7 +6970,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>Tova Wool Beanie</t>
@@ -2124,7 +7055,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>Vara Alpha Cap</t>
@@ -2209,7 +7140,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>Vassi Beanie</t>
@@ -2294,7 +7225,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Vassi Headband</t>
@@ -2379,7 +7310,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>Flat accessory bag II</t>
@@ -2421,7 +7352,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>59.8</v>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>2</v>
@@ -2478,7 +7411,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>Fram 1L</t>
@@ -2514,7 +7447,9 @@
         <v>650</v>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>2</v>
@@ -2571,7 +7506,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>Keywallet</t>
@@ -2603,7 +7538,9 @@
         <v>450</v>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>60.5</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>1</v>
@@ -2656,7 +7593,7 @@
         <v>16.9</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>Lava travel tube</t>
@@ -2692,7 +7629,9 @@
         <v>550</v>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>2</v>
@@ -2749,7 +7688,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>Magma Waist pack 3,5L</t>
@@ -2785,7 +7724,9 @@
         <v>800</v>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>2</v>
@@ -2842,7 +7783,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Packing cube 12L</t>
@@ -2878,7 +7819,9 @@
         <v>800</v>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>2</v>
@@ -2935,7 +7878,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>Packing cube 8L</t>
@@ -2971,7 +7914,9 @@
         <v>700</v>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>2</v>
@@ -3028,7 +7973,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>Raincover 15-30L</t>
@@ -3064,7 +8009,9 @@
         <v>400</v>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>70</v>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>2</v>
@@ -3117,7 +8064,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
           <t>Raincover 25-40L</t>
@@ -3153,7 +8100,9 @@
         <v>450</v>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>73.09999999999999</v>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>2</v>
@@ -3206,7 +8155,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
           <t>Raincover 40-60L</t>
@@ -3242,7 +8191,9 @@
         <v>500</v>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>66.09999999999999</v>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>2</v>
@@ -3295,7 +8246,7 @@
         <v>46.3</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
           <t>Raincover 60-80L</t>
@@ -3331,7 +8282,9 @@
         <v>600</v>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>63.5</v>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>2</v>
@@ -3384,7 +8337,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
           <t>Shoulder pocket</t>
@@ -3420,7 +8373,9 @@
         <v>500</v>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
         <v>2</v>
@@ -3477,7 +8432,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>Shoulder pouch</t>
@@ -3513,7 +8468,9 @@
         <v>400</v>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>2</v>
@@ -3570,7 +8527,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
           <t>Sling pouch 2L</t>
@@ -3606,7 +8563,9 @@
         <v>800</v>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>55.3</v>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>2</v>
@@ -3663,7 +8622,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
           <t>Tight Pocket bag</t>
@@ -3699,7 +8658,9 @@
         <v>350</v>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>63.1</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Special edition: Blueberry</t>
@@ -3760,7 +8721,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
           <t>Tight hip pack 1</t>
@@ -3796,7 +8757,9 @@
         <v>350</v>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>61.8</v>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>2</v>
@@ -3853,7 +8816,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
           <t>Tight hip pack 3,5</t>
@@ -3889,7 +8852,9 @@
         <v>450</v>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>61.8</v>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>2</v>
@@ -3946,7 +8911,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
           <t>Utility pouch 3L</t>
@@ -3982,7 +8947,9 @@
         <v>800</v>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>2</v>
@@ -4039,7 +9006,7 @@
         <v>43.7</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>Courier Messenger Bag</t>
@@ -4075,7 +9042,9 @@
         <v>1600</v>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>61.8</v>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>2</v>
@@ -4132,7 +9101,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>Fjatla 40</t>
@@ -4168,7 +9137,9 @@
         <v>1000</v>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>58.5</v>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>2</v>
@@ -4225,7 +9196,7 @@
         <v>53.6</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>Fjatla 60</t>
@@ -4261,7 +9232,9 @@
         <v>1200</v>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>60.7</v>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>2</v>
@@ -4318,7 +9291,7 @@
         <v>57.7</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>Lava 110</t>
@@ -4354,7 +9327,9 @@
         <v>1700</v>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>2</v>
@@ -4411,7 +9386,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>Lava 30</t>
@@ -4447,7 +9422,9 @@
         <v>1300</v>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>58.2</v>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
         <v>2</v>
@@ -4504,7 +9481,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>Lava 50</t>
@@ -4540,7 +9517,9 @@
         <v>1400</v>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>58</v>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>2</v>
@@ -4597,7 +9576,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>Lava 70</t>
@@ -4633,7 +9612,9 @@
         <v>1500</v>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>58.5</v>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>2</v>
@@ -4690,7 +9671,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>Lava 90</t>
@@ -4726,7 +9707,9 @@
         <v>1600</v>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>58.5</v>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
         <v>2</v>
@@ -4783,7 +9766,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="60" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
           <t>Magma 42L</t>
@@ -4819,7 +9802,9 @@
         <v>1800</v>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>59.7</v>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>2</v>
@@ -4876,7 +9861,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
           <t>Magma 65L</t>
@@ -4912,7 +9897,9 @@
         <v>2000</v>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>59.4</v>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
         <v>2</v>
@@ -4969,7 +9956,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>Tight duffle 50</t>
@@ -5005,7 +9992,9 @@
         <v>1300</v>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>61</v>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
         <v>2</v>
@@ -5062,7 +10051,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
           <t>Latnja Wool 3/4 Pant</t>
@@ -5147,7 +10136,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
           <t>Latnja Wool Crew Neck</t>
@@ -5232,7 +10221,7 @@
         <v>16.1</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
           <t>Latnja Wool Long John's</t>
@@ -5317,7 +10306,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
           <t>Kobbe Sandal Low</t>
@@ -5349,7 +10338,9 @@
         <v>1000</v>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>55.1</v>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
         <v>2</v>
@@ -5402,7 +10393,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
           <t>Backup</t>
@@ -5438,7 +10429,9 @@
         <v>1500</v>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>64.40000000000001</v>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
         <v>2</v>
@@ -5495,7 +10488,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
           <t>Corker Large</t>
@@ -5531,7 +10524,9 @@
         <v>1300</v>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>58.4</v>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
         <v>2</v>
@@ -5588,7 +10583,7 @@
         <v>40.3</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="60" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
           <t>Corker Medium</t>
@@ -5624,7 +10619,9 @@
         <v>1200</v>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>58.9</v>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
         <v>2</v>
@@ -5681,7 +10678,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
           <t>Jarve Multi 22</t>
@@ -5717,7 +10714,9 @@
         <v>1500</v>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>60.9</v>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
         <v>2</v>
@@ -5774,7 +10773,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
           <t>Jarve Multi 28</t>
@@ -5810,7 +10809,9 @@
         <v>1600</v>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>60.6</v>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
         <v>2</v>
@@ -5867,7 +10868,7 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
           <t>Skuta 15</t>
@@ -5903,7 +10904,9 @@
         <v>800</v>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>57</v>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
         <v>2</v>
@@ -5960,7 +10963,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="60" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
           <t>Tight 15</t>
@@ -6000,7 +11003,9 @@
         <v>1000</v>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>55.3</v>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
         <v>2</v>
@@ -6057,7 +11062,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
           <t>Tight 8</t>
@@ -6097,7 +11102,9 @@
         <v>900</v>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>58.2</v>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
         <v>2</v>
@@ -6154,7 +11161,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="60" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
           <t>Tight Large</t>
@@ -6190,7 +11197,9 @@
         <v>1200</v>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>61.1</v>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
         <v>2</v>
@@ -6247,7 +11256,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
           <t>Tight Medium</t>
@@ -6283,7 +11292,9 @@
         <v>1100</v>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>60.1</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>Special edition: Blueberry</t>
@@ -6344,7 +11355,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="60" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
           <t>Tight Pro Large</t>
@@ -6380,7 +11391,9 @@
         <v>1300</v>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>63.5</v>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
         <v>2</v>
@@ -6437,7 +11450,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
           <t>Tight Pro Medium</t>
@@ -6473,7 +11486,9 @@
         <v>1200</v>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>62.5</v>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
         <v>2</v>
@@ -6530,7 +11545,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="60" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
           <t>Tight Small</t>
@@ -6566,7 +11581,9 @@
         <v>1000</v>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>57.8</v>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
         <v>2</v>
@@ -6623,7 +11640,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="60" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
           <t>Tight Tote 25</t>
@@ -6659,7 +11676,9 @@
         <v>1000</v>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>60.6</v>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
         <v>2</v>
@@ -6716,7 +11735,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="60" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>Tight X-Small</t>
@@ -6752,7 +11771,9 @@
         <v>900</v>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>56.3</v>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
         <v>2</v>
@@ -6809,7 +11830,7 @@
         <v>45.1</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="60" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>Vara 20L</t>
@@ -6845,7 +11866,9 @@
         <v>1500</v>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
         <v>2</v>
@@ -6902,7 +11925,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="60" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
           <t>L.I.M Mountain Trail 25</t>
@@ -6938,7 +11961,9 @@
         <v>1700</v>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="n">
+        <v>59.7</v>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
         <v>2</v>
@@ -6995,7 +12020,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="60" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
           <t>L.I.M Trail 15</t>
@@ -7031,7 +12056,9 @@
         <v>1300</v>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="n">
+        <v>60.2</v>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
         <v>2</v>
@@ -7088,7 +12115,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="60" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>Magma 30</t>
@@ -7124,7 +12151,9 @@
         <v>1700</v>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
         <v>2</v>
@@ -7181,7 +12210,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
           <t>Magma 50L</t>
@@ -7217,7 +12246,9 @@
         <v>2600</v>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
         <v>2</v>
@@ -7274,7 +12305,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="60" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
           <t>Magma 60L</t>
@@ -7310,7 +12341,9 @@
         <v>2800</v>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
         <v>2</v>
@@ -7367,7 +12400,7 @@
         <v>45.6</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="60" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
           <t>Magma Roll-top 40 WR</t>
@@ -7403,7 +12436,9 @@
         <v>2000</v>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>61</v>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
         <v>2</v>
@@ -7460,7 +12495,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="60" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
           <t>Vide 20</t>
@@ -7496,7 +12531,9 @@
         <v>1100</v>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>52.8</v>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="n">
         <v>2</v>
@@ -7553,7 +12590,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="60" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
           <t>Vide 30</t>
@@ -7589,7 +12626,9 @@
         <v>1300</v>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>54.4</v>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
         <v>2</v>
@@ -7646,7 +12685,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="60" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
           <t>Fast Hike Low</t>
@@ -7682,7 +12721,9 @@
         <v>1700</v>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="n">
+        <v>58.9</v>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
         <v>4</v>
@@ -7739,7 +12780,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="60" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
           <t>Haglöfs Fast Hike PROOF Low</t>
@@ -7775,7 +12816,9 @@
         <v>1900</v>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
         <v>4</v>
@@ -7832,7 +12875,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="60" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
           <t>Haglöfs Horizon Hike GTX WL Mid</t>
@@ -7917,7 +12960,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="60" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon Hike GTX Low</t>
@@ -7953,7 +12996,9 @@
         <v>2200</v>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
         <v>4</v>
@@ -8010,7 +13055,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="60" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon Hike GTX Mid</t>
@@ -8046,7 +13091,9 @@
         <v>2500</v>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="n">
         <v>4</v>
@@ -8103,7 +13150,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="60" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon Hike Light Mid</t>
@@ -8188,7 +13235,7 @@
         <v>35.3</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="60" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
           <t>Haglöfs Ridge GTX II Low</t>
@@ -8224,7 +13271,9 @@
         <v>2200</v>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="n">
+        <v>52.4</v>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
         <v>4</v>
@@ -8281,7 +13330,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="60" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
           <t>Haglöfs Ridge GTX II Mid</t>
@@ -8317,7 +13366,9 @@
         <v>2500</v>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>53.9</v>
+      </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
         <v>4</v>
@@ -8374,7 +13425,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="60" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
           <t>Haglöfs Rosson FG Proof Mid</t>
@@ -8410,7 +13461,9 @@
         <v>2200</v>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
         <v>4</v>
@@ -8467,7 +13520,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="60" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
           <t>Haglöfs Rosson Proof Mid</t>
@@ -8503,7 +13556,9 @@
         <v>2000</v>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="n">
+        <v>53.4</v>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
         <v>4</v>
@@ -8560,7 +13615,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="60" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
           <t>Haglöfs Vertigo QL PROOF Low</t>
@@ -8602,7 +13657,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>59.9</v>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
         <v>4</v>
@@ -8659,7 +13716,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="60" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
           <t>Vertigo Proof Low</t>
@@ -8695,7 +13752,9 @@
         <v>1800</v>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>58</v>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="n">
         <v>4</v>
@@ -8752,7 +13811,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="60" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
           <t>Breeze Mimic Hood</t>
@@ -8837,7 +13896,7 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="60" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
           <t>Fram Mimic Jacket</t>
@@ -8922,7 +13981,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="60" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
           <t>Hede Down Coat</t>
@@ -9011,7 +14070,7 @@
         <v>58.8</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="60" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
           <t>Hede Down Hood</t>
@@ -9047,7 +14106,9 @@
         <v>2800</v>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="J95" t="n">
+        <v>60</v>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
         <v>4</v>
@@ -9104,7 +14165,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="60" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
           <t>Hede Down Vest</t>
@@ -9140,7 +14201,9 @@
         <v>2000</v>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="J96" t="n">
+        <v>60</v>
+      </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
         <v>4</v>
@@ -9197,7 +14260,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="60" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
           <t>L.I.M Down Hood Jacket</t>
@@ -9229,7 +14292,9 @@
         <v>6000</v>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>50</v>
+      </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
         <v>2</v>
@@ -9282,7 +14347,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="60" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
           <t>L.I.M Down II Hood</t>
@@ -9367,7 +14432,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="60" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
           <t>L.I.M Mimic Barrier Hood</t>
@@ -9399,7 +14464,9 @@
         <v>2500</v>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="J99" t="n">
+        <v>60</v>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>Special edition: Blueberry</t>
@@ -9456,7 +14523,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="60" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
           <t>L.I.M Mimic Barrier Vest</t>
@@ -9488,7 +14555,9 @@
         <v>1800</v>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="J100" t="n">
+        <v>60</v>
+      </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
         <v>2</v>
@@ -9541,7 +14610,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="60" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
           <t>Long Down II Parka</t>
@@ -9630,7 +14699,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="60" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
           <t>Long Mimic III Parka</t>
@@ -9719,7 +14788,7 @@
         <v>59.3</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="60" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
           <t>Lugna Softshell Overshirt</t>
@@ -9755,7 +14824,9 @@
         <v>1700</v>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="J103" t="n">
+        <v>60</v>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
         <v>4</v>
@@ -9812,7 +14883,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="60" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
           <t>Mimic Alert 2.0 Hood</t>
@@ -9848,7 +14919,9 @@
         <v>2500</v>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="n">
+        <v>63</v>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
         <v>4</v>
@@ -9905,7 +14978,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="60" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
           <t>Mimic Alert 2.0 Jacket</t>
@@ -9941,7 +15014,9 @@
         <v>2200</v>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="J105" t="n">
+        <v>62</v>
+      </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="n">
         <v>4</v>
@@ -9998,7 +15073,7 @@
         <v>34.2</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="60" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
           <t>Mojo Down Hood</t>
@@ -10083,7 +15158,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="60" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
           <t>Nallo Touring Down Hood</t>
@@ -10168,7 +15243,7 @@
         <v>36.8</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="60" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
           <t>ROC Flash Down Hood</t>
@@ -10204,7 +15279,9 @@
         <v>3200</v>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="J108" t="n">
+        <v>60</v>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="n">
         <v>4</v>
@@ -10261,7 +15338,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="60" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
           <t>ROC Flash Down Jacket</t>
@@ -10346,7 +15423,7 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="60" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
           <t>ROC Flash Down Vest</t>
@@ -10431,7 +15508,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="60" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
           <t>Rosson Down Hood</t>
@@ -10516,7 +15593,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="60" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
           <t>Rosson Down Parka</t>
@@ -10601,7 +15678,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="60" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
           <t>Salix Proof Mimic II Parka</t>
@@ -10686,7 +15763,7 @@
         <v>58.3</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="60" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
           <t>Spitz Down Hood</t>
@@ -10771,7 +15848,7 @@
         <v>35.7</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="60" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
           <t>Särna Mimic II Hood</t>
@@ -10807,7 +15884,9 @@
         <v>2200</v>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+      <c r="J115" t="n">
+        <v>70</v>
+      </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
         <v>4</v>
@@ -10864,7 +15943,7 @@
         <v>66.59999999999999</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="60" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
           <t>Alert Mid Pant</t>
@@ -10900,7 +15979,9 @@
         <v>1700</v>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>62</v>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
         <v>4</v>
@@ -10957,7 +16038,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="60" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
           <t>Alert Mid Shorts</t>
@@ -10989,7 +16070,9 @@
         <v>1200</v>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+      <c r="J117" t="n">
+        <v>63</v>
+      </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
         <v>2</v>
@@ -11042,7 +16125,7 @@
         <v>54.4</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="60" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
           <t>Essential Tights</t>
@@ -11078,7 +16161,9 @@
         <v>1000</v>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+      <c r="J118" t="n">
+        <v>66</v>
+      </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
         <v>1</v>
@@ -11131,7 +16216,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="60" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
           <t>Front Flex Pant</t>
@@ -11167,7 +16252,9 @@
         <v>1500</v>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>62</v>
+      </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
         <v>4</v>
@@ -11224,7 +16311,7 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="60" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
           <t>Fuse Pant</t>
@@ -11256,7 +16343,9 @@
         <v>1200</v>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+      <c r="J120" t="n">
+        <v>60</v>
+      </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
         <v>2</v>
@@ -11309,7 +16398,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="60" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
           <t>Fuse Short</t>
@@ -11341,7 +16430,9 @@
         <v>1000</v>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
+      <c r="J121" t="n">
+        <v>60</v>
+      </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
         <v>2</v>
@@ -11394,7 +16485,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="60" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
           <t>Hede Cargo II Pant</t>
@@ -11430,7 +16521,9 @@
         <v>1800</v>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>55</v>
+      </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
         <v>4</v>
@@ -11479,7 +16572,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="60" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
           <t>Hede II Shorts</t>
@@ -11511,7 +16604,9 @@
         <v>1100</v>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>64</v>
+      </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
         <v>2</v>
@@ -11564,7 +16659,7 @@
         <v>55.6</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="60" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
           <t>Hiking Tights</t>
@@ -11600,7 +16695,9 @@
         <v>1200</v>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>60</v>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
         <v>1</v>
@@ -11653,7 +16750,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="60" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
           <t>Korp Lite Pant</t>
@@ -11685,7 +16782,9 @@
         <v>1300</v>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>63</v>
+      </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
         <v>2</v>
@@ -11738,7 +16837,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="60" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
           <t>Korp Lite Shorts</t>
@@ -11770,7 +16869,9 @@
         <v>1000</v>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+      <c r="J126" t="n">
+        <v>60</v>
+      </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
         <v>2</v>
@@ -11823,7 +16924,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="60" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
           <t>L.I.M Pace Shorts</t>
@@ -11855,7 +16956,9 @@
         <v>900</v>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
+      <c r="J127" t="n">
+        <v>62</v>
+      </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
         <v>2</v>
@@ -11908,7 +17011,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="60" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
           <t>L.I.M Windpace Hybrid Pant</t>
@@ -11940,7 +17043,9 @@
         <v>1900</v>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
+      <c r="J128" t="n">
+        <v>50</v>
+      </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
         <v>2</v>
@@ -11993,7 +17098,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="60" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
           <t>Levante Pant</t>
@@ -12029,7 +17134,9 @@
         <v>1500</v>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>61</v>
+      </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="n">
         <v>4</v>
@@ -12086,7 +17193,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="60" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
           <t>Levante Shorts</t>
@@ -12118,7 +17225,9 @@
         <v>1200</v>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+      <c r="J130" t="n">
+        <v>61</v>
+      </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="n">
         <v>2</v>
@@ -12171,7 +17280,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="60" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
           <t>Lite Standard Zip-Off II Pant</t>
@@ -12203,7 +17312,9 @@
         <v>1500</v>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
+      <c r="J131" t="n">
+        <v>59.5</v>
+      </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="n">
         <v>2</v>
@@ -12256,7 +17367,7 @@
         <v>58.6</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="60" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
           <t>Lizard Softshell II Shorts</t>
@@ -12288,7 +17399,9 @@
         <v>1300</v>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
+      <c r="J132" t="n">
+        <v>63</v>
+      </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="n">
         <v>2</v>
@@ -12341,7 +17454,7 @@
         <v>67.09999999999999</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="60" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
           <t>Magma Rugged Pant</t>
@@ -12377,7 +17490,9 @@
         <v>2000</v>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+      <c r="J133" t="n">
+        <v>62</v>
+      </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="n">
         <v>4</v>
@@ -12434,7 +17549,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="60" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
           <t>Magma Rugged Wide Pant</t>
@@ -12466,7 +17581,9 @@
         <v>2000</v>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
+      <c r="J134" t="n">
+        <v>65</v>
+      </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="n">
         <v>2</v>
@@ -12519,7 +17636,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="60" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
           <t>Mid Standard II Pant</t>
@@ -12551,7 +17668,9 @@
         <v>1700</v>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
+      <c r="J135" t="n">
+        <v>65</v>
+      </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="n">
         <v>2</v>
@@ -12588,7 +17707,7 @@
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
     </row>
-    <row r="136">
+    <row r="136" ht="60" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
           <t>Mid Standard II Shorts</t>
@@ -12620,7 +17739,9 @@
         <v>1000</v>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
+      <c r="J136" t="n">
+        <v>65</v>
+      </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="n">
         <v>2</v>
@@ -12657,7 +17778,7 @@
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
     </row>
-    <row r="137">
+    <row r="137" ht="60" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
           <t>Mimic Silver II Pant</t>
@@ -12742,7 +17863,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="60" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
           <t>ROC Lite Slim II Pant</t>
@@ -12774,7 +17895,9 @@
         <v>1400</v>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>65</v>
+      </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
         <v>2</v>
@@ -12823,7 +17946,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="60" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
           <t>Solis Zip Off Pant</t>
@@ -12859,7 +17982,9 @@
         <v>2200</v>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>65</v>
+      </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="n">
         <v>4</v>
@@ -12916,7 +18041,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="60" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
           <t>Solvik Seersucker Shorts</t>
@@ -12948,7 +18073,9 @@
         <v>1000</v>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>65</v>
+      </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="n">
         <v>2</v>
@@ -13001,7 +18128,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="60" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
           <t>Sun Capsule Pant</t>
@@ -13033,7 +18160,9 @@
         <v>2400</v>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>65.3</v>
+      </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="n">
         <v>1</v>
@@ -13070,7 +18199,7 @@
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
     </row>
-    <row r="142">
+    <row r="142" ht="60" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
           <t>Brisen Tech Mid Hood</t>
@@ -13106,7 +18235,9 @@
         <v>1800</v>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>58</v>
+      </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="n">
         <v>4</v>
@@ -13163,7 +18294,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="60" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
           <t>Buteo Mid II Jacket</t>
@@ -13199,7 +18330,9 @@
         <v>900</v>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>65</v>
+      </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="n">
         <v>4</v>
@@ -13256,7 +18389,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="60" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
           <t>Funäs Pile Hood</t>
@@ -13341,7 +18474,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="60" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
           <t>Haglöfs Hoodie</t>
@@ -13377,7 +18510,9 @@
         <v>1500</v>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>58</v>
+      </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="n">
         <v>4</v>
@@ -13434,7 +18569,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="60" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
           <t>Korp Mid Halfzip</t>
@@ -13470,7 +18605,9 @@
         <v>800</v>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>62</v>
+      </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="n">
         <v>4</v>
@@ -13527,7 +18664,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="60" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
           <t>Korp Mid Hood</t>
@@ -13563,7 +18700,9 @@
         <v>1000</v>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>60</v>
+      </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
         <v>4</v>
@@ -13620,7 +18759,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="60" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
           <t>Korp Mid Jacket</t>
@@ -13656,7 +18795,9 @@
         <v>900</v>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>62</v>
+      </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="n">
         <v>4</v>
@@ -13713,7 +18854,7 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="60" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
           <t>L.I.M Mid Hybrid</t>
@@ -13745,7 +18886,9 @@
         <v>1500</v>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="J149" t="n">
+        <v>62.9</v>
+      </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="n">
         <v>2</v>
@@ -13798,7 +18941,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="60" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
           <t>L.I.M Mid Multi II Hood</t>
@@ -13834,7 +18977,9 @@
         <v>1200</v>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="J150" t="n">
+        <v>60</v>
+      </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="n">
         <v>4</v>
@@ -13891,7 +19036,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="60" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
           <t>L.I.M Mid Multi Jacket</t>
@@ -13923,7 +19068,9 @@
         <v>1100</v>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="J151" t="n">
+        <v>60</v>
+      </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="n">
         <v>2</v>
@@ -13976,7 +19123,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="60" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
           <t>L.I.M Mid Reversible Crew</t>
@@ -14008,7 +19155,9 @@
         <v>1200</v>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="J152" t="n">
+        <v>62.9</v>
+      </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="n">
         <v>2</v>
@@ -14061,7 +19210,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="60" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
           <t>Nallo Touring Hybrid Mid</t>
@@ -14097,7 +19246,9 @@
         <v>2200</v>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
+      <c r="J153" t="n">
+        <v>60</v>
+      </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="n">
         <v>4</v>
@@ -14154,7 +19305,7 @@
         <v>37.3</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="60" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
           <t>Rosson II Tights</t>
@@ -14239,7 +19390,7 @@
         <v>56.6</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="60" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
           <t>Rosson Mid II Hood</t>
@@ -14275,7 +19426,9 @@
         <v>1400</v>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+      <c r="J155" t="n">
+        <v>64</v>
+      </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="n">
         <v>4</v>
@@ -14332,7 +19485,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="60" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
           <t>Rosson Mid II Jacket</t>
@@ -14368,7 +19521,9 @@
         <v>1200</v>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+      <c r="J156" t="n">
+        <v>64</v>
+      </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="n">
         <v>4</v>
@@ -14425,7 +19580,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" ht="60" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
           <t>Swook II Mid Hood</t>
@@ -14461,7 +19616,9 @@
         <v>1700</v>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+      <c r="J157" t="n">
+        <v>60</v>
+      </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="n">
         <v>4</v>
@@ -14518,7 +19675,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="60" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
           <t>Swook II Mid Jacket</t>
@@ -14554,7 +19711,9 @@
         <v>1500</v>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+      <c r="J158" t="n">
+        <v>60</v>
+      </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="n">
         <v>4</v>
@@ -14611,7 +19770,7 @@
         <v>53.7</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="60" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
           <t>Swook Mid Halfzip W</t>
@@ -14651,7 +19810,9 @@
         <v>1400</v>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+      <c r="J159" t="n">
+        <v>65</v>
+      </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="n">
         <v>2</v>
@@ -14708,7 +19869,7 @@
         <v>36.8</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="60" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
           <t>Swook Mid Sweater M</t>
@@ -14748,7 +19909,9 @@
         <v>1200</v>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+      <c r="J160" t="n">
+        <v>64</v>
+      </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="n">
         <v>2</v>
@@ -14805,7 +19968,7 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" ht="60" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
           <t>Vara Alpha Sweater</t>
@@ -14841,7 +20004,9 @@
         <v>1500</v>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+      <c r="J161" t="n">
+        <v>55</v>
+      </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
         <v>4</v>
@@ -14898,7 +20063,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="60" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
           <t>Vassi Mid Hood</t>
@@ -14983,7 +20148,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" ht="60" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
           <t>Latnja 18L</t>
@@ -15068,7 +20233,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="60" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
           <t>Nallo Pro 40L</t>
@@ -15153,7 +20318,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="60" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
           <t>Vassi Pro 32L</t>
@@ -15238,7 +20403,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="60" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
           <t>Alert GTX II Jacket</t>
@@ -15274,7 +20439,9 @@
         <v>3800</v>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+      <c r="J166" t="n">
+        <v>58</v>
+      </c>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="n">
         <v>4</v>
@@ -15327,7 +20494,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" ht="60" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
           <t>Alper Proof Jacket</t>
@@ -15412,7 +20579,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="60" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
           <t>Alper Proof Pant</t>
@@ -15497,7 +20664,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="60" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
           <t>Astral GTX II Jacket</t>
@@ -15533,7 +20700,9 @@
         <v>4500</v>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+      <c r="J169" t="n">
+        <v>61.5</v>
+      </c>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="n">
         <v>4</v>
@@ -15590,7 +20759,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="60" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
           <t>Breeze Proof Jacket</t>
@@ -15626,7 +20795,9 @@
         <v>2000</v>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
+      <c r="J170" t="n">
+        <v>60</v>
+      </c>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="n">
         <v>4</v>
@@ -15683,7 +20854,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="60" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
           <t>Front Proof II Jacket</t>
@@ -15719,7 +20890,9 @@
         <v>3300</v>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
+      <c r="J171" t="n">
+        <v>60</v>
+      </c>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="n">
         <v>4</v>
@@ -15776,7 +20949,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="60" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
           <t>Holm GTX II Pant</t>
@@ -15812,7 +20985,9 @@
         <v>2800</v>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
+      <c r="J172" t="n">
+        <v>55</v>
+      </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="n">
         <v>6</v>
@@ -15869,7 +21044,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="60" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
           <t>Klyva GTX II Jacket</t>
@@ -15905,7 +21080,9 @@
         <v>3500</v>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
+      <c r="J173" t="n">
+        <v>59.2</v>
+      </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="n">
         <v>6</v>
@@ -15958,7 +21135,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="60" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
           <t>Korp Proof II Pant</t>
@@ -15994,7 +21171,9 @@
         <v>1300</v>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+      <c r="J174" t="n">
+        <v>58</v>
+      </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="n">
         <v>4</v>
@@ -16051,7 +21230,7 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="60" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
           <t>Korp Proof Jacket</t>
@@ -16087,7 +21266,9 @@
         <v>1800</v>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
+      <c r="J175" t="n">
+        <v>64</v>
+      </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="n">
         <v>4</v>
@@ -16144,7 +21325,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="60" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
           <t>L.I.M Airak 2,5L Jacket</t>
@@ -16229,7 +21410,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="60" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
           <t>L.I.M Airak 2,5L Pant</t>
@@ -16314,7 +21495,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="60" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
           <t>L.I.M Airak 2,5L Proof II Jacket</t>
@@ -16346,7 +21527,9 @@
         <v>2500</v>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
+      <c r="J178" t="n">
+        <v>58</v>
+      </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="n">
         <v>2</v>
@@ -16399,7 +21582,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" ht="60" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
           <t>L.I.M Airak 2,5L Proof II Pant</t>
@@ -16431,7 +21614,9 @@
         <v>2000</v>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
+      <c r="J179" t="n">
+        <v>59</v>
+      </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="n">
         <v>2</v>
@@ -16484,7 +21669,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" ht="60" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
           <t>L.I.M Airak GTX Jacket</t>
@@ -16569,7 +21754,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="60" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
           <t>L.I.M GTX III Jacket</t>
@@ -16605,7 +21790,9 @@
         <v>3300</v>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
+      <c r="J181" t="n">
+        <v>59.2</v>
+      </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="n">
         <v>4</v>
@@ -16662,7 +21849,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="60" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
           <t>L.I.M GTX III Pant</t>
@@ -16694,7 +21881,9 @@
         <v>2800</v>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
+      <c r="J182" t="n">
+        <v>49</v>
+      </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="n">
         <v>2</v>
@@ -16731,7 +21920,7 @@
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr"/>
     </row>
-    <row r="183">
+    <row r="183" ht="60" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
           <t>L.I.M Light Proof Jacket</t>
@@ -16763,7 +21952,9 @@
         <v>3700</v>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="J183" t="n">
+        <v>50</v>
+      </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="n">
         <v>2</v>
@@ -16816,7 +22007,7 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" ht="60" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
           <t>L.I.M Windpack Hood Jacket</t>
@@ -16848,7 +22039,9 @@
         <v>2000</v>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+      <c r="J184" t="n">
+        <v>50</v>
+      </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="n">
         <v>2</v>
@@ -16901,7 +22094,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="60" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
           <t>Latnja GTX Insulated II Jacket</t>
@@ -16986,7 +22179,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="60" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
           <t>Latnja GTX Insulated II Pant</t>
@@ -17071,7 +22264,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="60" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
           <t>Ljusna Proof Parka</t>
@@ -17107,7 +22300,9 @@
         <v>3000</v>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
+      <c r="J187" t="n">
+        <v>58</v>
+      </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="n">
         <v>4</v>
@@ -17164,7 +22359,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" ht="60" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
           <t>Nallo Touring GTX Jacket</t>
@@ -17249,7 +22444,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" ht="60" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
           <t>Nallo Touring GTX Pant</t>
@@ -17334,7 +22529,7 @@
         <v>37.2</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" ht="60" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
           <t>Norrvind Shield Hood</t>
@@ -17370,7 +22565,9 @@
         <v>1300</v>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+      <c r="J190" t="n">
+        <v>60</v>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="n">
         <v>4</v>
@@ -17427,7 +22624,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" ht="60" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
           <t>Ozka Proof Jacket</t>
@@ -17463,7 +22660,9 @@
         <v>3000</v>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+      <c r="J191" t="n">
+        <v>57</v>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="n">
         <v>4</v>
@@ -17520,7 +22719,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" ht="60" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
           <t>Ozka Proof Pant</t>
@@ -17556,7 +22755,9 @@
         <v>2200</v>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
+      <c r="J192" t="n">
+        <v>58</v>
+      </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="n">
         <v>4</v>
@@ -17613,7 +22814,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" ht="60" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
           <t>ROC Sight GTX Jacket</t>
@@ -17649,7 +22850,9 @@
         <v>5000</v>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
+      <c r="J193" t="n">
+        <v>55</v>
+      </c>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="n">
         <v>4</v>
@@ -17706,7 +22909,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" ht="60" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
           <t>Saulo Proof Jacket</t>
@@ -17791,7 +22994,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="60" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
           <t>Saulo Proof Pant</t>
@@ -17876,7 +23079,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" ht="60" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
           <t>Skalvik Softshell Parka</t>
@@ -17912,7 +23115,9 @@
         <v>3500</v>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
+      <c r="J196" t="n">
+        <v>58</v>
+      </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="n">
         <v>4</v>
@@ -17969,7 +23174,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" ht="60" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
           <t>Spitz GTX Pro II Jacket</t>
@@ -18005,7 +23210,9 @@
         <v>7500</v>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
+      <c r="J197" t="n">
+        <v>55</v>
+      </c>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="n">
         <v>4</v>
@@ -18062,7 +23269,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" ht="60" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
           <t>Tarre Proof Insulated Jacket</t>
@@ -18147,7 +23354,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" ht="60" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
           <t>Tarre Proof Insulated Pant</t>
@@ -18232,7 +23439,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" ht="60" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
           <t>Vara Down GTX Parka</t>
@@ -18317,7 +23524,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" ht="60" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
           <t>Vassi GTX II Jacket</t>
@@ -18402,7 +23609,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" ht="60" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
           <t>Vassi GTX II Pant</t>
@@ -18487,7 +23694,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" ht="60" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
           <t>Vassi GTX Pro II Bib</t>
@@ -18572,7 +23779,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" ht="60" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
           <t>Vassi GTX Pro II Jacket</t>
@@ -18657,7 +23864,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" ht="60" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
           <t>Yra Mimic Proof Parka</t>
@@ -18742,7 +23949,7 @@
         <v>53.7</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" ht="60" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
           <t>Moonlite</t>
@@ -18782,7 +23989,9 @@
         <v>1300</v>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
+      <c r="J206" t="n">
+        <v>57.9</v>
+      </c>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="n">
         <v>2</v>
@@ -18839,7 +24048,7 @@
         <v>34.3</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" ht="60" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
           <t>Moonlite +7</t>
@@ -18875,7 +24084,9 @@
         <v>1300</v>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
+      <c r="J207" t="n">
+        <v>50.8</v>
+      </c>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="n">
         <v>2</v>
@@ -18932,7 +24143,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" ht="60" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
           <t>Moonlite -1</t>
@@ -18968,7 +24179,9 @@
         <v>1500</v>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
+      <c r="J208" t="n">
+        <v>53.7</v>
+      </c>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="n">
         <v>2</v>
@@ -19025,7 +24238,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" ht="60" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
           <t>Musca -1</t>
@@ -19061,7 +24274,9 @@
         <v>1500</v>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
+      <c r="J209" t="n">
+        <v>53.5</v>
+      </c>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="n">
         <v>2</v>
@@ -19118,7 +24333,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" ht="60" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
           <t>Musca -13</t>
@@ -19154,7 +24369,9 @@
         <v>1800</v>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
+      <c r="J210" t="n">
+        <v>55.6</v>
+      </c>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="n">
         <v>2</v>
@@ -19211,7 +24428,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" ht="60" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
           <t>Musca -26</t>
@@ -19247,7 +24464,9 @@
         <v>2200</v>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
+      <c r="J211" t="n">
+        <v>55</v>
+      </c>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="n">
         <v>2</v>
@@ -19304,7 +24523,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" ht="60" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
           <t>Musca -5</t>
@@ -19340,7 +24559,9 @@
         <v>1700</v>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
+      <c r="J212" t="n">
+        <v>54.4</v>
+      </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="n">
         <v>2</v>
@@ -19397,7 +24618,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" ht="60" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
           <t>Tarius +1</t>
@@ -19433,7 +24654,9 @@
         <v>1600</v>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
+      <c r="J213" t="n">
+        <v>55.6</v>
+      </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="n">
         <v>2</v>
@@ -19490,7 +24713,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" ht="60" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
           <t>Tarius +6</t>
@@ -19575,7 +24798,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" ht="60" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
           <t>Tarius -18</t>
@@ -19611,7 +24834,9 @@
         <v>2200</v>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
+      <c r="J215" t="n">
+        <v>53.9</v>
+      </c>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="n">
         <v>2</v>
@@ -19668,7 +24893,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" ht="60" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
           <t>Tarius -5</t>
@@ -19704,7 +24929,9 @@
         <v>1800</v>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
+      <c r="J216" t="n">
+        <v>56.8</v>
+      </c>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="n">
         <v>2</v>
@@ -19761,7 +24988,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" ht="60" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
           <t>Tarius Lite +8</t>
@@ -19797,7 +25024,9 @@
         <v>1200</v>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
+      <c r="J217" t="n">
+        <v>56.4</v>
+      </c>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="n">
         <v>2</v>
@@ -19854,7 +25083,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" ht="60" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
           <t>Korp Softshell Hood</t>
@@ -19890,7 +25119,9 @@
         <v>1800</v>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
+      <c r="J218" t="n">
+        <v>62</v>
+      </c>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="n">
         <v>4</v>
@@ -19947,7 +25178,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" ht="60" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
           <t>Korp Softshell Pant</t>
@@ -19983,7 +25214,9 @@
         <v>1400</v>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
+      <c r="J219" t="n">
+        <v>65</v>
+      </c>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="n">
         <v>4</v>
@@ -20040,7 +25273,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" ht="60" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
           <t>ROC Sight Softshell II Jacket</t>
@@ -20076,7 +25309,9 @@
         <v>3200</v>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
+      <c r="J220" t="n">
+        <v>60</v>
+      </c>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="n">
         <v>4</v>
@@ -20133,7 +25368,7 @@
         <v>42.4</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" ht="60" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
           <t>ROC Sight Softshell II Pant</t>
@@ -20169,7 +25404,9 @@
         <v>2800</v>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
+      <c r="J221" t="n">
+        <v>61</v>
+      </c>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="n">
         <v>4</v>
@@ -20226,7 +25463,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" ht="60" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
           <t>Warm Flex Pant</t>
@@ -20311,7 +25548,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" ht="60" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
           <t>Haglöfs LS Tee</t>
@@ -20347,7 +25584,9 @@
         <v>800</v>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
+      <c r="J223" t="n">
+        <v>61.1</v>
+      </c>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="n">
         <v>4</v>
@@ -20404,7 +25643,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" ht="60" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
           <t>Haglöfs Tee</t>
@@ -20440,7 +25679,9 @@
         <v>700</v>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
+      <c r="J224" t="n">
+        <v>60</v>
+      </c>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="n">
         <v>4</v>
@@ -20497,7 +25738,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" ht="60" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
           <t>Kaise Wool II LS Tee</t>
@@ -20529,7 +25770,9 @@
         <v>1000</v>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
+      <c r="J225" t="n">
+        <v>61</v>
+      </c>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="n">
         <v>2</v>
@@ -20582,7 +25825,7 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" ht="60" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
           <t>Kaise Wool II Tee</t>
@@ -20614,7 +25857,9 @@
         <v>900</v>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
+      <c r="J226" t="n">
+        <v>61</v>
+      </c>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="n">
         <v>2</v>
@@ -20667,7 +25912,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" ht="60" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
           <t>Kaise Wool Tank Top</t>
@@ -20703,7 +25948,9 @@
         <v>750</v>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
+      <c r="J227" t="n">
+        <v>62</v>
+      </c>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="n">
         <v>1</v>
@@ -20756,7 +26003,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" ht="60" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
           <t>L.I.M Delta Crop Tee</t>
@@ -20792,7 +26039,9 @@
         <v>700</v>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
+      <c r="J228" t="n">
+        <v>63</v>
+      </c>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="n">
         <v>1</v>
@@ -20845,7 +26094,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" ht="60" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
           <t>L.I.M Delta Tee</t>
@@ -20881,7 +26130,9 @@
         <v>700</v>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
+      <c r="J229" t="n">
+        <v>61</v>
+      </c>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="n">
         <v>1</v>
@@ -20934,7 +26185,7 @@
         <v>46.2</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="60" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
           <t>L.I.M Light T-Shirt</t>
@@ -20966,7 +26217,9 @@
         <v>1200</v>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
+      <c r="J230" t="n">
+        <v>50</v>
+      </c>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="n">
         <v>2</v>
@@ -21019,7 +26272,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" ht="60" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
           <t>L.I.M Ridge Tank</t>
@@ -21055,7 +26308,9 @@
         <v>450</v>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
+      <c r="J231" t="n">
+        <v>60</v>
+      </c>
       <c r="K231" t="inlineStr">
         <is>
           <t>Special edition: Blueberry</t>
@@ -21112,7 +26367,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" ht="60" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
           <t>L.I.M Ridge Tee</t>
@@ -21144,7 +26399,9 @@
         <v>500</v>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
+      <c r="J232" t="n">
+        <v>61</v>
+      </c>
       <c r="K232" t="inlineStr">
         <is>
           <t>Special edition: Blueberry</t>
@@ -21201,7 +26458,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" ht="60" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
           <t>L.I.M Sunpack Hoodie</t>
@@ -21233,7 +26490,9 @@
         <v>1500</v>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
+      <c r="J233" t="n">
+        <v>58</v>
+      </c>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="n">
         <v>2</v>
@@ -21286,7 +26545,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" ht="60" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
           <t>Outsiders Graphic Tee</t>
@@ -21322,7 +26581,9 @@
         <v>450</v>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
+      <c r="J234" t="n">
+        <v>62</v>
+      </c>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="n">
         <v>4</v>
@@ -21379,7 +26640,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="60" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
           <t>Outsiders Tee</t>
@@ -21415,7 +26676,9 @@
         <v>400</v>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
+      <c r="J235" t="n">
+        <v>61.1</v>
+      </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="n">
         <v>4</v>
@@ -21472,7 +26735,7 @@
         <v>32.3</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="60" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
           <t>Ridge Hike Tee</t>
@@ -21508,7 +26771,9 @@
         <v>600</v>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
+      <c r="J236" t="n">
+        <v>64.59999999999999</v>
+      </c>
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="n">
         <v>1</v>
@@ -21561,7 +26826,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" ht="60" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
           <t>Ridge II LS Tee</t>
@@ -21593,7 +26858,9 @@
         <v>800</v>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
+      <c r="J237" t="n">
+        <v>62</v>
+      </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="n">
         <v>2</v>
@@ -21646,7 +26913,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" ht="60" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
           <t>Ridge II Tee</t>
@@ -21678,7 +26945,9 @@
         <v>700</v>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
+      <c r="J238" t="n">
+        <v>62</v>
+      </c>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="n">
         <v>2</v>
@@ -21731,7 +27000,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" ht="60" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
           <t>Salo Dress</t>
@@ -21767,7 +27036,9 @@
         <v>1200</v>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
+      <c r="J239" t="n">
+        <v>57</v>
+      </c>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="n">
         <v>1</v>
@@ -21820,7 +27091,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" ht="60" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
           <t>Salo Shirt II</t>
@@ -21852,7 +27123,9 @@
         <v>1000</v>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
+      <c r="J240" t="n">
+        <v>60</v>
+      </c>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="n">
         <v>2</v>
@@ -21905,7 +27178,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" ht="60" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
           <t>Salo Shirt SS II</t>
@@ -21941,7 +27214,9 @@
         <v>900</v>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
+      <c r="J241" t="n">
+        <v>60</v>
+      </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="n">
         <v>1</v>
@@ -21994,7 +27269,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" ht="60" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
           <t>Selme LS Crewneck</t>
@@ -22030,7 +27305,9 @@
         <v>1200</v>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
+      <c r="J242" t="n">
+        <v>56</v>
+      </c>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="n">
         <v>4</v>
@@ -22087,7 +27364,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" ht="60" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
           <t>Solvik Seersucker SS Shirt</t>
@@ -22119,7 +27396,9 @@
         <v>1100</v>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
+      <c r="J243" t="n">
+        <v>58.4</v>
+      </c>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="n">
         <v>2</v>
@@ -22172,7 +27451,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" ht="60" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
           <t>Sun Capsule Halfzip</t>
@@ -22204,7 +27483,9 @@
         <v>2700</v>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
+      <c r="J244" t="n">
+        <v>62.5</v>
+      </c>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="n">
         <v>1</v>
@@ -22241,7 +27522,7 @@
       <c r="X244" t="inlineStr"/>
       <c r="Y244" t="inlineStr"/>
     </row>
-    <row r="245">
+    <row r="245" ht="60" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
           <t>Trekk Tech II LS Tee</t>
@@ -22273,7 +27554,9 @@
         <v>700</v>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
+      <c r="J245" t="n">
+        <v>62</v>
+      </c>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="n">
         <v>2</v>
@@ -22326,7 +27609,7 @@
         <v>60.8</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" ht="60" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
           <t>Trekk Tech II Tee</t>
@@ -22358,7 +27641,9 @@
         <v>500</v>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
+      <c r="J246" t="n">
+        <v>62</v>
+      </c>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="n">
         <v>2</v>
@@ -22411,7 +27696,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" ht="60" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon GTX Low</t>
@@ -22447,7 +27732,9 @@
         <v>2200</v>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="n">
         <v>4</v>
@@ -22504,7 +27791,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" ht="60" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon GTX Mid</t>
@@ -22540,7 +27827,9 @@
         <v>2300</v>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
+      <c r="J248" t="n">
+        <v>56</v>
+      </c>
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="n">
         <v>4</v>
@@ -22597,7 +27886,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" ht="60" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon Low</t>
@@ -22633,7 +27922,9 @@
         <v>1800</v>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="n">
         <v>4</v>
@@ -22690,7 +27981,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" ht="60" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
           <t>L.I.M Light Low</t>
@@ -22722,7 +28013,9 @@
         <v>2200</v>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
+      <c r="J250" t="n">
+        <v>60</v>
+      </c>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="n">
         <v>2</v>
@@ -22775,7 +28068,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" ht="60" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
           <t>L.I.M Ultralight GTX Low</t>
@@ -22807,7 +28100,9 @@
         <v>2700</v>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
+      <c r="J251" t="n">
+        <v>57.3</v>
+      </c>
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="n">
         <v>2</v>
@@ -22860,7 +28155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" ht="60" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
           <t>L.I.M Ultralight Low</t>
@@ -22892,7 +28187,9 @@
         <v>2400</v>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
+      <c r="J252" t="n">
+        <v>56.7</v>
+      </c>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="n">
         <v>2</v>
@@ -22945,7 +28242,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" ht="60" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
           <t>Oxo 60 W</t>
@@ -22981,7 +28278,9 @@
         <v>3200</v>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="n">
         <v>2</v>
@@ -23038,7 +28337,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" ht="60" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
           <t>Oxo 80</t>
@@ -23074,7 +28373,9 @@
         <v>3500</v>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="n">
         <v>2</v>
@@ -23131,7 +28432,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" ht="60" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
           <t>Haglöfs Incline GTX Mid</t>
@@ -23167,7 +28468,9 @@
         <v>3000</v>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="n">
         <v>2</v>
@@ -23224,7 +28527,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" ht="60" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
           <t>Haglöfs Incline Pro GTX High</t>
@@ -23260,7 +28563,9 @@
         <v>3800</v>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
+      <c r="J256" t="n">
+        <v>48</v>
+      </c>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="n">
         <v>2</v>
@@ -23317,7 +28622,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" ht="60" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
           <t>Haglöfs Scand GTX Mid</t>
@@ -23398,7 +28703,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" ht="60" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
           <t>Haglöfs Solid Pro 2 GTX Mid</t>
@@ -23434,7 +28739,9 @@
         <v>3500</v>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="n">
         <v>2</v>
@@ -23487,7 +28794,7 @@
         <v>57.2</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" ht="60" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
           <t>Haglöfs Solid Pro 2 WL GTX Mid</t>
@@ -23573,8 +28880,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y259"/>
+  <autoFilter ref="A1:Z259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23584,7 +28892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23647,89 +28955,101 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NOT available in the FW27/SS28 source files -- only Target RRP exists. Left blank. See RR-008.</t>
+          <t>Target GM0% from the SS28 'Pic Centric' workbook -- the FW27/SS28 range files themselves have no margin field (RR-008). SS28-only for now; blank for franchises with no SS28 code until an equivalent FW27 file arrives.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Core Assortment FW27</t>
+          <t>Product Image</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Yes/No, from the flag already in the SS26 tiering workbook (57/1,860 Base+Gender rows = 'Yes'), rolled up to Base grain (Yes if either gender was Yes).</t>
+          <t>The franchise's representative SS28 colorway photo, from the same Pic Centric workbook. Blank for FW27-only franchises (pending an FW27 image source) and for the small number of SS28 codes with no photo anchored in that file. CAVEAT: these are floating images anchored to a fixed row position, not tied to the row's data -- using Excel's Sort feature (not its Filter arrows, which is safe) can detach an image from its franchise. Re-run build_franchise_list.py for a clean, re-aligned copy rather than fixing it by hand.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Core Assortment SS28</t>
+          <t>Core Assortment FW27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>No source yet -- the flag was only ever defined for FW27. Left as 'To confirm' for every row until Tobias/Isabelle define it for SS28.</t>
+          <t>Yes/No, from the flag already in the SS26 tiering workbook (57/1,860 Base+Gender rows = 'Yes'), rolled up to Base grain (Yes if either gender was Yes).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t># active colors</t>
+          <t>Core Assortment SS28</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sum of active colorways (the colorway-level Active flag, not just a row listed in the sheet) across every style rolled into this franchise -- both genders, both seasons. A colorway still in the file but not Active this season (e.g. a discontinued or carried-forward-for-reference color) is not counted. CAVEAT: 88/616 main-range style rows (incl. 18 Shell styles) have NO colorway sub-rows at all in this export -- showing 0 here, which may be a real single-color item or a data gap in the export. Worth confirming with Tobias before treating 0 as fact.</t>
+          <t>No source yet -- the flag was only ever defined for FW27. Left as 'To confirm' for every row until Tobias/Isabelle define it for SS28.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t># active colors</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Yes if an ABS or ABS Exclusive variant of this franchise exists anywhere in FW27/SS28 (even though RR-006 keeps those styles out of the main range count above) -- so a reviewer knows one exists before deciding the franchise's main-range fate.</t>
+          <t>Sum of active colorways (the colorway-level Active flag, not just a row listed in the sheet) across every style rolled into this franchise -- both genders, both seasons. A colorway still in the file but not Active this season (e.g. a discontinued or carried-forward-for-reference color) is not counted. CAVEAT: 88/616 main-range style rows (incl. 18 Shell styles) have NO colorway sub-rows at all in this export -- showing 0 here, which may be a real single-color item or a data gap in the export. Worth confirming with Tobias before treating 0 as fact.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Asia Fit</t>
+          <t>ABS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Yes if an 'AF'-suffixed (Asian Fit) variant of this franchise exists anywhere in FW27/SS28 (RR-007) -- always also ABS=Yes, since every AF style is tagged ABS Exclusive in the source data.</t>
+          <t>Yes if an ABS or ABS Exclusive variant of this franchise exists anywhere in FW27/SS28 (even though RR-006 keeps those styles out of the main range count above) -- so a reviewer knows one exists before deciding the franchise's main-range fate.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Status FW27 / Status SS28</t>
+          <t>Asia Fit</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Carry Over / New / Update, from the forecast files' Status field -- shown per season since a franchise can differ between them (e.g. New in FW27, Carry Over in SS28). Blank if no forecast row matched that season (see RR-014).</t>
+          <t>Yes if an 'AF'-suffixed (Asian Fit) variant of this franchise exists anywhere in FW27/SS28 (RR-007) -- always also ABS=Yes, since every AF style is tagged ABS Exclusive in the source data.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Status FW27 / Status SS28</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Carry Over / New / Update, from the forecast files' Status field -- shown per season since a franchise can differ between them (e.g. New in FW27, Carry Over in SS28). Blank if no forecast row matched that season (see RR-014).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Forecast Qty / GP% (total, DTC, Wholesale)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Summed across every style and season rolled into the franchise, from the two forecast files (RR-011/RR-012). Blank (not 0) when none of the franchise's styles have a forecast match -- 25/616 main-range style rows don't (RR-014). GP% blended vs. DTC/Wholesale split -- blended hides a real spread, so both are shown.</t>
         </is>

--- a/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
+++ b/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$Z$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Franchise Review List'!$A$1:$Y$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,4911 +138,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>30</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>44</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>48</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>50</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>54</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>55</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>56</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>57</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>58</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId45"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>61</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId46"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId47"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId48"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId49"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>66</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId50"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>67</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId51"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>68</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId52"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId53"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>70</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId54"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>71</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="55" name="Image 55" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId55"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>72</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="56" name="Image 56" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId56"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>73</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Image 57" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId57"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>74</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="58" name="Image 58" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId58"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>75</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="59" name="Image 59" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId59"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId60"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>77</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId61"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId62"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId63"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>80</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId64"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>83</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>85</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId68"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>87</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId69"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId70"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId71"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>90</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId72"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId73"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>95</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId74"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>96</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId75"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>98</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId76"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>99</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId77"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId78"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>103</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId79"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId80"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>107</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId81"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="82" name="Image 82" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId82"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="83" name="Image 83" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId83"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>116</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="84" name="Image 84" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId84"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>117</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId85"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId86"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>119</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId87"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>120</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId88"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>121</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId89"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>122</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId90"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>123</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="91" name="Image 91" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId91"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>124</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="92" name="Image 92" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId92"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>125</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="93" name="Image 93" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId93"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId94"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId95"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>128</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId96"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId97"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>130</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="98" name="Image 98" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId98"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>131</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="99" name="Image 99" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId99"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>132</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="100" name="Image 100" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId100"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="101" name="Image 101" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId101"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>134</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="102" name="Image 102" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId102"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>135</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="103" name="Image 103" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId103"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>137</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="104" name="Image 104" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId104"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>138</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="105" name="Image 105" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId105"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>139</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="106" name="Image 106" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId106"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>140</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="107" name="Image 107" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId107"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>141</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="108" name="Image 108" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId108"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>142</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="109" name="Image 109" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId109"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>144</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="110" name="Image 110" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId110"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>145</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="111" name="Image 111" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId111"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>146</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="112" name="Image 112" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId112"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>147</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="113" name="Image 113" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId113"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>148</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="114" name="Image 114" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId114"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>149</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="115" name="Image 115" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId115"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>150</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="116" name="Image 116" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId116"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="117" name="Image 117" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId117"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>152</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="118" name="Image 118" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId118"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>154</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="119" name="Image 119" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId119"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>155</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="120" name="Image 120" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId120"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>156</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="121" name="Image 121" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId121"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>157</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="122" name="Image 122" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId122"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>158</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="123" name="Image 123" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId123"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>159</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="124" name="Image 124" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId124"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>160</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="125" name="Image 125" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId125"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>165</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="126" name="Image 126" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId126"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>168</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="127" name="Image 127" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId127"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>169</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="128" name="Image 128" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId128"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>170</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="129" name="Image 129" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId129"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>171</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="130" name="Image 130" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId130"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>172</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="131" name="Image 131" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId131"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>173</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="132" name="Image 132" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId132"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>174</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="133" name="Image 133" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId133"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="134" name="Image 134" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId134"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>178</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="135" name="Image 135" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId135"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>180</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="136" name="Image 136" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId136"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>181</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="137" name="Image 137" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId137"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>182</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="138" name="Image 138" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId138"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="139" name="Image 139" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId139"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>186</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="140" name="Image 140" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId140"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>189</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="141" name="Image 141" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId141"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>190</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="142" name="Image 142" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId142"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>191</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="143" name="Image 143" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId143"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>192</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="144" name="Image 144" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId144"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="145" name="Image 145" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId145"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>196</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="146" name="Image 146" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId146"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>205</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="147" name="Image 147" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId147"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>206</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="148" name="Image 148" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId148"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>207</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="149" name="Image 149" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId149"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>208</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="150" name="Image 150" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId150"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>209</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="151" name="Image 151" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId151"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>210</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="152" name="Image 152" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId152"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>211</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="153" name="Image 153" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId153"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>212</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="154" name="Image 154" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId154"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>214</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="155" name="Image 155" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId155"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>215</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="156" name="Image 156" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId156"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>216</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="157" name="Image 157" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId157"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>217</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="158" name="Image 158" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId158"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>218</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="159" name="Image 159" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId159"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>219</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="160" name="Image 160" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId160"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>220</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="161" name="Image 161" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId161"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>222</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="162" name="Image 162" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId162"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>223</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="163" name="Image 163" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId163"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>224</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="164" name="Image 164" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId164"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>225</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="165" name="Image 165" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId165"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>226</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="166" name="Image 166" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId166"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>227</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="167" name="Image 167" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId167"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="168" name="Image 168" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId168"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>229</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="169" name="Image 169" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId169"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>230</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="170" name="Image 170" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId170"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>231</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="171" name="Image 171" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId171"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>232</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="172" name="Image 172" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId172"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>233</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="173" name="Image 173" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId173"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>234</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="174" name="Image 174" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId174"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>235</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="175" name="Image 175" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId175"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>236</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="176" name="Image 176" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId176"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>237</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="177" name="Image 177" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId177"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>238</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="178" name="Image 178" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId178"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>239</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="179" name="Image 179" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId179"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>240</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="180" name="Image 180" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId180"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="181" name="Image 181" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId181"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="182" name="Image 182" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId182"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>243</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="183" name="Image 183" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId183"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>244</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="184" name="Image 184" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId184"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>245</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="185" name="Image 185" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId185"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>246</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="186" name="Image 186" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId186"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="187" name="Image 187" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId187"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>248</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="188" name="Image 188" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId188"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>249</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="189" name="Image 189" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId189"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>250</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="190" name="Image 190" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId190"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="191" name="Image 191" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId191"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>252</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="192" name="Image 192" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId192"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="193" name="Image 193" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId193"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>254</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="194" name="Image 194" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId194"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="195" name="Image 195" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId195"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>257</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="476250" cy="714375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="196" name="Image 196" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId196"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5334,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z259"/>
+  <dimension ref="A1:Y259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5362,7 +457,6 @@
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="26" customWidth="1" min="24" max="24"/>
     <col width="26" customWidth="1" min="25" max="25"/>
-    <col width="8.571428571428571" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5491,13 +585,8 @@
           <t>Forecast GP% (Wholesale)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Product Image</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
+    </row>
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>Aresk Beanie</t>
@@ -5582,7 +671,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Aze II Beanie</t>
@@ -5667,7 +756,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>Brand Five Panel Cap</t>
@@ -5762,7 +851,7 @@
         <v>59.4</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>Haglöfs Bandana</t>
@@ -5853,7 +942,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>Haglöfs Cap</t>
@@ -5940,7 +1029,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>Haglöfs LX Hat</t>
@@ -6027,7 +1116,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>Haglöfs Neck Tube</t>
@@ -6114,7 +1203,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>Haglöfs Trucker Cap</t>
@@ -6201,7 +1290,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>L.I.M Pace Cap</t>
@@ -6292,7 +1381,7 @@
         <v>58.3</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>Mountain II Cap</t>
@@ -6377,7 +1466,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>Outsiders Beanie</t>
@@ -6462,7 +1551,7 @@
         <v>55.6</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>Rosson Beanie</t>
@@ -6547,7 +1636,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>Rosson II Balaclava</t>
@@ -6632,7 +1721,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>Solis Hat</t>
@@ -6719,7 +1808,7 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>Stretch Webbing Belt</t>
@@ -6814,7 +1903,7 @@
         <v>45.6</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>Sun Capsule Multi Cover</t>
@@ -6885,7 +1974,7 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>Thermal Beanie</t>
@@ -6970,7 +2059,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>Tova Wool Beanie</t>
@@ -7055,7 +2144,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>Vara Alpha Cap</t>
@@ -7140,7 +2229,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>Vassi Beanie</t>
@@ -7225,7 +2314,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>Vassi Headband</t>
@@ -7310,7 +2399,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>Flat accessory bag II</t>
@@ -7411,7 +2500,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>Fram 1L</t>
@@ -7506,7 +2595,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>Keywallet</t>
@@ -7593,7 +2682,7 @@
         <v>16.9</v>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>Lava travel tube</t>
@@ -7688,7 +2777,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>Magma Waist pack 3,5L</t>
@@ -7783,7 +2872,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
+    <row r="28">
       <c r="A28" t="inlineStr">
         <is>
           <t>Packing cube 12L</t>
@@ -7878,7 +2967,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>Packing cube 8L</t>
@@ -7973,7 +3062,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30">
       <c r="A30" t="inlineStr">
         <is>
           <t>Raincover 15-30L</t>
@@ -8064,7 +3153,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>Raincover 25-40L</t>
@@ -8155,7 +3244,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32">
       <c r="A32" t="inlineStr">
         <is>
           <t>Raincover 40-60L</t>
@@ -8246,7 +3335,7 @@
         <v>46.3</v>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>Raincover 60-80L</t>
@@ -8337,7 +3426,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
+    <row r="34">
       <c r="A34" t="inlineStr">
         <is>
           <t>Shoulder pocket</t>
@@ -8432,7 +3521,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35">
       <c r="A35" t="inlineStr">
         <is>
           <t>Shoulder pouch</t>
@@ -8527,7 +3616,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
+    <row r="36">
       <c r="A36" t="inlineStr">
         <is>
           <t>Sling pouch 2L</t>
@@ -8622,7 +3711,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
+    <row r="37">
       <c r="A37" t="inlineStr">
         <is>
           <t>Tight Pocket bag</t>
@@ -8721,7 +3810,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38">
       <c r="A38" t="inlineStr">
         <is>
           <t>Tight hip pack 1</t>
@@ -8816,7 +3905,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
+    <row r="39">
       <c r="A39" t="inlineStr">
         <is>
           <t>Tight hip pack 3,5</t>
@@ -8911,7 +4000,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
+    <row r="40">
       <c r="A40" t="inlineStr">
         <is>
           <t>Utility pouch 3L</t>
@@ -9006,7 +4095,7 @@
         <v>43.7</v>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
+    <row r="41">
       <c r="A41" t="inlineStr">
         <is>
           <t>Courier Messenger Bag</t>
@@ -9101,7 +4190,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42">
       <c r="A42" t="inlineStr">
         <is>
           <t>Fjatla 40</t>
@@ -9196,7 +4285,7 @@
         <v>53.6</v>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
+    <row r="43">
       <c r="A43" t="inlineStr">
         <is>
           <t>Fjatla 60</t>
@@ -9291,7 +4380,7 @@
         <v>57.7</v>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44">
       <c r="A44" t="inlineStr">
         <is>
           <t>Lava 110</t>
@@ -9386,7 +4475,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
+    <row r="45">
       <c r="A45" t="inlineStr">
         <is>
           <t>Lava 30</t>
@@ -9481,7 +4570,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
+    <row r="46">
       <c r="A46" t="inlineStr">
         <is>
           <t>Lava 50</t>
@@ -9576,7 +4665,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
+    <row r="47">
       <c r="A47" t="inlineStr">
         <is>
           <t>Lava 70</t>
@@ -9671,7 +4760,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
+    <row r="48">
       <c r="A48" t="inlineStr">
         <is>
           <t>Lava 90</t>
@@ -9766,7 +4855,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49">
       <c r="A49" t="inlineStr">
         <is>
           <t>Magma 42L</t>
@@ -9861,7 +4950,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
+    <row r="50">
       <c r="A50" t="inlineStr">
         <is>
           <t>Magma 65L</t>
@@ -9956,7 +5045,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
+    <row r="51">
       <c r="A51" t="inlineStr">
         <is>
           <t>Tight duffle 50</t>
@@ -10051,7 +5140,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
+    <row r="52">
       <c r="A52" t="inlineStr">
         <is>
           <t>Latnja Wool 3/4 Pant</t>
@@ -10136,7 +5225,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
+    <row r="53">
       <c r="A53" t="inlineStr">
         <is>
           <t>Latnja Wool Crew Neck</t>
@@ -10221,7 +5310,7 @@
         <v>16.1</v>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
+    <row r="54">
       <c r="A54" t="inlineStr">
         <is>
           <t>Latnja Wool Long John's</t>
@@ -10306,7 +5395,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
+    <row r="55">
       <c r="A55" t="inlineStr">
         <is>
           <t>Kobbe Sandal Low</t>
@@ -10393,7 +5482,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56">
       <c r="A56" t="inlineStr">
         <is>
           <t>Backup</t>
@@ -10488,7 +5577,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
+    <row r="57">
       <c r="A57" t="inlineStr">
         <is>
           <t>Corker Large</t>
@@ -10583,7 +5672,7 @@
         <v>40.3</v>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58">
       <c r="A58" t="inlineStr">
         <is>
           <t>Corker Medium</t>
@@ -10678,7 +5767,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
+    <row r="59">
       <c r="A59" t="inlineStr">
         <is>
           <t>Jarve Multi 22</t>
@@ -10773,7 +5862,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
+    <row r="60">
       <c r="A60" t="inlineStr">
         <is>
           <t>Jarve Multi 28</t>
@@ -10868,7 +5957,7 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
+    <row r="61">
       <c r="A61" t="inlineStr">
         <is>
           <t>Skuta 15</t>
@@ -10963,7 +6052,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
+    <row r="62">
       <c r="A62" t="inlineStr">
         <is>
           <t>Tight 15</t>
@@ -11062,7 +6151,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
+    <row r="63">
       <c r="A63" t="inlineStr">
         <is>
           <t>Tight 8</t>
@@ -11161,7 +6250,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
+    <row r="64">
       <c r="A64" t="inlineStr">
         <is>
           <t>Tight Large</t>
@@ -11256,7 +6345,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
+    <row r="65">
       <c r="A65" t="inlineStr">
         <is>
           <t>Tight Medium</t>
@@ -11355,7 +6444,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
+    <row r="66">
       <c r="A66" t="inlineStr">
         <is>
           <t>Tight Pro Large</t>
@@ -11450,7 +6539,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
+    <row r="67">
       <c r="A67" t="inlineStr">
         <is>
           <t>Tight Pro Medium</t>
@@ -11545,7 +6634,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
+    <row r="68">
       <c r="A68" t="inlineStr">
         <is>
           <t>Tight Small</t>
@@ -11640,7 +6729,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
+    <row r="69">
       <c r="A69" t="inlineStr">
         <is>
           <t>Tight Tote 25</t>
@@ -11735,7 +6824,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
+    <row r="70">
       <c r="A70" t="inlineStr">
         <is>
           <t>Tight X-Small</t>
@@ -11830,7 +6919,7 @@
         <v>45.1</v>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
+    <row r="71">
       <c r="A71" t="inlineStr">
         <is>
           <t>Vara 20L</t>
@@ -11925,7 +7014,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
+    <row r="72">
       <c r="A72" t="inlineStr">
         <is>
           <t>L.I.M Mountain Trail 25</t>
@@ -12020,7 +7109,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
+    <row r="73">
       <c r="A73" t="inlineStr">
         <is>
           <t>L.I.M Trail 15</t>
@@ -12115,7 +7204,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
+    <row r="74">
       <c r="A74" t="inlineStr">
         <is>
           <t>Magma 30</t>
@@ -12210,7 +7299,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
+    <row r="75">
       <c r="A75" t="inlineStr">
         <is>
           <t>Magma 50L</t>
@@ -12305,7 +7394,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
+    <row r="76">
       <c r="A76" t="inlineStr">
         <is>
           <t>Magma 60L</t>
@@ -12400,7 +7489,7 @@
         <v>45.6</v>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
+    <row r="77">
       <c r="A77" t="inlineStr">
         <is>
           <t>Magma Roll-top 40 WR</t>
@@ -12495,7 +7584,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
+    <row r="78">
       <c r="A78" t="inlineStr">
         <is>
           <t>Vide 20</t>
@@ -12590,7 +7679,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
+    <row r="79">
       <c r="A79" t="inlineStr">
         <is>
           <t>Vide 30</t>
@@ -12685,7 +7774,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
+    <row r="80">
       <c r="A80" t="inlineStr">
         <is>
           <t>Fast Hike Low</t>
@@ -12780,7 +7869,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
+    <row r="81">
       <c r="A81" t="inlineStr">
         <is>
           <t>Haglöfs Fast Hike PROOF Low</t>
@@ -12875,7 +7964,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
+    <row r="82">
       <c r="A82" t="inlineStr">
         <is>
           <t>Haglöfs Horizon Hike GTX WL Mid</t>
@@ -12960,7 +8049,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
+    <row r="83">
       <c r="A83" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon Hike GTX Low</t>
@@ -13055,7 +8144,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
+    <row r="84">
       <c r="A84" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon Hike GTX Mid</t>
@@ -13150,7 +8239,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
+    <row r="85">
       <c r="A85" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon Hike Light Mid</t>
@@ -13235,7 +8324,7 @@
         <v>35.3</v>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
+    <row r="86">
       <c r="A86" t="inlineStr">
         <is>
           <t>Haglöfs Ridge GTX II Low</t>
@@ -13330,7 +8419,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
+    <row r="87">
       <c r="A87" t="inlineStr">
         <is>
           <t>Haglöfs Ridge GTX II Mid</t>
@@ -13425,7 +8514,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
+    <row r="88">
       <c r="A88" t="inlineStr">
         <is>
           <t>Haglöfs Rosson FG Proof Mid</t>
@@ -13520,7 +8609,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
+    <row r="89">
       <c r="A89" t="inlineStr">
         <is>
           <t>Haglöfs Rosson Proof Mid</t>
@@ -13615,7 +8704,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
+    <row r="90">
       <c r="A90" t="inlineStr">
         <is>
           <t>Haglöfs Vertigo QL PROOF Low</t>
@@ -13716,7 +8805,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
+    <row r="91">
       <c r="A91" t="inlineStr">
         <is>
           <t>Vertigo Proof Low</t>
@@ -13811,7 +8900,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
+    <row r="92">
       <c r="A92" t="inlineStr">
         <is>
           <t>Breeze Mimic Hood</t>
@@ -13896,7 +8985,7 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
+    <row r="93">
       <c r="A93" t="inlineStr">
         <is>
           <t>Fram Mimic Jacket</t>
@@ -13981,7 +9070,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
+    <row r="94">
       <c r="A94" t="inlineStr">
         <is>
           <t>Hede Down Coat</t>
@@ -14070,7 +9159,7 @@
         <v>58.8</v>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
+    <row r="95">
       <c r="A95" t="inlineStr">
         <is>
           <t>Hede Down Hood</t>
@@ -14165,7 +9254,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
+    <row r="96">
       <c r="A96" t="inlineStr">
         <is>
           <t>Hede Down Vest</t>
@@ -14260,7 +9349,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
+    <row r="97">
       <c r="A97" t="inlineStr">
         <is>
           <t>L.I.M Down Hood Jacket</t>
@@ -14347,7 +9436,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
+    <row r="98">
       <c r="A98" t="inlineStr">
         <is>
           <t>L.I.M Down II Hood</t>
@@ -14432,7 +9521,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
+    <row r="99">
       <c r="A99" t="inlineStr">
         <is>
           <t>L.I.M Mimic Barrier Hood</t>
@@ -14523,7 +9612,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
+    <row r="100">
       <c r="A100" t="inlineStr">
         <is>
           <t>L.I.M Mimic Barrier Vest</t>
@@ -14610,7 +9699,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
+    <row r="101">
       <c r="A101" t="inlineStr">
         <is>
           <t>Long Down II Parka</t>
@@ -14699,7 +9788,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
+    <row r="102">
       <c r="A102" t="inlineStr">
         <is>
           <t>Long Mimic III Parka</t>
@@ -14788,7 +9877,7 @@
         <v>59.3</v>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
+    <row r="103">
       <c r="A103" t="inlineStr">
         <is>
           <t>Lugna Softshell Overshirt</t>
@@ -14883,7 +9972,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
+    <row r="104">
       <c r="A104" t="inlineStr">
         <is>
           <t>Mimic Alert 2.0 Hood</t>
@@ -14978,7 +10067,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
+    <row r="105">
       <c r="A105" t="inlineStr">
         <is>
           <t>Mimic Alert 2.0 Jacket</t>
@@ -15073,7 +10162,7 @@
         <v>34.2</v>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
+    <row r="106">
       <c r="A106" t="inlineStr">
         <is>
           <t>Mojo Down Hood</t>
@@ -15158,7 +10247,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
+    <row r="107">
       <c r="A107" t="inlineStr">
         <is>
           <t>Nallo Touring Down Hood</t>
@@ -15243,7 +10332,7 @@
         <v>36.8</v>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
+    <row r="108">
       <c r="A108" t="inlineStr">
         <is>
           <t>ROC Flash Down Hood</t>
@@ -15338,7 +10427,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
+    <row r="109">
       <c r="A109" t="inlineStr">
         <is>
           <t>ROC Flash Down Jacket</t>
@@ -15423,7 +10512,7 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
+    <row r="110">
       <c r="A110" t="inlineStr">
         <is>
           <t>ROC Flash Down Vest</t>
@@ -15508,7 +10597,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
+    <row r="111">
       <c r="A111" t="inlineStr">
         <is>
           <t>Rosson Down Hood</t>
@@ -15593,7 +10682,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
+    <row r="112">
       <c r="A112" t="inlineStr">
         <is>
           <t>Rosson Down Parka</t>
@@ -15678,7 +10767,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
+    <row r="113">
       <c r="A113" t="inlineStr">
         <is>
           <t>Salix Proof Mimic II Parka</t>
@@ -15763,7 +10852,7 @@
         <v>58.3</v>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
+    <row r="114">
       <c r="A114" t="inlineStr">
         <is>
           <t>Spitz Down Hood</t>
@@ -15848,7 +10937,7 @@
         <v>35.7</v>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
+    <row r="115">
       <c r="A115" t="inlineStr">
         <is>
           <t>Särna Mimic II Hood</t>
@@ -15943,7 +11032,7 @@
         <v>66.59999999999999</v>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
+    <row r="116">
       <c r="A116" t="inlineStr">
         <is>
           <t>Alert Mid Pant</t>
@@ -16038,7 +11127,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
+    <row r="117">
       <c r="A117" t="inlineStr">
         <is>
           <t>Alert Mid Shorts</t>
@@ -16125,7 +11214,7 @@
         <v>54.4</v>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
+    <row r="118">
       <c r="A118" t="inlineStr">
         <is>
           <t>Essential Tights</t>
@@ -16216,7 +11305,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
+    <row r="119">
       <c r="A119" t="inlineStr">
         <is>
           <t>Front Flex Pant</t>
@@ -16311,7 +11400,7 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
+    <row r="120">
       <c r="A120" t="inlineStr">
         <is>
           <t>Fuse Pant</t>
@@ -16398,7 +11487,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
+    <row r="121">
       <c r="A121" t="inlineStr">
         <is>
           <t>Fuse Short</t>
@@ -16485,7 +11574,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
+    <row r="122">
       <c r="A122" t="inlineStr">
         <is>
           <t>Hede Cargo II Pant</t>
@@ -16572,7 +11661,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
+    <row r="123">
       <c r="A123" t="inlineStr">
         <is>
           <t>Hede II Shorts</t>
@@ -16659,7 +11748,7 @@
         <v>55.6</v>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
+    <row r="124">
       <c r="A124" t="inlineStr">
         <is>
           <t>Hiking Tights</t>
@@ -16750,7 +11839,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
+    <row r="125">
       <c r="A125" t="inlineStr">
         <is>
           <t>Korp Lite Pant</t>
@@ -16837,7 +11926,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
+    <row r="126">
       <c r="A126" t="inlineStr">
         <is>
           <t>Korp Lite Shorts</t>
@@ -16924,7 +12013,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
+    <row r="127">
       <c r="A127" t="inlineStr">
         <is>
           <t>L.I.M Pace Shorts</t>
@@ -17011,7 +12100,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
+    <row r="128">
       <c r="A128" t="inlineStr">
         <is>
           <t>L.I.M Windpace Hybrid Pant</t>
@@ -17098,7 +12187,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
+    <row r="129">
       <c r="A129" t="inlineStr">
         <is>
           <t>Levante Pant</t>
@@ -17193,7 +12282,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
+    <row r="130">
       <c r="A130" t="inlineStr">
         <is>
           <t>Levante Shorts</t>
@@ -17280,7 +12369,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
+    <row r="131">
       <c r="A131" t="inlineStr">
         <is>
           <t>Lite Standard Zip-Off II Pant</t>
@@ -17367,7 +12456,7 @@
         <v>58.6</v>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
+    <row r="132">
       <c r="A132" t="inlineStr">
         <is>
           <t>Lizard Softshell II Shorts</t>
@@ -17454,7 +12543,7 @@
         <v>67.09999999999999</v>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
+    <row r="133">
       <c r="A133" t="inlineStr">
         <is>
           <t>Magma Rugged Pant</t>
@@ -17549,7 +12638,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
+    <row r="134">
       <c r="A134" t="inlineStr">
         <is>
           <t>Magma Rugged Wide Pant</t>
@@ -17636,7 +12725,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
+    <row r="135">
       <c r="A135" t="inlineStr">
         <is>
           <t>Mid Standard II Pant</t>
@@ -17707,7 +12796,7 @@
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
     </row>
-    <row r="136" ht="60" customHeight="1">
+    <row r="136">
       <c r="A136" t="inlineStr">
         <is>
           <t>Mid Standard II Shorts</t>
@@ -17778,7 +12867,7 @@
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
     </row>
-    <row r="137" ht="60" customHeight="1">
+    <row r="137">
       <c r="A137" t="inlineStr">
         <is>
           <t>Mimic Silver II Pant</t>
@@ -17863,7 +12952,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
+    <row r="138">
       <c r="A138" t="inlineStr">
         <is>
           <t>ROC Lite Slim II Pant</t>
@@ -17946,7 +13035,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
+    <row r="139">
       <c r="A139" t="inlineStr">
         <is>
           <t>Solis Zip Off Pant</t>
@@ -18041,7 +13130,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
+    <row r="140">
       <c r="A140" t="inlineStr">
         <is>
           <t>Solvik Seersucker Shorts</t>
@@ -18128,7 +13217,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
+    <row r="141">
       <c r="A141" t="inlineStr">
         <is>
           <t>Sun Capsule Pant</t>
@@ -18199,7 +13288,7 @@
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
     </row>
-    <row r="142" ht="60" customHeight="1">
+    <row r="142">
       <c r="A142" t="inlineStr">
         <is>
           <t>Brisen Tech Mid Hood</t>
@@ -18294,7 +13383,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
+    <row r="143">
       <c r="A143" t="inlineStr">
         <is>
           <t>Buteo Mid II Jacket</t>
@@ -18389,7 +13478,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
+    <row r="144">
       <c r="A144" t="inlineStr">
         <is>
           <t>Funäs Pile Hood</t>
@@ -18474,7 +13563,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
+    <row r="145">
       <c r="A145" t="inlineStr">
         <is>
           <t>Haglöfs Hoodie</t>
@@ -18569,7 +13658,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
+    <row r="146">
       <c r="A146" t="inlineStr">
         <is>
           <t>Korp Mid Halfzip</t>
@@ -18664,7 +13753,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
+    <row r="147">
       <c r="A147" t="inlineStr">
         <is>
           <t>Korp Mid Hood</t>
@@ -18759,7 +13848,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
+    <row r="148">
       <c r="A148" t="inlineStr">
         <is>
           <t>Korp Mid Jacket</t>
@@ -18854,7 +13943,7 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
+    <row r="149">
       <c r="A149" t="inlineStr">
         <is>
           <t>L.I.M Mid Hybrid</t>
@@ -18941,7 +14030,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
+    <row r="150">
       <c r="A150" t="inlineStr">
         <is>
           <t>L.I.M Mid Multi II Hood</t>
@@ -19036,7 +14125,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
+    <row r="151">
       <c r="A151" t="inlineStr">
         <is>
           <t>L.I.M Mid Multi Jacket</t>
@@ -19123,7 +14212,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
+    <row r="152">
       <c r="A152" t="inlineStr">
         <is>
           <t>L.I.M Mid Reversible Crew</t>
@@ -19210,7 +14299,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
+    <row r="153">
       <c r="A153" t="inlineStr">
         <is>
           <t>Nallo Touring Hybrid Mid</t>
@@ -19305,7 +14394,7 @@
         <v>37.3</v>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
+    <row r="154">
       <c r="A154" t="inlineStr">
         <is>
           <t>Rosson II Tights</t>
@@ -19390,7 +14479,7 @@
         <v>56.6</v>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
+    <row r="155">
       <c r="A155" t="inlineStr">
         <is>
           <t>Rosson Mid II Hood</t>
@@ -19485,7 +14574,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
+    <row r="156">
       <c r="A156" t="inlineStr">
         <is>
           <t>Rosson Mid II Jacket</t>
@@ -19580,7 +14669,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
+    <row r="157">
       <c r="A157" t="inlineStr">
         <is>
           <t>Swook II Mid Hood</t>
@@ -19675,7 +14764,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
+    <row r="158">
       <c r="A158" t="inlineStr">
         <is>
           <t>Swook II Mid Jacket</t>
@@ -19770,7 +14859,7 @@
         <v>53.7</v>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
+    <row r="159">
       <c r="A159" t="inlineStr">
         <is>
           <t>Swook Mid Halfzip W</t>
@@ -19869,7 +14958,7 @@
         <v>36.8</v>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
+    <row r="160">
       <c r="A160" t="inlineStr">
         <is>
           <t>Swook Mid Sweater M</t>
@@ -19968,7 +15057,7 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
+    <row r="161">
       <c r="A161" t="inlineStr">
         <is>
           <t>Vara Alpha Sweater</t>
@@ -20063,7 +15152,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
+    <row r="162">
       <c r="A162" t="inlineStr">
         <is>
           <t>Vassi Mid Hood</t>
@@ -20148,7 +15237,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
+    <row r="163">
       <c r="A163" t="inlineStr">
         <is>
           <t>Latnja 18L</t>
@@ -20233,7 +15322,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
+    <row r="164">
       <c r="A164" t="inlineStr">
         <is>
           <t>Nallo Pro 40L</t>
@@ -20318,7 +15407,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
+    <row r="165">
       <c r="A165" t="inlineStr">
         <is>
           <t>Vassi Pro 32L</t>
@@ -20403,7 +15492,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
+    <row r="166">
       <c r="A166" t="inlineStr">
         <is>
           <t>Alert GTX II Jacket</t>
@@ -20494,7 +15583,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
+    <row r="167">
       <c r="A167" t="inlineStr">
         <is>
           <t>Alper Proof Jacket</t>
@@ -20579,7 +15668,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
+    <row r="168">
       <c r="A168" t="inlineStr">
         <is>
           <t>Alper Proof Pant</t>
@@ -20664,7 +15753,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
+    <row r="169">
       <c r="A169" t="inlineStr">
         <is>
           <t>Astral GTX II Jacket</t>
@@ -20759,7 +15848,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
+    <row r="170">
       <c r="A170" t="inlineStr">
         <is>
           <t>Breeze Proof Jacket</t>
@@ -20854,7 +15943,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
+    <row r="171">
       <c r="A171" t="inlineStr">
         <is>
           <t>Front Proof II Jacket</t>
@@ -20949,7 +16038,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
+    <row r="172">
       <c r="A172" t="inlineStr">
         <is>
           <t>Holm GTX II Pant</t>
@@ -21044,7 +16133,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
+    <row r="173">
       <c r="A173" t="inlineStr">
         <is>
           <t>Klyva GTX II Jacket</t>
@@ -21135,7 +16224,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
+    <row r="174">
       <c r="A174" t="inlineStr">
         <is>
           <t>Korp Proof II Pant</t>
@@ -21230,7 +16319,7 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
+    <row r="175">
       <c r="A175" t="inlineStr">
         <is>
           <t>Korp Proof Jacket</t>
@@ -21325,7 +16414,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
+    <row r="176">
       <c r="A176" t="inlineStr">
         <is>
           <t>L.I.M Airak 2,5L Jacket</t>
@@ -21410,7 +16499,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
+    <row r="177">
       <c r="A177" t="inlineStr">
         <is>
           <t>L.I.M Airak 2,5L Pant</t>
@@ -21495,7 +16584,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
+    <row r="178">
       <c r="A178" t="inlineStr">
         <is>
           <t>L.I.M Airak 2,5L Proof II Jacket</t>
@@ -21582,7 +16671,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
+    <row r="179">
       <c r="A179" t="inlineStr">
         <is>
           <t>L.I.M Airak 2,5L Proof II Pant</t>
@@ -21669,7 +16758,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
+    <row r="180">
       <c r="A180" t="inlineStr">
         <is>
           <t>L.I.M Airak GTX Jacket</t>
@@ -21754,7 +16843,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
+    <row r="181">
       <c r="A181" t="inlineStr">
         <is>
           <t>L.I.M GTX III Jacket</t>
@@ -21849,7 +16938,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
+    <row r="182">
       <c r="A182" t="inlineStr">
         <is>
           <t>L.I.M GTX III Pant</t>
@@ -21920,7 +17009,7 @@
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr"/>
     </row>
-    <row r="183" ht="60" customHeight="1">
+    <row r="183">
       <c r="A183" t="inlineStr">
         <is>
           <t>L.I.M Light Proof Jacket</t>
@@ -22007,7 +17096,7 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
+    <row r="184">
       <c r="A184" t="inlineStr">
         <is>
           <t>L.I.M Windpack Hood Jacket</t>
@@ -22094,7 +17183,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
+    <row r="185">
       <c r="A185" t="inlineStr">
         <is>
           <t>Latnja GTX Insulated II Jacket</t>
@@ -22179,7 +17268,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
+    <row r="186">
       <c r="A186" t="inlineStr">
         <is>
           <t>Latnja GTX Insulated II Pant</t>
@@ -22264,7 +17353,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
+    <row r="187">
       <c r="A187" t="inlineStr">
         <is>
           <t>Ljusna Proof Parka</t>
@@ -22359,7 +17448,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
+    <row r="188">
       <c r="A188" t="inlineStr">
         <is>
           <t>Nallo Touring GTX Jacket</t>
@@ -22444,7 +17533,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
+    <row r="189">
       <c r="A189" t="inlineStr">
         <is>
           <t>Nallo Touring GTX Pant</t>
@@ -22529,7 +17618,7 @@
         <v>37.2</v>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
+    <row r="190">
       <c r="A190" t="inlineStr">
         <is>
           <t>Norrvind Shield Hood</t>
@@ -22624,7 +17713,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
+    <row r="191">
       <c r="A191" t="inlineStr">
         <is>
           <t>Ozka Proof Jacket</t>
@@ -22719,7 +17808,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
+    <row r="192">
       <c r="A192" t="inlineStr">
         <is>
           <t>Ozka Proof Pant</t>
@@ -22814,7 +17903,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
+    <row r="193">
       <c r="A193" t="inlineStr">
         <is>
           <t>ROC Sight GTX Jacket</t>
@@ -22909,7 +17998,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
+    <row r="194">
       <c r="A194" t="inlineStr">
         <is>
           <t>Saulo Proof Jacket</t>
@@ -22994,7 +18083,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
+    <row r="195">
       <c r="A195" t="inlineStr">
         <is>
           <t>Saulo Proof Pant</t>
@@ -23079,7 +18168,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
+    <row r="196">
       <c r="A196" t="inlineStr">
         <is>
           <t>Skalvik Softshell Parka</t>
@@ -23174,7 +18263,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="197" ht="60" customHeight="1">
+    <row r="197">
       <c r="A197" t="inlineStr">
         <is>
           <t>Spitz GTX Pro II Jacket</t>
@@ -23269,7 +18358,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="198" ht="60" customHeight="1">
+    <row r="198">
       <c r="A198" t="inlineStr">
         <is>
           <t>Tarre Proof Insulated Jacket</t>
@@ -23354,7 +18443,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="199" ht="60" customHeight="1">
+    <row r="199">
       <c r="A199" t="inlineStr">
         <is>
           <t>Tarre Proof Insulated Pant</t>
@@ -23439,7 +18528,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="200" ht="60" customHeight="1">
+    <row r="200">
       <c r="A200" t="inlineStr">
         <is>
           <t>Vara Down GTX Parka</t>
@@ -23524,7 +18613,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="201" ht="60" customHeight="1">
+    <row r="201">
       <c r="A201" t="inlineStr">
         <is>
           <t>Vassi GTX II Jacket</t>
@@ -23609,7 +18698,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="202" ht="60" customHeight="1">
+    <row r="202">
       <c r="A202" t="inlineStr">
         <is>
           <t>Vassi GTX II Pant</t>
@@ -23694,7 +18783,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="203" ht="60" customHeight="1">
+    <row r="203">
       <c r="A203" t="inlineStr">
         <is>
           <t>Vassi GTX Pro II Bib</t>
@@ -23779,7 +18868,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="204" ht="60" customHeight="1">
+    <row r="204">
       <c r="A204" t="inlineStr">
         <is>
           <t>Vassi GTX Pro II Jacket</t>
@@ -23864,7 +18953,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="205" ht="60" customHeight="1">
+    <row r="205">
       <c r="A205" t="inlineStr">
         <is>
           <t>Yra Mimic Proof Parka</t>
@@ -23949,7 +19038,7 @@
         <v>53.7</v>
       </c>
     </row>
-    <row r="206" ht="60" customHeight="1">
+    <row r="206">
       <c r="A206" t="inlineStr">
         <is>
           <t>Moonlite</t>
@@ -24048,7 +19137,7 @@
         <v>34.3</v>
       </c>
     </row>
-    <row r="207" ht="60" customHeight="1">
+    <row r="207">
       <c r="A207" t="inlineStr">
         <is>
           <t>Moonlite +7</t>
@@ -24143,7 +19232,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="208" ht="60" customHeight="1">
+    <row r="208">
       <c r="A208" t="inlineStr">
         <is>
           <t>Moonlite -1</t>
@@ -24238,7 +19327,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="209" ht="60" customHeight="1">
+    <row r="209">
       <c r="A209" t="inlineStr">
         <is>
           <t>Musca -1</t>
@@ -24333,7 +19422,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="210" ht="60" customHeight="1">
+    <row r="210">
       <c r="A210" t="inlineStr">
         <is>
           <t>Musca -13</t>
@@ -24428,7 +19517,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="211" ht="60" customHeight="1">
+    <row r="211">
       <c r="A211" t="inlineStr">
         <is>
           <t>Musca -26</t>
@@ -24523,7 +19612,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="212" ht="60" customHeight="1">
+    <row r="212">
       <c r="A212" t="inlineStr">
         <is>
           <t>Musca -5</t>
@@ -24618,7 +19707,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="213" ht="60" customHeight="1">
+    <row r="213">
       <c r="A213" t="inlineStr">
         <is>
           <t>Tarius +1</t>
@@ -24713,7 +19802,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="214" ht="60" customHeight="1">
+    <row r="214">
       <c r="A214" t="inlineStr">
         <is>
           <t>Tarius +6</t>
@@ -24798,7 +19887,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="215" ht="60" customHeight="1">
+    <row r="215">
       <c r="A215" t="inlineStr">
         <is>
           <t>Tarius -18</t>
@@ -24893,7 +19982,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="216" ht="60" customHeight="1">
+    <row r="216">
       <c r="A216" t="inlineStr">
         <is>
           <t>Tarius -5</t>
@@ -24988,7 +20077,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="217" ht="60" customHeight="1">
+    <row r="217">
       <c r="A217" t="inlineStr">
         <is>
           <t>Tarius Lite +8</t>
@@ -25083,7 +20172,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="218" ht="60" customHeight="1">
+    <row r="218">
       <c r="A218" t="inlineStr">
         <is>
           <t>Korp Softshell Hood</t>
@@ -25178,7 +20267,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="219" ht="60" customHeight="1">
+    <row r="219">
       <c r="A219" t="inlineStr">
         <is>
           <t>Korp Softshell Pant</t>
@@ -25273,7 +20362,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="220" ht="60" customHeight="1">
+    <row r="220">
       <c r="A220" t="inlineStr">
         <is>
           <t>ROC Sight Softshell II Jacket</t>
@@ -25368,7 +20457,7 @@
         <v>42.4</v>
       </c>
     </row>
-    <row r="221" ht="60" customHeight="1">
+    <row r="221">
       <c r="A221" t="inlineStr">
         <is>
           <t>ROC Sight Softshell II Pant</t>
@@ -25463,7 +20552,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="222" ht="60" customHeight="1">
+    <row r="222">
       <c r="A222" t="inlineStr">
         <is>
           <t>Warm Flex Pant</t>
@@ -25548,7 +20637,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="223" ht="60" customHeight="1">
+    <row r="223">
       <c r="A223" t="inlineStr">
         <is>
           <t>Haglöfs LS Tee</t>
@@ -25643,7 +20732,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="224" ht="60" customHeight="1">
+    <row r="224">
       <c r="A224" t="inlineStr">
         <is>
           <t>Haglöfs Tee</t>
@@ -25738,7 +20827,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="225" ht="60" customHeight="1">
+    <row r="225">
       <c r="A225" t="inlineStr">
         <is>
           <t>Kaise Wool II LS Tee</t>
@@ -25825,7 +20914,7 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="226" ht="60" customHeight="1">
+    <row r="226">
       <c r="A226" t="inlineStr">
         <is>
           <t>Kaise Wool II Tee</t>
@@ -25912,7 +21001,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="227" ht="60" customHeight="1">
+    <row r="227">
       <c r="A227" t="inlineStr">
         <is>
           <t>Kaise Wool Tank Top</t>
@@ -26003,7 +21092,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="228" ht="60" customHeight="1">
+    <row r="228">
       <c r="A228" t="inlineStr">
         <is>
           <t>L.I.M Delta Crop Tee</t>
@@ -26094,7 +21183,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="229" ht="60" customHeight="1">
+    <row r="229">
       <c r="A229" t="inlineStr">
         <is>
           <t>L.I.M Delta Tee</t>
@@ -26185,7 +21274,7 @@
         <v>46.2</v>
       </c>
     </row>
-    <row r="230" ht="60" customHeight="1">
+    <row r="230">
       <c r="A230" t="inlineStr">
         <is>
           <t>L.I.M Light T-Shirt</t>
@@ -26272,7 +21361,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="231" ht="60" customHeight="1">
+    <row r="231">
       <c r="A231" t="inlineStr">
         <is>
           <t>L.I.M Ridge Tank</t>
@@ -26367,7 +21456,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="232" ht="60" customHeight="1">
+    <row r="232">
       <c r="A232" t="inlineStr">
         <is>
           <t>L.I.M Ridge Tee</t>
@@ -26458,7 +21547,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="233" ht="60" customHeight="1">
+    <row r="233">
       <c r="A233" t="inlineStr">
         <is>
           <t>L.I.M Sunpack Hoodie</t>
@@ -26545,7 +21634,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="234" ht="60" customHeight="1">
+    <row r="234">
       <c r="A234" t="inlineStr">
         <is>
           <t>Outsiders Graphic Tee</t>
@@ -26640,7 +21729,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="235" ht="60" customHeight="1">
+    <row r="235">
       <c r="A235" t="inlineStr">
         <is>
           <t>Outsiders Tee</t>
@@ -26735,7 +21824,7 @@
         <v>32.3</v>
       </c>
     </row>
-    <row r="236" ht="60" customHeight="1">
+    <row r="236">
       <c r="A236" t="inlineStr">
         <is>
           <t>Ridge Hike Tee</t>
@@ -26826,7 +21915,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="237" ht="60" customHeight="1">
+    <row r="237">
       <c r="A237" t="inlineStr">
         <is>
           <t>Ridge II LS Tee</t>
@@ -26913,7 +22002,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="238" ht="60" customHeight="1">
+    <row r="238">
       <c r="A238" t="inlineStr">
         <is>
           <t>Ridge II Tee</t>
@@ -27000,7 +22089,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="239" ht="60" customHeight="1">
+    <row r="239">
       <c r="A239" t="inlineStr">
         <is>
           <t>Salo Dress</t>
@@ -27091,7 +22180,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="240" ht="60" customHeight="1">
+    <row r="240">
       <c r="A240" t="inlineStr">
         <is>
           <t>Salo Shirt II</t>
@@ -27178,7 +22267,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="241" ht="60" customHeight="1">
+    <row r="241">
       <c r="A241" t="inlineStr">
         <is>
           <t>Salo Shirt SS II</t>
@@ -27269,7 +22358,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="242" ht="60" customHeight="1">
+    <row r="242">
       <c r="A242" t="inlineStr">
         <is>
           <t>Selme LS Crewneck</t>
@@ -27364,7 +22453,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="243" ht="60" customHeight="1">
+    <row r="243">
       <c r="A243" t="inlineStr">
         <is>
           <t>Solvik Seersucker SS Shirt</t>
@@ -27451,7 +22540,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="244" ht="60" customHeight="1">
+    <row r="244">
       <c r="A244" t="inlineStr">
         <is>
           <t>Sun Capsule Halfzip</t>
@@ -27522,7 +22611,7 @@
       <c r="X244" t="inlineStr"/>
       <c r="Y244" t="inlineStr"/>
     </row>
-    <row r="245" ht="60" customHeight="1">
+    <row r="245">
       <c r="A245" t="inlineStr">
         <is>
           <t>Trekk Tech II LS Tee</t>
@@ -27609,7 +22698,7 @@
         <v>60.8</v>
       </c>
     </row>
-    <row r="246" ht="60" customHeight="1">
+    <row r="246">
       <c r="A246" t="inlineStr">
         <is>
           <t>Trekk Tech II Tee</t>
@@ -27696,7 +22785,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="247" ht="60" customHeight="1">
+    <row r="247">
       <c r="A247" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon GTX Low</t>
@@ -27791,7 +22880,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="248" ht="60" customHeight="1">
+    <row r="248">
       <c r="A248" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon GTX Mid</t>
@@ -27886,7 +22975,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="249" ht="60" customHeight="1">
+    <row r="249">
       <c r="A249" t="inlineStr">
         <is>
           <t>Haglöfs L.I.M Horizon Low</t>
@@ -27981,7 +23070,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="250" ht="60" customHeight="1">
+    <row r="250">
       <c r="A250" t="inlineStr">
         <is>
           <t>L.I.M Light Low</t>
@@ -28068,7 +23157,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="251" ht="60" customHeight="1">
+    <row r="251">
       <c r="A251" t="inlineStr">
         <is>
           <t>L.I.M Ultralight GTX Low</t>
@@ -28155,7 +23244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="252" ht="60" customHeight="1">
+    <row r="252">
       <c r="A252" t="inlineStr">
         <is>
           <t>L.I.M Ultralight Low</t>
@@ -28242,7 +23331,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="253" ht="60" customHeight="1">
+    <row r="253">
       <c r="A253" t="inlineStr">
         <is>
           <t>Oxo 60 W</t>
@@ -28337,7 +23426,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="254" ht="60" customHeight="1">
+    <row r="254">
       <c r="A254" t="inlineStr">
         <is>
           <t>Oxo 80</t>
@@ -28432,7 +23521,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="255" ht="60" customHeight="1">
+    <row r="255">
       <c r="A255" t="inlineStr">
         <is>
           <t>Haglöfs Incline GTX Mid</t>
@@ -28527,7 +23616,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="256" ht="60" customHeight="1">
+    <row r="256">
       <c r="A256" t="inlineStr">
         <is>
           <t>Haglöfs Incline Pro GTX High</t>
@@ -28622,7 +23711,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="257" ht="60" customHeight="1">
+    <row r="257">
       <c r="A257" t="inlineStr">
         <is>
           <t>Haglöfs Scand GTX Mid</t>
@@ -28703,7 +23792,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="258" ht="60" customHeight="1">
+    <row r="258">
       <c r="A258" t="inlineStr">
         <is>
           <t>Haglöfs Solid Pro 2 GTX Mid</t>
@@ -28794,7 +23883,7 @@
         <v>57.2</v>
       </c>
     </row>
-    <row r="259" ht="60" customHeight="1">
+    <row r="259">
       <c r="A259" t="inlineStr">
         <is>
           <t>Haglöfs Solid Pro 2 WL GTX Mid</t>
@@ -28880,9 +23969,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z259"/>
+  <autoFilter ref="A1:Y259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28892,7 +23980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28962,94 +24050,82 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Product Image</t>
+          <t>Core Assortment FW27</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The franchise's representative SS28 colorway photo, from the same Pic Centric workbook. Blank for FW27-only franchises (pending an FW27 image source) and for the small number of SS28 codes with no photo anchored in that file. CAVEAT: these are floating images anchored to a fixed row position, not tied to the row's data -- using Excel's Sort feature (not its Filter arrows, which is safe) can detach an image from its franchise. Re-run build_franchise_list.py for a clean, re-aligned copy rather than fixing it by hand.</t>
+          <t>Yes/No, from the flag already in the SS26 tiering workbook (57/1,860 Base+Gender rows = 'Yes'), rolled up to Base grain (Yes if either gender was Yes).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Core Assortment FW27</t>
+          <t>Core Assortment SS28</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Yes/No, from the flag already in the SS26 tiering workbook (57/1,860 Base+Gender rows = 'Yes'), rolled up to Base grain (Yes if either gender was Yes).</t>
+          <t>No source yet -- the flag was only ever defined for FW27. Left as 'To confirm' for every row until Tobias/Isabelle define it for SS28.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Core Assortment SS28</t>
+          <t># active colors</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>No source yet -- the flag was only ever defined for FW27. Left as 'To confirm' for every row until Tobias/Isabelle define it for SS28.</t>
+          <t>Sum of active colorways (the colorway-level Active flag, not just a row listed in the sheet) across every style rolled into this franchise -- both genders, both seasons. A colorway still in the file but not Active this season (e.g. a discontinued or carried-forward-for-reference color) is not counted. CAVEAT: 88/616 main-range style rows (incl. 18 Shell styles) have NO colorway sub-rows at all in this export -- showing 0 here, which may be a real single-color item or a data gap in the export. Worth confirming with Tobias before treating 0 as fact.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t># active colors</t>
+          <t>ABS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sum of active colorways (the colorway-level Active flag, not just a row listed in the sheet) across every style rolled into this franchise -- both genders, both seasons. A colorway still in the file but not Active this season (e.g. a discontinued or carried-forward-for-reference color) is not counted. CAVEAT: 88/616 main-range style rows (incl. 18 Shell styles) have NO colorway sub-rows at all in this export -- showing 0 here, which may be a real single-color item or a data gap in the export. Worth confirming with Tobias before treating 0 as fact.</t>
+          <t>Yes if an ABS or ABS Exclusive variant of this franchise exists anywhere in FW27/SS28 (even though RR-006 keeps those styles out of the main range count above) -- so a reviewer knows one exists before deciding the franchise's main-range fate.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>Asia Fit</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Yes if an ABS or ABS Exclusive variant of this franchise exists anywhere in FW27/SS28 (even though RR-006 keeps those styles out of the main range count above) -- so a reviewer knows one exists before deciding the franchise's main-range fate.</t>
+          <t>Yes if an 'AF'-suffixed (Asian Fit) variant of this franchise exists anywhere in FW27/SS28 (RR-007) -- always also ABS=Yes, since every AF style is tagged ABS Exclusive in the source data.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Asia Fit</t>
+          <t>Status FW27 / Status SS28</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Yes if an 'AF'-suffixed (Asian Fit) variant of this franchise exists anywhere in FW27/SS28 (RR-007) -- always also ABS=Yes, since every AF style is tagged ABS Exclusive in the source data.</t>
+          <t>Carry Over / New / Update, from the forecast files' Status field -- shown per season since a franchise can differ between them (e.g. New in FW27, Carry Over in SS28). Blank if no forecast row matched that season (see RR-014).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Status FW27 / Status SS28</t>
+          <t>Forecast Qty / GP% (total, DTC, Wholesale)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Carry Over / New / Update, from the forecast files' Status field -- shown per season since a franchise can differ between them (e.g. New in FW27, Carry Over in SS28). Blank if no forecast row matched that season (see RR-014).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Forecast Qty / GP% (total, DTC, Wholesale)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Summed across every style and season rolled into the franchise, from the two forecast files (RR-011/RR-012). Blank (not 0) when none of the franchise's styles have a forecast match -- 25/616 main-range style rows don't (RR-014). GP% blended vs. DTC/Wholesale split -- blended hides a real spread, so both are shown.</t>
         </is>

--- a/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
+++ b/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
@@ -629,7 +629,9 @@
           <t>Everyday Outdoor; Freeride Ski &amp; Snowboard; Skitouring; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>65</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>1</v>
@@ -719,7 +721,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>61.3</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>1</v>
@@ -1465,7 +1469,9 @@
           <t>Mountaineering / Alpinism; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>61</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1</v>
@@ -1555,7 +1561,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>64</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1</v>
@@ -1645,7 +1653,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>74.3</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1</v>
@@ -1735,7 +1745,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>61.3</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1</v>
@@ -2089,7 +2101,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>61.3</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>1</v>
@@ -2179,7 +2193,9 @@
           <t>Everyday Outdoor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>62</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>1</v>
@@ -2269,7 +2285,9 @@
           <t>Everyday Outdoor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>62</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>1</v>
@@ -2359,7 +2377,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>61.3</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>1</v>
@@ -2449,7 +2469,9 @@
           <t>Everyday Outdoor; Freeride Ski &amp; Snowboard; Resort Skiing</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>60</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>1</v>
@@ -5425,7 +5447,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing; Skitouring; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>64</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
         <v>2</v>
@@ -5515,7 +5539,9 @@
           <t>Everyday Outdoor; Freeride Ski &amp; Snowboard; Resort Skiing; Skitouring; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>57</v>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
         <v>2</v>
@@ -5605,7 +5631,9 @@
           <t>Freeride Ski &amp; Snowboard; Mountaineering / Alpinism; Resort Skiing; Ski Mountaineering; Skitouring; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>60</v>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
         <v>2</v>
@@ -8399,7 +8427,9 @@
           <t>Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="n">
+        <v>60</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
         <v>2</v>
@@ -8689,7 +8719,9 @@
           <t>Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
         <v>2</v>
@@ -9385,7 +9417,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="n">
+        <v>65</v>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
         <v>2</v>
@@ -9475,7 +9509,9 @@
           <t>Everyday Outdoor</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>61</v>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
         <v>2</v>
@@ -9569,7 +9605,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>64</v>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="n">
         <v>1</v>
@@ -9947,7 +9985,9 @@
           <t>Fast Hiking; Skitouring; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="n">
+        <v>60</v>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
         <v>2</v>
@@ -10229,7 +10269,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="n">
+        <v>65.40000000000001</v>
+      </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
         <v>1</v>
@@ -10323,7 +10365,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="n">
+        <v>65.40000000000001</v>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
         <v>1</v>
@@ -10713,7 +10757,9 @@
           <t>Freeride Ski &amp; Snowboard; Mountaineering / Alpinism; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="n">
+        <v>61.5</v>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
         <v>2</v>
@@ -10803,7 +10849,9 @@
           <t>Freeride Ski &amp; Snowboard; Mountaineering / Alpinism; Skitouring</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>55</v>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
         <v>2</v>
@@ -10993,7 +11041,9 @@
           <t>Mountaineering / Alpinism; Ski Mountaineering; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>60</v>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
         <v>2</v>
@@ -11083,7 +11133,9 @@
           <t>Mountaineering / Alpinism; Ski Mountaineering; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>66</v>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="n">
         <v>2</v>
@@ -11173,7 +11225,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="n">
+        <v>61</v>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
         <v>2</v>
@@ -11263,7 +11317,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>60</v>
+      </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="n">
         <v>2</v>
@@ -11353,7 +11409,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>61.5</v>
+      </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
         <v>2</v>
@@ -11443,7 +11501,9 @@
           <t>Expeditions; Mountaineering / Alpinism; Ski Mountaineering</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="n">
+        <v>55</v>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
         <v>2</v>
@@ -13549,7 +13609,9 @@
           <t>Everyday Outdoor; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>65</v>
+      </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="n">
         <v>2</v>
@@ -14191,7 +14253,9 @@
           <t>Everyday Outdoor</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="n">
+        <v>62.9</v>
+      </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
         <v>2</v>
@@ -15149,7 +15213,9 @@
           <t>Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="n">
+        <v>65</v>
+      </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="n">
         <v>2</v>
@@ -15947,7 +16013,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing; Ski Mountaineering; Skitouring</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="n">
+        <v>62.9</v>
+      </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="n">
         <v>2</v>
@@ -16037,7 +16105,9 @@
           <t>Freeride Ski &amp; Snowboard</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="n">
+        <v>59.3</v>
+      </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="n">
         <v>1</v>
@@ -16127,7 +16197,9 @@
           <t>Skitouring</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="n">
+        <v>52.2</v>
+      </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="n">
         <v>1</v>
@@ -16217,7 +16289,9 @@
           <t>Freeride Ski &amp; Snowboard</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="n">
+        <v>65</v>
+      </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="n">
         <v>1</v>
@@ -16403,7 +16477,9 @@
           <t>Mountaineering / Alpinism; Resort Skiing; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="n">
+        <v>60</v>
+      </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="n">
         <v>2</v>
@@ -16493,7 +16569,9 @@
           <t>Mountaineering / Alpinism; Resort Skiing</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="n">
+        <v>60</v>
+      </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="n">
         <v>2</v>
@@ -17279,7 +17357,9 @@
           <t>Everyday Outdoor; Fast Hiking; Trail Running; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="n">
+        <v>60</v>
+      </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="n">
         <v>2</v>
@@ -17369,7 +17449,9 @@
           <t>Everyday Outdoor; Fast Hiking; Trail Running; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="n">
+        <v>60</v>
+      </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="n">
         <v>2</v>
@@ -17635,7 +17717,9 @@
           <t>Everyday Outdoor; Fast Hiking; Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="n">
+        <v>50</v>
+      </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="n">
         <v>2</v>
@@ -18073,7 +18157,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="n">
+        <v>62</v>
+      </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="n">
         <v>2</v>
@@ -18163,7 +18249,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="n">
+        <v>64</v>
+      </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="n">
         <v>2</v>
@@ -18353,7 +18441,9 @@
           <t>Freeride Ski &amp; Snowboard; Mountaineering / Alpinism; Skitouring</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="n">
+        <v>55</v>
+      </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="n">
         <v>2</v>
@@ -18443,7 +18533,9 @@
           <t>Freeride Ski &amp; Snowboard; Mountaineering / Alpinism; Skitouring</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="n">
+        <v>55</v>
+      </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="n">
         <v>2</v>
@@ -18933,7 +19025,9 @@
           <t>Resort Skiing</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="n">
+        <v>60</v>
+      </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="n">
         <v>2</v>
@@ -19023,7 +19117,9 @@
           <t>Resort Skiing</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="n">
+        <v>60</v>
+      </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="n">
         <v>2</v>
@@ -19313,7 +19409,9 @@
           <t>Resort Skiing</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="n">
+        <v>62</v>
+      </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="n">
         <v>2</v>
@@ -19403,7 +19501,9 @@
           <t>Resort Skiing</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="n">
+        <v>63</v>
+      </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="n">
         <v>2</v>
@@ -19493,7 +19593,9 @@
           <t>Everyday Outdoor</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="n">
+        <v>55</v>
+      </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="n">
         <v>2</v>
@@ -19583,7 +19685,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing; Skitouring</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="n">
+        <v>59.2</v>
+      </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="n">
         <v>2</v>
@@ -19673,7 +19777,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="n">
+        <v>59.2</v>
+      </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="n">
         <v>2</v>
@@ -19763,7 +19869,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="n">
+        <v>59.2</v>
+      </c>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="n">
         <v>2</v>
@@ -19853,7 +19961,9 @@
           <t>Freeride Ski &amp; Snowboard; Resort Skiing; Skitouring</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="n">
+        <v>59.2</v>
+      </c>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="n">
         <v>2</v>
@@ -19943,7 +20053,9 @@
           <t>Everyday Outdoor</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="n">
+        <v>57</v>
+      </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="n">
         <v>2</v>
@@ -20837,7 +20949,9 @@
           <t>Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="n">
+        <v>52.2</v>
+      </c>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="n">
         <v>1</v>
@@ -21627,7 +21741,9 @@
           <t>Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="n">
+        <v>60</v>
+      </c>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="n">
         <v>2</v>
@@ -24925,7 +25041,9 @@
           <t>Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
       <c r="L257" t="inlineStr"/>
       <c r="M257" t="n">
         <v>1</v>
@@ -25107,7 +25225,9 @@
           <t>Trekking / Hiking</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="n">
+        <v>59.8</v>
+      </c>
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="n">
         <v>1</v>
@@ -25235,7 +25355,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Target GM0% from the SS28 'Pic Centric' workbook -- the FW27/SS28 range files themselves have no margin field (RR-008). SS28-only for now; blank for franchises with no SS28 code until an equivalent FW27 file arrives.</t>
+          <t>Target GM0% from the FW27+SS28 'Pic Centric' workbooks -- the FW27/SS28 range files themselves have no margin field (RR-008). Blank only for franchises with no Pic Centric match in either season.</t>
         </is>
       </c>
     </row>

--- a/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
+++ b/data/range_review/outputs/FW27_SS28_Franchise_Review_List.xlsx
@@ -442,7 +442,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Margin target</t>
+          <t>Target GM0%</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -25350,12 +25350,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Margin target</t>
+          <t>Target GM0%</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Target GM0% from the FW27+SS28 'Pic Centric' workbooks -- the FW27/SS28 range files themselves have no margin field (RR-008). Blank only for franchises with no Pic Centric match in either season.</t>
+          <t>A pricing/costing GOAL set during product costing (Target RRP vs. Target FOB), from the FW27+SS28 'Pic Centric' workbooks -- the FW27/SS28 range files themselves have no margin field (RR-008). NOT the same thing as Forecast GP% (the Forecast sheet/page's blended/DTC/Wholesale GP% columns), which is a forecast OUTCOME derived from FC3 volume, price and channel mix -- the two can genuinely differ, and the gap is itself worth a look. Blank only for franchises with no Pic Centric match in either season.</t>
         </is>
       </c>
     </row>
